--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,6 +493,44 @@
       </c>
       <c r="F2" t="n">
         <v>1873.577880859375</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1922.77001953125</v>
+      </c>
+      <c r="H2" t="n">
+        <v>49.192138671875</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.558399505514835</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1.220130314884305</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-07-21 03:31:15</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>24</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1925.20458984375</v>
       </c>
     </row>
   </sheetData>
@@ -506,7 +544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -603,6 +641,24 @@
           <t>1877.442017,1877.204590,1876.797119,1877.826172,1876.849731,1876.970825,1877.297363,1877.297119,1877.280884,1876.560181,1876.011230,1875.771973,1875.289307,1874.681641,1875.572388,1875.859375,1875.291748,1875.497437,1875.097412,1874.511719,1875.065674,1874.502075,1873.956299,1873.577881</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>1867.079956,1853.800049,1848.000000,1862.380005,1859.180054,1862.400024,1867.239990,1891.560059,1871.300049,1860.670044,1866.189941,1901.089966,1898.119995,1906.329956,1898.010010,1897.400024,1903.540039,1901.050049,1894.589966,1903.540039,1913.900024,1906.300049,1916.170044,1922.770020</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>10.362061,23.404541,28.797119,15.446167,17.669677,14.570801,10.057373,14.262940,5.980835,15.890137,9.821289,25.317993,22.830688,31.648315,22.437622,21.540649,28.248291,25.552612,19.492554,29.028320,38.834350,31.797974,42.213745,49.192139</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.554988,1.262517,1.558286,0.829378,0.950402,0.782367,0.538622,0.754030,0.319609,0.854001,0.526275,1.331762,1.202805,1.660170,1.182166,1.135272,1.483987,1.344131,1.028853,1.524965,2.029069,1.668047,2.203027,2.558399</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>1.220130314884305</v>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>1875.048340,1877.019287,1875.474365,1876.376343,1875.971924,1873.927979,1875.453979,1876.460449,1873.301758,1873.637939,1870.822266,1868.605713,1870.102783,1869.653809,1869.937988,1871.181885,1869.429077,1866.023682,1869.940430,1867.824951,1867.569580,1869.179932,1863.516357,1863.707031</t>
@@ -616,6 +672,49 @@
       <c r="M2" t="inlineStr">
         <is>
           <t>1872.552368,1870.937500,1869.330566,1870.117188,1867.649170,1866.812256,1866.338623,1866.149170,1865.640747,1863.329224,1860.798340,1858.688232,1858.617920,1855.901123,1855.123779,1855.679199,1854.498535,1852.960938,1850.050171,1848.266357,1848.167969,1844.511719,1844.890625,1844.204590</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-07-21 03:31:15</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>24</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>1921.732910,1921.634277,1921.937988,1923.443848,1922.829956,1923.478271,1924.910400,1925.087036,1925.714600,1924.514160,1924.456055,1925.101318,1923.960205,1923.725098,1923.904175,1923.616211,1924.223999,1923.730957,1923.489380,1923.617188,1923.829346,1925.102783,1925.842529,1925.204590</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>1917.355713,1922.012695,1919.313721,1919.401123,1921.230591,1918.906494,1921.270264,1924.113037,1920.694336,1922.198853,1921.366089,1916.194702,1917.369019,1917.748047,1918.340698,1917.905273,1917.958008,1917.209717,1918.196533,1915.456299,1917.239990,1921.618408,1917.398193,1916.763428</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>1907.859009,1904.376587,1902.559692,1903.225830,1898.378906,1897.147461,1896.985596,1893.948975,1893.554321,1889.665405,1888.268311,1884.862427,1884.738037,1883.569824,1880.457153,1879.935181,1878.177002,1876.502075,1869.637329,1867.996826,1868.086182,1868.271973,1869.400146,1868.550049</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>1913.900635,1911.617920,1911.142822,1911.756104,1908.929565,1907.915771,1908.181030,1907.647217,1907.792358,1903.803223,1902.291748,1901.830933,1901.338623,1898.902832,1897.166260,1898.534668,1898.078491,1894.950928,1892.376099,1892.025757,1890.947021,1890.281860,1892.522217,1891.007812</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,6 +531,44 @@
       </c>
       <c r="F3" t="n">
         <v>1925.20458984375</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1931.099975585938</v>
+      </c>
+      <c r="H3" t="n">
+        <v>5.8953857421875</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.3052864075770449</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.3756383728789763</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-07-22 03:29:46</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>24</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1932.864501953125</v>
       </c>
     </row>
   </sheetData>
@@ -544,7 +582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -702,6 +740,24 @@
           <t>1921.732910,1921.634277,1921.937988,1923.443848,1922.829956,1923.478271,1924.910400,1925.087036,1925.714600,1924.514160,1924.456055,1925.101318,1923.960205,1923.725098,1923.904175,1923.616211,1924.223999,1923.730957,1923.489380,1923.617188,1923.829346,1925.102783,1925.842529,1925.204590</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>1923.359985,1929.260010,1933.589966,1932.890015,1938.619995,1940.800049,1932.849976,1934.609985,1941.609985,1938.939941,1930.150024,1930.760010,1925.300049,1917.300049,1918.949951,1922.640015,1922.180054,1923.170044,1919.599976,1922.800049,1938.130005,1932.420044,1929.069946,1931.099976</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>1.627075,7.625733,11.651978,9.446167,15.790039,17.321778,7.939576,9.522949,15.895385,14.425781,5.693969,5.658692,1.339844,6.425049,4.954224,0.976196,2.043945,0.560913,3.889404,0.817139,14.300659,7.317261,3.227417,5.895386</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.084595,0.395267,0.602609,0.488707,0.814499,0.892507,0.410770,0.492241,0.818670,0.744004,0.295001,0.293081,0.069591,0.335109,0.258174,0.050774,0.106335,0.029166,0.202615,0.042497,0.737859,0.378658,0.167304,0.305286</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0.3756383728789763</v>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>1917.355713,1922.012695,1919.313721,1919.401123,1921.230591,1918.906494,1921.270264,1924.113037,1920.694336,1922.198853,1921.366089,1916.194702,1917.369019,1917.748047,1918.340698,1917.905273,1917.958008,1917.209717,1918.196533,1915.456299,1917.239990,1921.618408,1917.398193,1916.763428</t>
@@ -715,6 +771,49 @@
       <c r="M3" t="inlineStr">
         <is>
           <t>1913.900635,1911.617920,1911.142822,1911.756104,1908.929565,1907.915771,1908.181030,1907.647217,1907.792358,1903.803223,1902.291748,1901.830933,1901.338623,1898.902832,1897.166260,1898.534668,1898.078491,1894.950928,1892.376099,1892.025757,1890.947021,1890.281860,1892.522217,1891.007812</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-07-22 03:29:46</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>24</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1931.755615,1931.542358,1931.414185,1932.862305,1931.626831,1932.569092,1933.620605,1931.673462,1933.245361,1932.512207,1931.754883,1933.075195,1932.510498,1930.834961,1931.790283,1931.958252,1932.972900,1932.558105,1931.784180,1932.661987,1932.434326,1933.539795,1933.521851,1932.864502</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>1928.032715,1932.031006,1929.485352,1929.980835,1929.821655,1929.386230,1932.090332,1931.623291,1929.995850,1930.729980,1929.468018,1926.420410,1927.060059,1926.233521,1926.762085,1927.078491,1930.116577,1927.510254,1927.470825,1928.033203,1928.205811,1927.900391,1927.456421,1926.428223</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>1923.563110,1921.253784,1919.539307,1920.121582,1914.201904,1913.412231,1912.494385,1907.723755,1908.490234,1905.725830,1903.082031,1901.429443,1901.203979,1898.734131,1896.056396,1896.798584,1896.909058,1895.674072,1888.714111,1887.968750,1888.735107,1888.311035,1888.398682,1888.132324</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>1927.719971,1925.501709,1924.843262,1925.598389,1922.532471,1921.077881,1919.828613,1917.960571,1919.612061,1916.211182,1915.029541,1914.963623,1914.661865,1911.414917,1909.118896,1910.812256,1912.533447,1909.466064,1907.094238,1907.676147,1907.051270,1905.774780,1906.663208,1905.496704</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -569,6 +569,44 @@
       </c>
       <c r="F4" t="n">
         <v>1932.864501953125</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1922.599975585938</v>
+      </c>
+      <c r="H4" t="n">
+        <v>10.2645263671875</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.5338877820415686</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.4172979547539208</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-07-23 03:34:46</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>24</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1923.03125</v>
       </c>
     </row>
   </sheetData>
@@ -582,7 +620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -801,6 +839,24 @@
           <t>1931.755615,1931.542358,1931.414185,1932.862305,1931.626831,1932.569092,1933.620605,1931.673462,1933.245361,1932.512207,1931.754883,1933.075195,1932.510498,1930.834961,1931.790283,1931.958252,1932.972900,1932.558105,1931.784180,1932.661987,1932.434326,1933.539795,1933.521851,1932.864502</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>1935.489990,1918.079956,1916.270020,1912.880005,1919.800049,1923.199951,1929.410034,1926.160034,1915.589966,1938.810059,1932.119995,1941.949951,1949.420044,1937.660034,1929.910034,1924.300049,1926.030029,1937.930054,1937.430054,1933.540039,1931.400024,1927.650024,1926.339966,1922.599976</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>3.734375,13.462402,15.144165,19.982300,11.826782,9.369141,4.210571,5.513428,17.655395,6.297852,0.365112,8.874756,16.909546,6.825073,1.880249,7.658203,6.942871,5.371949,5.645874,0.878052,1.034302,5.889771,7.181885,10.264526</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.192942,0.701869,0.790294,1.044619,0.616042,0.487164,0.218231,0.286239,0.921669,0.324831,0.018897,0.457002,0.867414,0.352233,0.097427,0.397973,0.360476,0.277200,0.291410,0.045412,0.053552,0.305541,0.372825,0.533888</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0.4172979547539208</v>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>1928.032715,1932.031006,1929.485352,1929.980835,1929.821655,1929.386230,1932.090332,1931.623291,1929.995850,1930.729980,1929.468018,1926.420410,1927.060059,1926.233521,1926.762085,1927.078491,1930.116577,1927.510254,1927.470825,1928.033203,1928.205811,1927.900391,1927.456421,1926.428223</t>
@@ -814,6 +870,49 @@
       <c r="M4" t="inlineStr">
         <is>
           <t>1927.719971,1925.501709,1924.843262,1925.598389,1922.532471,1921.077881,1919.828613,1917.960571,1919.612061,1916.211182,1915.029541,1914.963623,1914.661865,1911.414917,1909.118896,1910.812256,1912.533447,1909.466064,1907.094238,1907.676147,1907.051270,1905.774780,1906.663208,1905.496704</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-07-23 03:34:46</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>24</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1922.198364,1921.192139,1921.234619,1922.578979,1921.290405,1922.337158,1923.579224,1922.411499,1924.189209,1924.078735,1924.380859,1924.989868,1924.573242,1923.459717,1924.351318,1924.696533,1925.066650,1924.489014,1923.668457,1924.288818,1924.254639,1923.715088,1923.282959,1923.031250</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>1920.710693,1921.844727,1919.191040,1921.843994,1921.150635,1922.070068,1920.826294,1921.520142,1920.604980,1924.359863,1921.637451,1919.919189,1921.485962,1921.973755,1920.755005,1919.849854,1921.038330,1917.654175,1918.843018,1918.577393,1919.483032,1916.256348,1916.341919,1916.663086</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>1913.027466,1911.017334,1907.837158,1908.398682,1903.704346,1903.891479,1902.960449,1899.796143,1900.630981,1898.597412,1897.022949,1895.951538,1893.895874,1891.333740,1889.936279,1888.225098,1888.426758,1886.109863,1878.601196,1878.027954,1876.149536,1875.175537,1872.944702,1872.709717</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>1917.818115,1914.835449,1912.982056,1914.146729,1910.950806,1910.235840,1910.891113,1909.390503,1910.650879,1908.881592,1908.233887,1907.980713,1907.283447,1903.963867,1903.356201,1903.570557,1904.319458,1901.108154,1899.116699,1898.130127,1896.780762,1894.432495,1894.257324,1894.185303</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -607,6 +607,44 @@
       </c>
       <c r="F5" t="n">
         <v>1923.03125</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1878.27001953125</v>
+      </c>
+      <c r="H5" t="n">
+        <v>44.76123046875</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.383109457282443</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.539974086681727</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-07-24 03:31:08</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>24</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1872.238525390625</v>
       </c>
     </row>
   </sheetData>
@@ -620,7 +658,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -900,6 +938,24 @@
           <t>1922.198364,1921.192139,1921.234619,1922.578979,1921.290405,1922.337158,1923.579224,1922.411499,1924.189209,1924.078735,1924.380859,1924.989868,1924.573242,1923.459717,1924.351318,1924.696533,1925.066650,1924.489014,1923.668457,1924.288818,1924.254639,1923.715088,1923.282959,1923.031250</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>1918.459961,1921.949951,1924.400024,1914.199951,1925.550049,1923.180054,1927.300049,1925.260010,1903.099976,1897.349976,1895.650024,1893.800049,1886.310059,1877.000000,1879.640015,1874.140015,1884.469971,1881.199951,1881.969971,1876.910034,1869.949951,1871.219971,1867.819946,1878.270020</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>3.738403,0.757812,3.165405,8.379028,4.259644,0.842896,3.720825,2.848511,21.089233,26.728759,28.730835,31.189819,38.263183,46.459717,44.711303,50.556518,40.596679,43.289063,41.698486,47.378784,54.304688,52.495117,55.463013,44.761230</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.194865,0.039429,0.164488,0.437730,0.221217,0.043828,0.193059,0.147955,1.108152,1.408742,1.515619,1.646944,2.028467,2.475211,2.378716,2.697585,2.154276,2.301141,2.215683,2.524297,2.904072,2.805395,2.969398,2.383109</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>1.539974086681727</v>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>1920.710693,1921.844727,1919.191040,1921.843994,1921.150635,1922.070068,1920.826294,1921.520142,1920.604980,1924.359863,1921.637451,1919.919189,1921.485962,1921.973755,1920.755005,1919.849854,1921.038330,1917.654175,1918.843018,1918.577393,1919.483032,1916.256348,1916.341919,1916.663086</t>
@@ -913,6 +969,49 @@
       <c r="M5" t="inlineStr">
         <is>
           <t>1917.818115,1914.835449,1912.982056,1914.146729,1910.950806,1910.235840,1910.891113,1909.390503,1910.650879,1908.881592,1908.233887,1907.980713,1907.283447,1903.963867,1903.356201,1903.570557,1904.319458,1901.108154,1899.116699,1898.130127,1896.780762,1894.432495,1894.257324,1894.185303</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-07-24 03:31:08</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>24</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1875.861816,1874.985474,1874.746094,1875.506592,1874.302002,1874.553467,1875.041016,1873.679321,1873.799072,1873.808105,1873.157959,1873.372070,1873.562988,1872.920166,1873.192993,1872.911621,1873.083496,1872.795166,1872.259766,1872.801025,1873.063110,1872.514526,1871.661499,1872.238525</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>1875.056763,1875.691895,1872.808350,1873.829712,1875.905762,1874.942871,1872.499390,1870.510742,1872.286743,1874.656738,1870.661011,1869.418457,1872.779175,1872.885254,1872.306152,1867.307861,1871.382568,1870.471191,1872.713867,1867.609863,1871.132080,1865.713379,1868.994751,1870.475342</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>1861.242188,1859.039795,1855.843262,1855.021240,1852.115234,1850.315186,1849.809082,1847.412598,1845.424316,1844.129517,1841.813232,1840.488525,1839.349365,1837.948486,1836.922363,1833.934814,1833.254395,1831.352905,1825.120850,1824.596558,1823.680176,1822.678711,1821.193359,1821.241943</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>1867.857666,1865.037354,1862.850342,1863.164551,1860.474731,1859.273926,1859.620850,1857.511597,1857.564453,1855.573853,1853.625122,1853.181641,1853.344238,1851.064575,1852.180664,1850.438232,1849.632690,1847.124023,1845.520752,1845.058594,1844.633789,1842.099121,1842.159668,1842.807373</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -645,6 +645,44 @@
       </c>
       <c r="F6" t="n">
         <v>1872.238525390625</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1857.829956054688</v>
+      </c>
+      <c r="H6" t="n">
+        <v>14.4085693359375</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.7755591026498319</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.6481572305569343</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-07-25 03:29:04</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>24</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1856.755126953125</v>
       </c>
     </row>
   </sheetData>
@@ -658,7 +696,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -999,6 +1037,24 @@
           <t>1875.861816,1874.985474,1874.746094,1875.506592,1874.302002,1874.553467,1875.041016,1873.679321,1873.799072,1873.808105,1873.157959,1873.372070,1873.562988,1872.920166,1873.192993,1872.911621,1873.083496,1872.795166,1872.259766,1872.801025,1873.063110,1872.514526,1871.661499,1872.238525</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1874.380005,1879.280029,1886.750000,1894.640015,1886.660034,1886.660034,1882.400024,1882.760010,1870.709961,1854.900024,1860.880005,1860.000000,1855.660034,1864.900024,1860.800049,1862.030029,1859.229980,1855.619995,1857.680054,1859.880005,1858.510010,1858.130005,1857.900024,1857.829956</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>1.481811,4.294555,12.003906,19.133423,12.358032,12.106567,7.359008,9.080689,3.089111,18.908081,12.277954,13.372070,17.902954,8.020142,12.392944,10.881592,13.853516,17.175171,14.579712,12.921020,14.553100,14.384521,13.761475,14.408569</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.079056,0.228521,0.636221,1.009871,0.655022,0.641693,0.390938,0.482307,0.165130,1.019358,0.659793,0.718928,0.964776,0.430057,0.666001,0.584394,0.745121,0.925576,0.784834,0.694723,0.783052,0.774140,0.740700,0.775559</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0.6481572305569343</v>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>1875.056763,1875.691895,1872.808350,1873.829712,1875.905762,1874.942871,1872.499390,1870.510742,1872.286743,1874.656738,1870.661011,1869.418457,1872.779175,1872.885254,1872.306152,1867.307861,1871.382568,1870.471191,1872.713867,1867.609863,1871.132080,1865.713379,1868.994751,1870.475342</t>
@@ -1012,6 +1068,49 @@
       <c r="M6" t="inlineStr">
         <is>
           <t>1867.857666,1865.037354,1862.850342,1863.164551,1860.474731,1859.273926,1859.620850,1857.511597,1857.564453,1855.573853,1853.625122,1853.181641,1853.344238,1851.064575,1852.180664,1850.438232,1849.632690,1847.124023,1845.520752,1845.058594,1844.633789,1842.099121,1842.159668,1842.807373</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-07-25 03:29:04</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>24</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1857.638672,1857.595947,1857.676270,1858.183594,1857.608643,1858.190430,1858.267700,1858.046021,1858.175781,1858.000488,1857.212646,1857.385986,1857.358154,1857.264404,1857.673340,1856.898682,1857.429443,1856.821045,1857.013672,1856.931274,1857.208740,1856.152588,1855.703003,1856.755127</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>1857.093018,1857.490845,1856.793091,1857.337402,1859.642456,1858.813965,1856.568115,1854.664062,1858.069824,1859.367188,1855.819702,1856.816162,1856.145752,1858.896729,1858.298584,1855.116943,1856.711426,1858.228516,1859.084473,1854.159180,1855.814941,1852.685791,1856.680176,1856.460205</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>1848.715576,1846.807983,1843.470215,1842.807129,1840.759888,1839.416260,1838.107910,1836.425049,1834.267090,1832.057129,1830.270386,1828.885498,1827.364990,1827.320557,1826.735474,1824.000000,1823.660400,1821.810059,1817.097168,1816.597412,1816.780518,1814.280029,1812.584473,1813.058350</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>1852.990845,1850.797607,1848.899170,1848.331543,1847.160156,1846.196289,1846.355347,1844.474121,1845.184570,1841.956055,1839.772705,1839.303223,1839.979492,1837.823730,1839.543213,1838.184326,1837.207031,1834.251465,1833.712280,1833.579468,1832.960693,1829.815674,1830.382324,1830.615356</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,6 +683,44 @@
       </c>
       <c r="F7" t="n">
         <v>1856.755126953125</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1881.239990234375</v>
+      </c>
+      <c r="H7" t="n">
+        <v>24.48486328125</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.301527896937782</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.5559999591962549</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-07-26 03:41:58</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>24</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1890.021362304688</v>
       </c>
     </row>
   </sheetData>
@@ -696,7 +734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1098,6 +1136,24 @@
           <t>1857.638672,1857.595947,1857.676270,1858.183594,1857.608643,1858.190430,1858.267700,1858.046021,1858.175781,1858.000488,1857.212646,1857.385986,1857.358154,1857.264404,1857.673340,1856.898682,1857.429443,1856.821045,1857.013672,1856.931274,1857.208740,1856.152588,1855.703003,1856.755127</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1859.619995,1856.640015,1857.180054,1854.489990,1852.079956,1856.540039,1856.770020,1856.060059,1858.369995,1865.260010,1867.050049,1866.099976,1866.329956,1871.359985,1873.709961,1873.060059,1870.500000,1870.989990,1874.310059,1872.239990,1879.400024,1877.040039,1879.140015,1881.239990</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1.981323,0.955932,0.496216,3.693604,5.528687,1.650391,1.497680,1.985962,0.194214,7.259522,9.837403,8.713990,8.971802,14.095581,16.036621,16.161377,13.070557,14.168945,17.296387,15.308716,22.191284,20.887451,23.437012,24.484863</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.106545,0.051487,0.026719,0.199171,0.298512,0.088896,0.080661,0.106999,0.010451,0.389196,0.526896,0.466963,0.480719,0.753227,0.855875,0.862833,0.698773,0.757297,0.922814,0.817668,1.180764,1.112787,1.247220,1.301528</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0.5559999591962549</v>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>1857.093018,1857.490845,1856.793091,1857.337402,1859.642456,1858.813965,1856.568115,1854.664062,1858.069824,1859.367188,1855.819702,1856.816162,1856.145752,1858.896729,1858.298584,1855.116943,1856.711426,1858.228516,1859.084473,1854.159180,1855.814941,1852.685791,1856.680176,1856.460205</t>
@@ -1111,6 +1167,49 @@
       <c r="M7" t="inlineStr">
         <is>
           <t>1852.990845,1850.797607,1848.899170,1848.331543,1847.160156,1846.196289,1846.355347,1844.474121,1845.184570,1841.956055,1839.772705,1839.303223,1839.979492,1837.823730,1839.543213,1838.184326,1837.207031,1834.251465,1833.712280,1833.579468,1832.960693,1829.815674,1830.382324,1830.615356</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-07-26 03:41:58</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>24</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1882.171631,1882.730713,1883.256104,1884.011475,1884.218750,1885.406982,1885.971680,1886.104492,1886.743896,1887.076904,1887.377197,1887.689941,1888.261475,1888.753662,1889.114136,1888.557495,1889.880615,1889.018433,1889.493042,1889.846313,1888.941162,1888.800049,1889.155273,1890.021362</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>1880.841064,1882.462769,1883.969238,1883.322876,1885.819946,1885.640869,1885.100098,1886.360352,1883.845947,1887.343384,1884.912598,1885.753662,1887.844604,1888.848389,1888.569336,1885.451660,1887.355103,1887.449341,1888.337402,1886.327148,1886.355835,1884.544678,1886.935425,1887.178955</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>1875.704346,1874.382080,1871.673828,1871.008789,1869.564331,1868.744629,1868.674561,1866.826904,1865.883423,1863.608521,1863.424927,1861.006836,1860.907227,1860.440063,1859.419189,1856.953857,1857.057861,1855.594971,1851.700562,1850.117676,1849.434082,1847.221436,1846.047852,1845.645996</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>1879.387329,1878.035645,1876.572266,1876.175171,1875.226074,1875.319092,1875.842529,1874.622681,1874.843994,1872.453003,1871.930908,1871.775146,1873.069092,1870.576660,1871.608398,1870.540405,1870.233643,1868.039062,1866.929565,1866.625732,1864.807373,1863.255005,1864.048096,1864.428467</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -721,6 +721,44 @@
       </c>
       <c r="F8" t="n">
         <v>1890.021362304688</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1945.449951171875</v>
+      </c>
+      <c r="H8" t="n">
+        <v>55.42858886718705</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.849139800990444</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.182445014524379</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-07-27 03:51:29</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>24</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1950.993530273438</v>
       </c>
     </row>
   </sheetData>
@@ -734,7 +772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1197,6 +1235,24 @@
           <t>1882.171631,1882.730713,1883.256104,1884.011475,1884.218750,1885.406982,1885.971680,1886.104492,1886.743896,1887.076904,1887.377197,1887.689941,1888.261475,1888.753662,1889.114136,1888.557495,1889.880615,1889.018433,1889.493042,1889.846313,1888.941162,1888.800049,1889.155273,1890.021362</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>1884.680054,1881.739990,1883.380005,1879.849976,1879.829956,1882.089966,1884.319946,1884.229980,1884.780029,1885.010010,1896.939941,1913.290039,1914.520020,1909.550049,1912.739990,1912.479980,1912.020020,1924.180054,1947.910034,1952.890015,1940.680054,1946.300049,1941.250000,1945.449951</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2.508423,0.990723,0.123901,4.161499,4.388794,3.317016,1.651734,1.874512,1.963867,2.066894,9.562744,25.600098,26.258545,20.796387,23.625854,23.922485,22.139405,35.161621,58.416992,63.043702,51.738892,57.500000,52.094727,55.428589</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0.133095,0.052649,0.006579,0.221374,0.233468,0.176241,0.087657,0.099484,0.104196,0.109649,0.504114,1.338014,1.371547,1.089073,1.235184,1.250862,1.157907,1.827356,2.998957,3.228226,2.666019,2.954324,2.683566,2.849140</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>1.182445014524379</v>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>1880.841064,1882.462769,1883.969238,1883.322876,1885.819946,1885.640869,1885.100098,1886.360352,1883.845947,1887.343384,1884.912598,1885.753662,1887.844604,1888.848389,1888.569336,1885.451660,1887.355103,1887.449341,1888.337402,1886.327148,1886.355835,1884.544678,1886.935425,1887.178955</t>
@@ -1210,6 +1266,49 @@
       <c r="M8" t="inlineStr">
         <is>
           <t>1879.387329,1878.035645,1876.572266,1876.175171,1875.226074,1875.319092,1875.842529,1874.622681,1874.843994,1872.453003,1871.930908,1871.775146,1873.069092,1870.576660,1871.608398,1870.540405,1870.233643,1868.039062,1866.929565,1866.625732,1864.807373,1863.255005,1864.048096,1864.428467</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-07-27 03:51:29</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>24</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1946.144775,1946.507812,1947.672852,1949.051514,1949.601562,1950.503784,1951.268799,1951.875610,1952.916748,1951.943604,1952.482910,1953.803955,1953.355713,1952.585449,1953.058350,1953.292358,1955.031738,1953.178101,1953.396240,1953.125977,1952.958252,1950.825928,1950.616211,1950.993530</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>1943.447998,1946.337402,1947.940674,1947.352051,1950.056885,1948.677734,1949.110962,1952.442871,1947.547607,1951.981323,1950.788330,1947.260986,1949.683105,1950.661743,1950.346436,1951.234131,1950.610596,1949.216187,1948.757080,1949.511841,1947.597412,1948.679810,1946.785400,1944.185547</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>1934.731201,1932.204102,1930.144287,1930.299072,1927.441650,1926.000366,1924.724976,1923.707764,1923.516724,1919.948730,1919.667725,1917.908325,1917.634766,1915.291016,1911.679199,1911.882080,1912.321045,1910.226562,1904.302490,1901.751221,1901.583496,1898.696411,1897.288086,1896.430664</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>1940.383789,1938.258423,1937.243896,1938.115234,1936.554443,1934.959106,1935.395996,1934.670898,1936.005859,1933.187988,1931.995605,1932.314941,1932.583008,1929.426147,1927.241333,1928.899170,1929.781494,1926.697754,1924.301880,1923.470703,1922.304688,1917.379883,1918.186768,1918.152222</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -759,6 +759,44 @@
       </c>
       <c r="F9" t="n">
         <v>1950.993530273438</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1878.050048828125</v>
+      </c>
+      <c r="H9" t="n">
+        <v>72.94348144531295</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.884000934417514</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.444608620068096</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-07-28 03:22:36</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>24</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1875.59619140625</v>
       </c>
     </row>
   </sheetData>
@@ -772,7 +810,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1296,6 +1334,24 @@
           <t>1946.144775,1946.507812,1947.672852,1949.051514,1949.601562,1950.503784,1951.268799,1951.875610,1952.916748,1951.943604,1952.482910,1953.803955,1953.355713,1952.585449,1953.058350,1953.292358,1955.031738,1953.178101,1953.396240,1953.125977,1952.958252,1950.825928,1950.616211,1950.993530</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>1951.540039,1963.930054,1966.770020,1962.689941,1963.300049,1963.420044,1965.920044,1957.979980,1955.579956,1959.089966,1930.170044,1925.439941,1938.500000,1941.900024,1937.199951,1946.839966,1945.000000,1940.000000,1892.109985,1890.670044,1877.310059,1874.130005,1874.000000,1878.050049</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>5.395264,17.422242,19.097168,13.638427,13.698487,12.916260,14.651245,6.104370,2.663208,7.146362,22.312866,28.364014,14.855713,10.685425,15.858399,6.452392,10.031738,13.178101,61.286255,62.455933,75.648193,76.695923,76.616211,72.943481</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0.276462,0.887111,0.970991,0.694884,0.697728,0.657845,0.745261,0.311769,0.136185,0.364780,1.156005,1.473119,0.766351,0.550256,0.818625,0.331429,0.515771,0.679284,3.239043,3.303376,4.029606,4.092348,4.088378,3.884001</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>1.444608620068096</v>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>1943.447998,1946.337402,1947.940674,1947.352051,1950.056885,1948.677734,1949.110962,1952.442871,1947.547607,1951.981323,1950.788330,1947.260986,1949.683105,1950.661743,1950.346436,1951.234131,1950.610596,1949.216187,1948.757080,1949.511841,1947.597412,1948.679810,1946.785400,1944.185547</t>
@@ -1309,6 +1365,49 @@
       <c r="M9" t="inlineStr">
         <is>
           <t>1940.383789,1938.258423,1937.243896,1938.115234,1936.554443,1934.959106,1935.395996,1934.670898,1936.005859,1933.187988,1931.995605,1932.314941,1932.583008,1929.426147,1927.241333,1928.899170,1929.781494,1926.697754,1924.301880,1923.470703,1922.304688,1917.379883,1918.186768,1918.152222</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-07-28 03:22:36</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>24</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1876.431885,1876.048340,1875.723633,1875.095215,1874.594116,1875.303711,1875.879395,1874.912231,1875.120972,1875.834473,1876.106079,1877.198242,1876.699219,1876.043945,1877.202881,1876.895020,1877.314209,1877.273438,1876.813721,1875.902588,1875.915039,1875.839111,1875.251953,1875.596191</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>1874.553833,1878.689087,1876.003906,1876.832764,1876.910889,1877.216553,1876.551025,1875.926636,1875.390503,1878.960205,1876.786255,1878.867676,1875.770630,1878.706909,1877.519043,1876.235474,1878.246338,1878.496460,1877.302734,1876.918091,1877.265625,1874.732422,1876.657104,1876.077637</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>1861.202148,1857.644043,1853.434326,1850.056396,1847.750854,1846.411743,1844.187988,1841.457153,1841.269897,1839.495605,1838.094727,1837.434082,1836.863647,1834.277832,1832.459229,1831.398804,1830.421387,1828.962036,1823.100342,1820.936768,1819.325195,1819.104492,1818.372314,1817.638428</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>1867.885986,1864.983154,1861.404907,1859.779663,1857.601562,1856.179688,1856.079590,1853.302734,1854.817383,1853.465210,1851.895264,1853.424561,1851.776367,1849.883789,1849.845459,1849.527344,1848.638428,1846.839844,1844.827515,1843.129761,1842.323364,1841.110229,1840.308594,1840.797852</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -797,6 +797,44 @@
       </c>
       <c r="F10" t="n">
         <v>1875.59619140625</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1904.300048828125</v>
+      </c>
+      <c r="H10" t="n">
+        <v>28.703857421875</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.507318000623845</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.141621036615555</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-07-29 03:23:33</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>24</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1902.686157226562</v>
       </c>
     </row>
   </sheetData>
@@ -810,7 +848,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1395,6 +1433,24 @@
           <t>1876.431885,1876.048340,1875.723633,1875.095215,1874.594116,1875.303711,1875.879395,1874.912231,1875.120972,1875.834473,1876.106079,1877.198242,1876.699219,1876.043945,1877.202881,1876.895020,1877.314209,1877.273438,1876.813721,1875.902588,1875.915039,1875.839111,1875.251953,1875.596191</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1877.369995,1881.310059,1886.599976,1881.880005,1882.489990,1874.260010,1876.920044,1874.790039,1890.400024,1872.099976,1886.890015,1918.300049,1924.010010,1899.489990,1908.819946,1919.510010,1916.160034,1921.849976,1909.760010,1904.400024,1915.170044,1903.270020,1908.400024,1904.300049</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0.938110,5.261719,10.876343,6.784790,7.895874,1.043701,1.040649,0.122192,15.279052,3.734497,10.783936,41.101807,47.310791,23.446045,31.617065,42.614990,38.845825,44.576538,32.946289,28.497436,39.255005,27.430909,33.148071,28.703858</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0.049969,0.279684,0.576505,0.360533,0.419438,0.055686,0.055445,0.006518,0.808244,0.199482,0.571519,2.142616,2.458968,1.234334,1.656367,2.220097,2.027275,2.319460,1.725153,1.496400,2.049688,1.441252,1.736956,1.507318</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>1.141621036615555</v>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>1874.553833,1878.689087,1876.003906,1876.832764,1876.910889,1877.216553,1876.551025,1875.926636,1875.390503,1878.960205,1876.786255,1878.867676,1875.770630,1878.706909,1877.519043,1876.235474,1878.246338,1878.496460,1877.302734,1876.918091,1877.265625,1874.732422,1876.657104,1876.077637</t>
@@ -1408,6 +1464,49 @@
       <c r="M10" t="inlineStr">
         <is>
           <t>1867.885986,1864.983154,1861.404907,1859.779663,1857.601562,1856.179688,1856.079590,1853.302734,1854.817383,1853.465210,1851.895264,1853.424561,1851.776367,1849.883789,1849.845459,1849.527344,1848.638428,1846.839844,1844.827515,1843.129761,1842.323364,1841.110229,1840.308594,1840.797852</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-07-29 03:23:33</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>24</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>1904.498291,1903.323364,1903.474854,1903.897339,1903.555176,1903.788208,1904.010498,1903.083008,1903.093994,1903.385498,1903.097900,1903.554932,1904.388428,1903.900391,1904.352051,1904.395020,1904.810303,1904.644287,1904.847656,1904.380615,1904.969727,1903.927368,1902.660034,1902.686157</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>1905.014893,1903.864014,1904.063232,1903.136963,1905.325806,1903.552979,1902.502930,1902.036621,1903.083496,1903.427368,1903.536743,1900.140137,1903.145874,1903.130371,1903.591187,1901.721191,1901.067749,1902.161987,1902.877441,1900.770630,1901.632446,1900.685181,1903.096436,1899.036987</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>1889.689575,1885.367920,1882.348389,1881.381104,1877.701904,1877.967041,1876.209717,1871.203369,1870.498291,1869.033936,1867.606445,1865.582031,1865.728516,1864.561523,1864.045410,1862.869995,1861.945312,1861.829956,1857.229492,1855.691528,1857.543701,1855.543213,1853.392822,1853.234863</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>1896.178467,1892.530029,1890.361816,1890.502197,1888.723511,1887.206055,1887.100342,1884.931152,1884.929688,1883.387695,1881.264160,1882.185547,1882.477539,1879.894287,1880.641846,1879.947754,1879.643799,1877.715332,1877.340088,1876.345703,1877.403320,1874.918213,1873.950195,1872.683716</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -835,6 +835,44 @@
       </c>
       <c r="F11" t="n">
         <v>1902.686157226562</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1908.2900390625</v>
+      </c>
+      <c r="H11" t="n">
+        <v>5.603881835937955</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.2936598588907908</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.4991348396418255</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-07-30 02:57:52</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>24</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1907.62109375</v>
       </c>
     </row>
   </sheetData>
@@ -848,7 +886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1494,6 +1532,24 @@
           <t>1904.498291,1903.323364,1903.474854,1903.897339,1903.555176,1903.788208,1904.010498,1903.083008,1903.093994,1903.385498,1903.097900,1903.554932,1904.388428,1903.900391,1904.352051,1904.395020,1904.810303,1904.644287,1904.847656,1904.380615,1904.969727,1903.927368,1902.660034,1902.686157</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1903.069946,1910.219971,1917.810059,1921.280029,1912.859985,1919.979980,1909.829956,1913.010010,1902.930054,1907.300049,1892.650024,1889.810059,1892.709961,1913.739990,1918.199951,1886.619995,1882.469971,1896.050049,1904.709961,1907.989990,1895.829956,1914.300049,1908.290039,1908.290039</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>1.428345,6.896607,14.335205,17.382690,9.304809,16.191772,5.819458,9.927002,0.163940,3.914551,10.447876,13.744873,11.678467,9.839599,13.847900,17.775025,22.340332,8.594238,0.137695,3.609375,9.139771,10.372681,5.630005,5.603882</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0.075055,0.361037,0.747478,0.904745,0.486434,0.843330,0.304711,0.518921,0.008615,0.205240,0.552024,0.727315,0.617024,0.514155,0.721922,0.942162,1.186756,0.453271,0.007229,0.189172,0.482099,0.541852,0.295029,0.293660</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>0.4991348396418255</v>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>1905.014893,1903.864014,1904.063232,1903.136963,1905.325806,1903.552979,1902.502930,1902.036621,1903.083496,1903.427368,1903.536743,1900.140137,1903.145874,1903.130371,1903.591187,1901.721191,1901.067749,1902.161987,1902.877441,1900.770630,1901.632446,1900.685181,1903.096436,1899.036987</t>
@@ -1507,6 +1563,49 @@
       <c r="M11" t="inlineStr">
         <is>
           <t>1896.178467,1892.530029,1890.361816,1890.502197,1888.723511,1887.206055,1887.100342,1884.931152,1884.929688,1883.387695,1881.264160,1882.185547,1882.477539,1879.894287,1880.641846,1879.947754,1879.643799,1877.715332,1877.340088,1876.345703,1877.403320,1874.918213,1873.950195,1872.683716</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-07-30 02:57:52</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>24</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>1907.331543,1907.427490,1907.489624,1907.946411,1908.081543,1908.633057,1908.636353,1907.400635,1907.296021,1907.656738,1906.492920,1906.988037,1908.175659,1907.235840,1907.634277,1908.018066,1908.803711,1907.861206,1908.145996,1908.318115,1908.557617,1907.425781,1907.687744,1907.621094</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>1906.934814,1907.259033,1908.561035,1907.280518,1910.362061,1909.210205,1909.795654,1906.462646,1906.066284,1905.234863,1906.653320,1905.528076,1906.458008,1906.227905,1906.882080,1903.899536,1905.052734,1906.710693,1907.669189,1903.965820,1905.386841,1904.560303,1907.985107,1904.915283</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>1890.927368,1887.859131,1885.139771,1884.304688,1882.130859,1882.212158,1880.254395,1876.283813,1875.711670,1874.524902,1872.082275,1870.019409,1869.802490,1867.384155,1867.077026,1865.970947,1865.578369,1864.198242,1861.996094,1860.917725,1860.749634,1858.777344,1859.127808,1858.219971</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>1897.466064,1895.083984,1893.052002,1893.558838,1891.754395,1890.798584,1890.590332,1888.450806,1887.821289,1886.882080,1883.706543,1884.623779,1884.646851,1881.226074,1882.448975,1882.425781,1881.872070,1879.982300,1880.440796,1879.300537,1879.680176,1877.755127,1879.438843,1878.086670</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -873,6 +873,44 @@
       </c>
       <c r="F12" t="n">
         <v>1907.62109375</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1902.180053710938</v>
+      </c>
+      <c r="H12" t="n">
+        <v>5.4410400390625</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.2860423243555544</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.4657319150407306</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-07-31 03:39:45</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>24</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1897.194091796875</v>
       </c>
     </row>
   </sheetData>
@@ -886,7 +924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1593,6 +1631,24 @@
           <t>1907.331543,1907.427490,1907.489624,1907.946411,1908.081543,1908.633057,1908.636353,1907.400635,1907.296021,1907.656738,1906.492920,1906.988037,1908.175659,1907.235840,1907.634277,1908.018066,1908.803711,1907.861206,1908.145996,1908.318115,1908.557617,1907.425781,1907.687744,1907.621094</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>1907.540039,1899.319946,1903.800049,1898.599976,1900.459961,1912.599976,1915.489990,1915.910034,1920.550049,1922.890015,1927.890015,1915.680054,1916.699951,1917.339966,1918.670044,1914.260010,1922.079956,1919.560059,1916.890015,1924.119995,1916.819946,1914.939941,1908.400024,1902.180054</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0.208496,8.107544,3.689575,9.346435,7.621582,3.966919,6.853637,8.509399,13.254028,15.233277,21.397095,8.692017,8.524292,10.104126,11.035767,6.241944,13.276245,11.698853,8.744019,15.801880,8.262329,7.514160,0.712280,5.441040</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>0.010930,0.426866,0.193801,0.492280,0.401039,0.207410,0.357801,0.444144,0.690116,0.792207,1.109871,0.453730,0.444738,0.526987,0.575178,0.326076,0.690723,0.609455,0.456157,0.821252,0.431044,0.392397,0.037323,0.286042</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>0.4657319150407306</v>
+      </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>1906.934814,1907.259033,1908.561035,1907.280518,1910.362061,1909.210205,1909.795654,1906.462646,1906.066284,1905.234863,1906.653320,1905.528076,1906.458008,1906.227905,1906.882080,1903.899536,1905.052734,1906.710693,1907.669189,1903.965820,1905.386841,1904.560303,1907.985107,1904.915283</t>
@@ -1606,6 +1662,49 @@
       <c r="M12" t="inlineStr">
         <is>
           <t>1897.466064,1895.083984,1893.052002,1893.558838,1891.754395,1890.798584,1890.590332,1888.450806,1887.821289,1886.882080,1883.706543,1884.623779,1884.646851,1881.226074,1882.448975,1882.425781,1881.872070,1879.982300,1880.440796,1879.300537,1879.680176,1877.755127,1879.438843,1878.086670</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-07-31 03:39:45</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>24</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>1904.330933,1904.071899,1903.358887,1904.143066,1903.567871,1904.056885,1904.629517,1903.184082,1903.170654,1903.171387,1901.893066,1902.675537,1902.119629,1901.570801,1901.311279,1901.217529,1900.757080,1900.230591,1900.294434,1898.453613,1898.630615,1897.661133,1896.916260,1897.194092</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>1903.589111,1904.171875,1902.914062,1904.042480,1905.837891,1904.558594,1904.405884,1901.597046,1903.128418,1902.335938,1902.014404,1901.995605,1902.804199,1900.287598,1899.561523,1898.636108,1897.582764,1899.074951,1898.862793,1895.258301,1895.737427,1894.090332,1894.427490,1894.760010</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>1892.200195,1889.014526,1884.918213,1884.177124,1881.338379,1880.762329,1878.957520,1875.849365,1874.120361,1871.796021,1868.842285,1867.263184,1865.021240,1862.960449,1861.594849,1858.883789,1857.640625,1855.889404,1852.479248,1849.260498,1848.812500,1847.206299,1845.802734,1845.402100</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>1897.089355,1894.649902,1891.874146,1891.754395,1889.633545,1888.336060,1888.320068,1886.072510,1886.183838,1884.000488,1880.255249,1880.568115,1879.446533,1876.759277,1876.175293,1875.313599,1874.655151,1872.371094,1871.384277,1868.430664,1867.973877,1867.319824,1866.217285,1866.375122</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,6 +911,44 @@
       </c>
       <c r="F13" t="n">
         <v>1897.194091796875</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1866.359985351562</v>
+      </c>
+      <c r="H13" t="n">
+        <v>30.8341064453125</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.65209856015555</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.487793013193667</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-08-01 03:39:54</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>24</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1861.636352539062</v>
       </c>
     </row>
   </sheetData>
@@ -924,7 +962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1692,6 +1730,24 @@
           <t>1904.330933,1904.071899,1903.358887,1904.143066,1903.567871,1904.056885,1904.629517,1903.184082,1903.170654,1903.171387,1901.893066,1902.675537,1902.119629,1901.570801,1901.311279,1901.217529,1900.757080,1900.230591,1900.294434,1898.453613,1898.630615,1897.661133,1896.916260,1897.194092</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>1903.920044,1904.400024,1900.800049,1888.239990,1888.619995,1881.930054,1885.180054,1882.599976,1880.560059,1864.329956,1857.300049,1860.560059,1862.979980,1873.270020,1869.780029,1866.520020,1860.400024,1860.000000,1859.630005,1860.640015,1862.859985,1865.160034,1866.569946,1866.359985</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0.410889,0.328125,2.558838,15.903076,14.947876,22.126831,19.449463,20.584106,22.610595,38.841431,44.593017,42.115478,39.139649,28.300781,31.531250,34.697509,40.357056,40.230591,40.664429,37.813598,35.770630,32.501099,30.346314,30.834107</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>0.021581,0.017230,0.134619,0.842217,0.791471,1.175752,1.031703,1.093387,1.202333,2.083399,2.400959,2.263591,2.100916,1.510769,1.686361,1.858941,2.169268,2.162935,2.186695,2.032290,1.920200,1.742537,1.625780,1.652099</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>1.487793013193667</v>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>1903.589111,1904.171875,1902.914062,1904.042480,1905.837891,1904.558594,1904.405884,1901.597046,1903.128418,1902.335938,1902.014404,1901.995605,1902.804199,1900.287598,1899.561523,1898.636108,1897.582764,1899.074951,1898.862793,1895.258301,1895.737427,1894.090332,1894.427490,1894.760010</t>
@@ -1705,6 +1761,49 @@
       <c r="M13" t="inlineStr">
         <is>
           <t>1897.089355,1894.649902,1891.874146,1891.754395,1889.633545,1888.336060,1888.320068,1886.072510,1886.183838,1884.000488,1880.255249,1880.568115,1879.446533,1876.759277,1876.175293,1875.313599,1874.655151,1872.371094,1871.384277,1868.430664,1867.973877,1867.319824,1866.217285,1866.375122</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-08-01 03:39:54</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>24</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>1866.391113,1866.590942,1866.798096,1866.920166,1866.322510,1866.392578,1866.120239,1865.371582,1865.004883,1864.754639,1863.692139,1864.192383,1864.101929,1864.019043,1864.042114,1863.900879,1863.269043,1863.058350,1862.979980,1862.235596,1862.223145,1861.591064,1860.972900,1861.636353</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>1866.115234,1867.767944,1868.384521,1867.424805,1868.649170,1867.491699,1868.051514,1866.403076,1866.213135,1866.418213,1866.277100,1865.943726,1866.887939,1867.253662,1867.209717,1864.364624,1865.299194,1867.009033,1866.208252,1864.852783,1863.413208,1861.855591,1863.613281,1864.748779</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>1860.448730,1858.898926,1856.446289,1855.864990,1853.341309,1852.325562,1850.843506,1848.187256,1846.622314,1844.875000,1843.527832,1842.804443,1841.949463,1840.893921,1840.103638,1837.943359,1836.857178,1835.415039,1832.506714,1830.992798,1830.031250,1828.973145,1827.421875,1827.210693</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>1862.937012,1861.859009,1860.534912,1860.126953,1858.550415,1857.417480,1856.209717,1854.439575,1854.010986,1852.222900,1850.378418,1850.831787,1850.523438,1849.288086,1848.856689,1847.895142,1846.583618,1845.177734,1843.975098,1843.400024,1842.523682,1841.319336,1840.542480,1840.997192</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -949,6 +949,44 @@
       </c>
       <c r="F14" t="n">
         <v>1861.636352539062</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1876.5</v>
+      </c>
+      <c r="H14" t="n">
+        <v>14.86364746093795</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.7920941892319721</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.5063505503548219</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-08-02 03:39:45</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>24</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1874.300537109375</v>
       </c>
     </row>
   </sheetData>
@@ -962,7 +1000,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1791,6 +1829,24 @@
           <t>1866.391113,1866.590942,1866.798096,1866.920166,1866.322510,1866.392578,1866.120239,1865.371582,1865.004883,1864.754639,1863.692139,1864.192383,1864.101929,1864.019043,1864.042114,1863.900879,1863.269043,1863.058350,1862.979980,1862.235596,1862.223145,1861.591064,1860.972900,1861.636353</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>1867.910034,1865.579956,1868.890015,1867.680054,1867.599976,1866.199951,1865.579956,1865.189941,1867.219971,1867.410034,1873.410034,1868.439941,1867.189941,1860.469971,1835.300049,1835.550049,1836.680054,1844.030029,1845.500000,1843.410034,1844.959961,1855.109985,1875.000000,1876.500000</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>1.518921,1.010986,2.091919,0.759888,1.277466,0.192627,0.540283,0.181641,2.215088,2.655395,9.717895,4.247558,3.088012,3.549072,28.742065,28.350830,26.588989,19.028321,17.479980,18.825562,17.263184,6.481079,14.027100,14.863647</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>0.081317,0.054192,0.111934,0.040686,0.068401,0.010322,0.028961,0.009738,0.118630,0.142197,0.518728,0.227332,0.165383,0.190762,1.566069,1.544541,1.447666,1.031888,0.947168,1.021236,0.935694,0.349364,0.748112,0.792094</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>0.5063505503548219</v>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>1866.115234,1867.767944,1868.384521,1867.424805,1868.649170,1867.491699,1868.051514,1866.403076,1866.213135,1866.418213,1866.277100,1865.943726,1866.887939,1867.253662,1867.209717,1864.364624,1865.299194,1867.009033,1866.208252,1864.852783,1863.413208,1861.855591,1863.613281,1864.748779</t>
@@ -1804,6 +1860,49 @@
       <c r="M14" t="inlineStr">
         <is>
           <t>1862.937012,1861.859009,1860.534912,1860.126953,1858.550415,1857.417480,1856.209717,1854.439575,1854.010986,1852.222900,1850.378418,1850.831787,1850.523438,1849.288086,1848.856689,1847.895142,1846.583618,1845.177734,1843.975098,1843.400024,1842.523682,1841.319336,1840.542480,1840.997192</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-08-02 03:39:45</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>24</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>1873.166504,1873.884766,1874.092896,1874.104492,1873.880859,1873.648438,1873.547607,1873.955078,1873.297852,1873.579102,1872.447266,1872.802490,1872.939209,1872.404541,1872.310791,1872.231689,1871.850098,1871.186401,1872.334229,1872.443848,1872.883667,1872.589600,1873.424561,1874.300537</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>1871.035156,1873.307129,1875.193848,1873.142334,1875.305908,1873.983521,1873.309326,1874.524414,1872.389893,1874.702881,1873.389771,1873.032471,1873.416748,1873.773438,1873.154297,1873.042725,1870.205566,1873.238525,1873.067749,1871.793457,1872.368774,1872.626099,1874.363525,1874.642090</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>1860.844238,1858.085938,1854.948975,1853.419922,1851.168213,1848.975098,1847.264648,1846.318359,1843.442261,1841.694580,1839.763306,1840.739380,1839.148682,1837.460083,1836.663940,1835.388428,1833.168335,1832.249512,1831.017090,1830.787842,1830.736816,1830.274536,1829.553955,1829.403931</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>1865.980469,1864.127441,1862.144775,1861.117798,1859.129272,1857.676025,1856.505005,1855.482666,1854.327148,1852.768799,1850.751221,1851.260132,1850.990845,1849.264648,1849.225830,1848.821777,1846.428467,1845.385742,1845.721558,1846.555664,1846.170166,1844.830811,1846.108887,1845.897949</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -987,6 +987,44 @@
       </c>
       <c r="F15" t="n">
         <v>1874.300537109375</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1859.359985351562</v>
+      </c>
+      <c r="H15" t="n">
+        <v>14.9405517578125</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.8035319612940677</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.517205125203742</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-08-03 03:41:54</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>24</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1878.908447265625</v>
       </c>
     </row>
   </sheetData>
@@ -1000,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1890,6 +1928,24 @@
           <t>1873.166504,1873.884766,1874.092896,1874.104492,1873.880859,1873.648438,1873.547607,1873.955078,1873.297852,1873.579102,1872.447266,1872.802490,1872.939209,1872.404541,1872.310791,1872.231689,1871.850098,1871.186401,1872.334229,1872.443848,1872.883667,1872.589600,1873.424561,1874.300537</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>1879.209961,1874.589966,1875.640015,1874.050049,1866.209961,1869.119995,1866.849976,1850.800049,1855.359985,1853.000000,1853.020020,1857.119995,1861.310059,1866.800049,1873.839966,1880.060059,1881.680054,1888.380005,1879.930054,1883.349976,1871.619995,1864.920044,1862.000000,1859.359985</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>6.043457,0.705200,1.547119,0.054443,7.670898,4.528443,6.697631,23.155029,17.937867,20.579102,19.427246,15.682495,11.629150,5.604492,1.529175,7.828370,9.829956,17.193604,7.595825,10.906128,1.263672,7.669556,11.424561,14.940552</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>0.321596,0.037619,0.082485,0.002905,0.411042,0.242277,0.358766,1.251082,0.966813,1.110583,1.048410,0.844452,0.624783,0.300219,0.081606,0.416389,0.522403,0.910495,0.404048,0.579081,0.067518,0.411254,0.613564,0.803532</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>0.517205125203742</v>
+      </c>
       <c r="K15" t="inlineStr">
         <is>
           <t>1871.035156,1873.307129,1875.193848,1873.142334,1875.305908,1873.983521,1873.309326,1874.524414,1872.389893,1874.702881,1873.389771,1873.032471,1873.416748,1873.773438,1873.154297,1873.042725,1870.205566,1873.238525,1873.067749,1871.793457,1872.368774,1872.626099,1874.363525,1874.642090</t>
@@ -1903,6 +1959,49 @@
       <c r="M15" t="inlineStr">
         <is>
           <t>1865.980469,1864.127441,1862.144775,1861.117798,1859.129272,1857.676025,1856.505005,1855.482666,1854.327148,1852.768799,1850.751221,1851.260132,1850.990845,1849.264648,1849.225830,1848.821777,1846.428467,1845.385742,1845.721558,1846.555664,1846.170166,1844.830811,1846.108887,1845.897949</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-08-03 03:41:54</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>24</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>1859.405273,1859.487427,1860.053711,1860.863037,1861.612549,1862.310913,1863.435791,1863.902100,1864.213379,1865.931030,1866.721558,1868.059692,1869.628174,1870.814575,1871.645264,1873.475586,1873.849365,1874.646240,1876.044434,1876.747559,1877.217163,1877.508789,1878.009521,1878.908447</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>1860.189819,1860.007812,1861.482178,1860.826904,1864.723999,1864.206787,1865.447266,1865.034668,1865.867676,1866.778442,1868.039062,1869.873535,1872.225220,1873.216797,1873.955811,1874.999756,1875.793213,1878.726318,1877.289917,1878.049316,1877.696289,1877.614014,1880.100586,1879.711182</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>1849.052734,1846.538940,1843.916748,1842.698486,1840.776245,1839.493774,1838.669312,1836.193237,1834.081055,1833.988525,1834.121338,1833.640015,1833.814941,1833.437622,1833.791748,1833.827637,1833.565186,1833.417603,1832.318481,1832.585449,1832.083740,1832.226685,1832.194580,1831.638184</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>1853.115723,1851.138428,1849.430176,1849.431152,1847.988525,1847.805908,1847.462646,1846.546387,1845.330322,1845.474121,1845.010742,1846.412354,1846.940796,1846.724121,1847.621704,1848.290894,1847.422363,1847.618652,1848.332031,1848.926270,1848.202026,1848.458130,1848.841553,1849.351318</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1025,6 +1025,44 @@
       </c>
       <c r="F16" t="n">
         <v>1878.908447265625</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1858.0400390625</v>
+      </c>
+      <c r="H16" t="n">
+        <v>20.868408203125</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.12314093154066</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.7078397515276028</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-08-04 03:26:01</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>24</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1868.696533203125</v>
       </c>
     </row>
   </sheetData>
@@ -1038,7 +1076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1989,6 +2027,24 @@
           <t>1859.405273,1859.487427,1860.053711,1860.863037,1861.612549,1862.310913,1863.435791,1863.902100,1864.213379,1865.931030,1866.721558,1868.059692,1869.628174,1870.814575,1871.645264,1873.475586,1873.849365,1874.646240,1876.044434,1876.747559,1877.217163,1877.508789,1878.009521,1878.908447</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>1852.569946,1857.530029,1846.729980,1841.430054,1837.849976,1850.109985,1843.680054,1837.400024,1841.229980,1856.900024,1871.699951,1861.099976,1864.319946,1867.130005,1867.000000,1868.569946,1867.520020,1862.089966,1858.630005,1858.890015,1849.300049,1865.829956,1864.339966,1858.040039</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>6.835327,1.957398,13.323731,19.432983,23.762573,12.200928,19.755737,26.502076,22.983399,9.031006,4.978393,6.959716,5.308228,3.684570,4.645264,4.905640,6.329345,12.556274,17.414429,17.857544,27.917114,11.678833,13.669555,20.868408</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>0.368965,0.105376,0.721477,1.055320,1.292955,0.659470,1.071538,1.442368,1.248263,0.486349,0.265982,0.373957,0.284727,0.197339,0.248809,0.262534,0.338917,0.674311,0.936950,0.960656,1.509604,0.625932,0.733212,1.123141</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>0.7078397515276028</v>
+      </c>
       <c r="K16" t="inlineStr">
         <is>
           <t>1860.189819,1860.007812,1861.482178,1860.826904,1864.723999,1864.206787,1865.447266,1865.034668,1865.867676,1866.778442,1868.039062,1869.873535,1872.225220,1873.216797,1873.955811,1874.999756,1875.793213,1878.726318,1877.289917,1878.049316,1877.696289,1877.614014,1880.100586,1879.711182</t>
@@ -2002,6 +2058,49 @@
       <c r="M16" t="inlineStr">
         <is>
           <t>1853.115723,1851.138428,1849.430176,1849.431152,1847.988525,1847.805908,1847.462646,1846.546387,1845.330322,1845.474121,1845.010742,1846.412354,1846.940796,1846.724121,1847.621704,1848.290894,1847.422363,1847.618652,1848.332031,1848.926270,1848.202026,1848.458130,1848.841553,1849.351318</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-08-04 03:26:01</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>24</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>1857.544067,1857.429565,1857.601196,1858.378540,1858.909424,1859.387207,1860.744141,1861.037842,1861.781372,1862.369019,1863.263306,1864.407471,1865.340820,1866.879028,1867.560059,1868.130127,1868.658936,1868.530640,1869.035889,1868.791016,1868.684326,1868.977295,1868.027832,1868.696533</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>1857.681152,1859.626465,1856.370361,1858.778564,1860.412598,1861.027588,1861.995850,1861.979492,1864.135376,1864.057861,1864.711426,1865.505371,1868.442627,1869.231689,1870.757324,1870.112427,1870.756348,1873.251587,1872.792358,1871.575684,1870.567139,1870.586670,1870.576538,1870.621826</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>1843.601807,1841.248047,1838.941406,1838.512329,1836.280029,1835.515381,1835.547607,1834.038818,1833.338257,1831.972900,1832.358521,1832.080566,1831.275635,1831.830078,1832.143555,1830.630127,1830.875977,1829.518555,1827.604248,1826.629639,1826.507324,1825.951904,1825.241211,1826.033325</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>1849.402100,1847.002808,1845.567139,1845.413330,1844.565674,1843.512451,1844.410645,1843.830811,1844.810669,1843.090942,1842.420898,1843.166260,1843.184814,1843.807129,1844.646484,1843.642578,1843.987915,1842.016724,1842.176514,1841.926270,1841.279053,1840.893066,1841.098755,1841.324219</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1063,6 +1063,44 @@
       </c>
       <c r="F17" t="n">
         <v>1868.696533203125</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1864.910034179688</v>
+      </c>
+      <c r="H17" t="n">
+        <v>3.7864990234375</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.2030392326728541</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.2786410249802107</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:20:55</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>24</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1863.19189453125</v>
       </c>
     </row>
   </sheetData>
@@ -1076,7 +1114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2088,6 +2126,24 @@
           <t>1857.544067,1857.429565,1857.601196,1858.378540,1858.909424,1859.387207,1860.744141,1861.037842,1861.781372,1862.369019,1863.263306,1864.407471,1865.340820,1866.879028,1867.560059,1868.130127,1868.658936,1868.530640,1869.035889,1868.791016,1868.684326,1868.977295,1868.027832,1868.696533</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>1866.280029,1862.660034,1855.229980,1862.079956,1855.760010,1856.680054,1864.910034,1870.829956,1873.510010,1859.229980,1871.119995,1871.410034,1868.219971,1868.060059,1873.900024,1873.680054,1875.319946,1870.880005,1875.199951,1862.469971,1862.469971,1871.949951,1872.979980,1864.910034</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>8.735962,5.230469,2.371216,3.701416,3.149414,2.707153,4.165893,9.792114,11.728638,3.139039,7.856689,7.002563,2.879151,1.181031,6.339965,5.549927,6.661010,2.349365,6.164062,6.321045,6.214355,2.972656,4.952148,3.786499</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>0.468095,0.280806,0.127812,0.198779,0.169710,0.145806,0.223383,0.523410,0.626025,0.168835,0.419892,0.374186,0.154112,0.063222,0.338330,0.296205,0.355193,0.125575,0.328715,0.339390,0.333662,0.158800,0.264399,0.203039</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>0.2786410249802107</v>
+      </c>
       <c r="K17" t="inlineStr">
         <is>
           <t>1857.681152,1859.626465,1856.370361,1858.778564,1860.412598,1861.027588,1861.995850,1861.979492,1864.135376,1864.057861,1864.711426,1865.505371,1868.442627,1869.231689,1870.757324,1870.112427,1870.756348,1873.251587,1872.792358,1871.575684,1870.567139,1870.586670,1870.576538,1870.621826</t>
@@ -2101,6 +2157,49 @@
       <c r="M17" t="inlineStr">
         <is>
           <t>1849.402100,1847.002808,1845.567139,1845.413330,1844.565674,1843.512451,1844.410645,1843.830811,1844.810669,1843.090942,1842.420898,1843.166260,1843.184814,1843.807129,1844.646484,1843.642578,1843.987915,1842.016724,1842.176514,1841.926270,1841.279053,1840.893066,1841.098755,1841.324219</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-08-05 03:20:55</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>24</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>1865.423340,1865.624023,1865.449707,1865.419189,1865.708252,1865.531128,1865.835693,1865.139038,1865.348511,1865.303589,1865.816162,1865.539551,1865.547363,1865.839355,1865.831299,1865.210083,1865.498779,1865.186035,1865.086182,1864.205444,1863.549561,1863.773682,1862.966309,1863.191895</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>1865.014526,1866.834595,1865.168945,1865.726318,1865.599609,1865.954468,1865.733887,1865.002441,1865.033325,1866.846436,1866.397949,1865.858154,1865.304443,1866.049805,1867.066895,1866.678711,1866.857178,1865.673828,1865.478516,1866.599854,1864.102295,1864.588989,1864.547729,1863.085205</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>1854.896240,1853.133789,1851.563721,1850.910400,1849.559814,1848.769287,1848.041260,1846.030151,1845.366943,1843.989502,1844.265991,1842.331787,1840.895996,1840.589111,1840.114746,1837.671875,1837.890625,1836.638672,1834.021606,1832.021484,1831.860107,1831.023193,1830.589844,1830.263428</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>1859.109131,1857.769531,1856.327026,1856.032715,1855.365112,1854.311279,1854.391602,1853.179810,1853.378296,1851.951416,1851.322266,1850.599609,1849.912354,1849.442627,1849.682373,1847.823242,1848.276367,1846.557251,1845.571777,1844.547241,1843.478027,1843.288574,1842.959229,1842.666870</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1101,6 +1101,44 @@
       </c>
       <c r="F18" t="n">
         <v>1863.19189453125</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1895.56005859375</v>
+      </c>
+      <c r="H18" t="n">
+        <v>32.3681640625</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.707577869440487</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.244239831778245</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:23:42</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>24</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1894.350708007812</v>
       </c>
     </row>
   </sheetData>
@@ -1114,7 +1152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2187,6 +2225,24 @@
           <t>1865.423340,1865.624023,1865.449707,1865.419189,1865.708252,1865.531128,1865.835693,1865.139038,1865.348511,1865.303589,1865.816162,1865.539551,1865.547363,1865.839355,1865.831299,1865.210083,1865.498779,1865.186035,1865.086182,1864.205444,1863.549561,1863.773682,1862.966309,1863.191895</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>1865.819946,1871.880005,1868.250000,1870.609985,1868.089966,1870.329956,1866.719971,1867.109985,1874.569946,1878.030029,1874.510010,1872.410034,1893.949951,1914.500000,1916.760010,1915.619995,1915.560059,1906.920044,1905.270020,1907.290039,1908.550049,1904.939941,1897.410034,1895.560059</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>0.396606,6.255982,2.800293,5.190796,2.381714,4.798828,0.884278,1.970947,9.221435,12.726440,8.693848,6.870483,28.402588,48.660645,50.928711,50.409912,50.061280,41.734009,40.183838,43.084595,45.000488,41.166259,34.443725,32.368164</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0.021256,0.334208,0.149889,0.277492,0.127495,0.256577,0.047371,0.105561,0.491923,0.677648,0.463793,0.366933,1.499648,2.541689,2.657021,2.631519,2.613402,2.188556,2.109089,2.258943,2.357836,2.161027,1.815302,1.707578</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>1.244239831778245</v>
+      </c>
       <c r="K18" t="inlineStr">
         <is>
           <t>1865.014526,1866.834595,1865.168945,1865.726318,1865.599609,1865.954468,1865.733887,1865.002441,1865.033325,1866.846436,1866.397949,1865.858154,1865.304443,1866.049805,1867.066895,1866.678711,1866.857178,1865.673828,1865.478516,1866.599854,1864.102295,1864.588989,1864.547729,1863.085205</t>
@@ -2200,6 +2256,49 @@
       <c r="M18" t="inlineStr">
         <is>
           <t>1859.109131,1857.769531,1856.327026,1856.032715,1855.365112,1854.311279,1854.391602,1853.179810,1853.378296,1851.951416,1851.322266,1850.599609,1849.912354,1849.442627,1849.682373,1847.823242,1848.276367,1846.557251,1845.571777,1844.547241,1843.478027,1843.288574,1842.959229,1842.666870</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-08-06 03:23:42</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>24</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>1896.478760,1896.140991,1896.297363,1896.007568,1895.828125,1895.567383,1895.269165,1894.629639,1895.534668,1895.354492,1895.711304,1895.735962,1895.914795,1895.832642,1896.047119,1895.643433,1896.466553,1895.479248,1895.606689,1895.070312,1894.437622,1894.397949,1894.406738,1894.350708</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>1895.608276,1896.484131,1895.649536,1896.532959,1895.899292,1896.225220,1894.557129,1895.075562,1894.121582,1896.155518,1895.331299,1895.342773,1894.429443,1894.564087,1895.467041,1895.566528,1894.960938,1894.365967,1894.419922,1894.842529,1893.885498,1894.254761,1894.311768,1893.497925</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>1883.750000,1880.322510,1877.912109,1875.958740,1874.028076,1872.570557,1870.557251,1867.728027,1867.977783,1866.263672,1866.243164,1864.698730,1864.384521,1863.069336,1861.752686,1860.094116,1861.073486,1859.648926,1857.508667,1855.206787,1855.540527,1854.778320,1854.730347,1854.803467</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>1889.086670,1886.276245,1884.166138,1883.198975,1881.534058,1880.110718,1878.837158,1877.294067,1877.854858,1876.457886,1875.808228,1875.666504,1875.185791,1873.978271,1873.464111,1872.338867,1873.791626,1871.886963,1871.299561,1870.272705,1869.443848,1868.961792,1869.296631,1868.988281</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1139,6 +1139,44 @@
       </c>
       <c r="F19" t="n">
         <v>1894.350708007812</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1901.510009765625</v>
+      </c>
+      <c r="H19" t="n">
+        <v>7.159301757812955</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.3765061304460549</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.5651377234270384</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-08-07 03:10:53</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>24</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1903.4130859375</v>
       </c>
     </row>
   </sheetData>
@@ -1152,7 +1190,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2286,6 +2324,24 @@
           <t>1896.478760,1896.140991,1896.297363,1896.007568,1895.828125,1895.567383,1895.269165,1894.629639,1895.534668,1895.354492,1895.711304,1895.735962,1895.914795,1895.832642,1896.047119,1895.643433,1896.466553,1895.479248,1895.606689,1895.070312,1894.437622,1894.397949,1894.406738,1894.350708</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>1906.089966,1912.469971,1911.670044,1907.119995,1914.199951,1905.660034,1900.739990,1905.839966,1896.750000,1905.839966,1913.239990,1909.109985,1914.010010,1912.439941,1904.430054,1908.569946,1905.660034,1904.579956,1903.719971,1902.420044,1902.189941,1901.780029,1900.979980,1901.510010</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>9.611206,16.328980,15.372681,11.112427,18.371826,10.092651,5.470825,11.210327,1.215332,10.485474,17.528686,13.374023,18.095215,16.607299,8.382935,12.926513,9.193481,9.100708,8.113282,7.349732,7.752319,7.382080,6.573242,7.159302</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0.504237,0.853816,0.804149,0.582681,0.959765,0.529614,0.287826,0.588209,0.064074,0.550176,0.916178,0.700537,0.945409,0.868383,0.440181,0.677288,0.482430,0.477833,0.426180,0.386336,0.407547,0.388167,0.345782,0.376506</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>0.5651377234270384</v>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
           <t>1895.608276,1896.484131,1895.649536,1896.532959,1895.899292,1896.225220,1894.557129,1895.075562,1894.121582,1896.155518,1895.331299,1895.342773,1894.429443,1894.564087,1895.467041,1895.566528,1894.960938,1894.365967,1894.419922,1894.842529,1893.885498,1894.254761,1894.311768,1893.497925</t>
@@ -2299,6 +2355,49 @@
       <c r="M19" t="inlineStr">
         <is>
           <t>1889.086670,1886.276245,1884.166138,1883.198975,1881.534058,1880.110718,1878.837158,1877.294067,1877.854858,1876.457886,1875.808228,1875.666504,1875.185791,1873.978271,1873.464111,1872.338867,1873.791626,1871.886963,1871.299561,1870.272705,1869.443848,1868.961792,1869.296631,1868.988281</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-08-07 03:10:53</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>24</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1901.604736,1901.386230,1901.427734,1901.344238,1901.603516,1901.394897,1901.782227,1901.661865,1901.886963,1901.845947,1902.386230,1902.476074,1902.969971,1903.105225,1903.504883,1903.317383,1904.065186,1904.103027,1903.833984,1904.110352,1903.585449,1903.759277,1903.557129,1903.413086</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>1901.011719,1902.416260,1900.979492,1900.880981,1901.909790,1900.642090,1902.497192,1900.856445,1900.574951,1901.742432,1900.889893,1901.340698,1902.224365,1902.888916,1903.190674,1902.290527,1903.537598,1902.339111,1902.849609,1903.593262,1902.235962,1902.375000,1902.230957,1902.667480</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>1895.050781,1892.585815,1890.094238,1888.106445,1886.408569,1884.577393,1883.788330,1881.463135,1881.331055,1879.496460,1879.487305,1878.031982,1878.303711,1876.564087,1876.025879,1874.375732,1874.196777,1873.931763,1870.546387,1869.796997,1869.343384,1868.826172,1868.176758,1867.126709</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>1898.080078,1896.335571,1894.540771,1893.527100,1892.514160,1890.909546,1890.897461,1889.982666,1889.674072,1888.261230,1888.155396,1888.288940,1887.809814,1886.523438,1886.526489,1886.050537,1886.276855,1885.260986,1884.193359,1884.230713,1883.167236,1882.919189,1882.850342,1882.032837</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1177,6 +1177,44 @@
       </c>
       <c r="F20" t="n">
         <v>1903.4130859375</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1913.4599609375</v>
+      </c>
+      <c r="H20" t="n">
+        <v>10.046875</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.5250632469506983</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.5236741476775159</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-08-08 02:07:53</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>24</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1908.713256835938</v>
       </c>
     </row>
   </sheetData>
@@ -1190,7 +1228,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2385,6 +2423,24 @@
           <t>1901.604736,1901.386230,1901.427734,1901.344238,1901.603516,1901.394897,1901.782227,1901.661865,1901.886963,1901.845947,1902.386230,1902.476074,1902.969971,1903.105225,1903.504883,1903.317383,1904.065186,1904.103027,1903.833984,1904.110352,1903.585449,1903.759277,1903.557129,1903.413086</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1895.650024,1899.810059,1903.040039,1900.930054,1909.359985,1911.800049,1911.430054,1914.890015,1930.989990,1921.380005,1912.109985,1916.589966,1908.010010,1911.010010,1908.229980,1918.099976,1913.859985,1917.030029,1917.030029,1913.569946,1913.569946,1913.719971,1913.459961,1913.459961</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>5.954712,1.576171,1.612305,0.414184,7.756469,10.405152,9.647827,13.228150,29.103027,19.534058,9.723755,14.113892,5.040039,7.904785,4.725097,14.782593,9.794799,12.927002,13.196045,9.459594,9.984497,9.960694,9.902832,10.046875</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>0.314125,0.082965,0.084723,0.021789,0.406234,0.544259,0.504744,0.690805,1.507156,1.016668,0.508535,0.736406,0.264152,0.413644,0.247617,0.770689,0.511782,0.674324,0.688359,0.494343,0.521773,0.520489,0.517535,0.525063</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>0.5236741476775159</v>
+      </c>
       <c r="K20" t="inlineStr">
         <is>
           <t>1901.011719,1902.416260,1900.979492,1900.880981,1901.909790,1900.642090,1902.497192,1900.856445,1900.574951,1901.742432,1900.889893,1901.340698,1902.224365,1902.888916,1903.190674,1902.290527,1903.537598,1902.339111,1902.849609,1903.593262,1902.235962,1902.375000,1902.230957,1902.667480</t>
@@ -2398,6 +2454,49 @@
       <c r="M20" t="inlineStr">
         <is>
           <t>1898.080078,1896.335571,1894.540771,1893.527100,1892.514160,1890.909546,1890.897461,1889.982666,1889.674072,1888.261230,1888.155396,1888.288940,1887.809814,1886.523438,1886.526489,1886.050537,1886.276855,1885.260986,1884.193359,1884.230713,1883.167236,1882.919189,1882.850342,1882.032837</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-08-08 02:07:53</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>24</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>1913.142090,1912.804810,1912.892578,1912.581421,1912.723633,1912.390869,1912.794678,1912.488037,1912.941162,1912.416504,1913.267090,1912.908447,1912.411743,1912.031860,1911.760010,1911.033691,1911.255371,1911.179321,1910.099854,1910.456299,1909.359863,1909.267578,1909.384033,1908.713257</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>1912.715088,1912.599365,1912.976562,1912.238525,1911.769531,1911.657471,1911.848145,1912.239502,1911.528198,1912.429321,1911.779907,1910.494629,1911.389160,1911.521118,1910.682983,1910.896606,1909.945312,1908.651367,1908.663330,1910.103271,1908.656738,1908.624390,1907.159058,1908.386475</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>1905.233154,1902.678833,1900.262695,1898.236938,1896.519775,1894.326416,1893.130127,1891.203613,1890.956299,1888.939697,1888.644043,1887.349854,1886.693604,1884.551270,1883.065308,1881.230469,1880.528564,1880.337891,1876.342285,1876.002075,1875.148926,1874.881958,1874.666504,1873.260254</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>1908.590576,1906.828857,1905.086426,1904.016479,1902.982666,1901.202515,1900.830444,1899.824463,1899.839233,1898.011108,1897.952148,1897.619385,1896.276978,1894.574585,1893.823242,1893.038574,1892.859619,1892.092773,1890.214600,1890.304932,1888.969116,1888.351196,1888.799194,1887.448608</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1215,6 +1215,44 @@
       </c>
       <c r="F21" t="n">
         <v>1908.713256835938</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1914.550048828125</v>
+      </c>
+      <c r="H21" t="n">
+        <v>5.836791992187045</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.3048649470281375</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.3321178951710577</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-08-09 02:18:56</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>24</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1913.218505859375</v>
       </c>
     </row>
   </sheetData>
@@ -1228,7 +1266,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2484,6 +2522,24 @@
           <t>1913.142090,1912.804810,1912.892578,1912.581421,1912.723633,1912.390869,1912.794678,1912.488037,1912.941162,1912.416504,1913.267090,1912.908447,1912.411743,1912.031860,1911.760010,1911.033691,1911.255371,1911.179321,1910.099854,1910.456299,1909.359863,1909.267578,1909.384033,1908.713257</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>1917.109985,1916.209961,1916.569946,1915.550049,1914.270020,1915.880005,1917.719971,1919.989990,1919.609985,1918.099976,1918.949951,1922.599976,1921.239990,1921.420044,1922.479980,1920.109985,1919.160034,1918.839966,1919.239990,1915.439941,1916.959961,1916.510010,1914.739990,1914.550049</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>3.967895,3.405151,3.677368,2.968628,1.546387,3.489136,4.925293,7.501953,6.668823,5.683472,5.682861,9.691529,8.828247,9.388184,10.719970,9.076294,7.904663,7.660645,9.140136,4.983642,7.600098,7.242432,5.355957,5.836792</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>0.206973,0.177702,0.191872,0.154975,0.080782,0.182117,0.256831,0.390729,0.347405,0.296307,0.296144,0.504085,0.459508,0.488607,0.557612,0.472697,0.411881,0.399233,0.476237,0.260183,0.396466,0.377897,0.279722,0.304865</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>0.3321178951710577</v>
+      </c>
       <c r="K21" t="inlineStr">
         <is>
           <t>1912.715088,1912.599365,1912.976562,1912.238525,1911.769531,1911.657471,1911.848145,1912.239502,1911.528198,1912.429321,1911.779907,1910.494629,1911.389160,1911.521118,1910.682983,1910.896606,1909.945312,1908.651367,1908.663330,1910.103271,1908.656738,1908.624390,1907.159058,1908.386475</t>
@@ -2497,6 +2553,49 @@
       <c r="M21" t="inlineStr">
         <is>
           <t>1908.590576,1906.828857,1905.086426,1904.016479,1902.982666,1901.202515,1900.830444,1899.824463,1899.839233,1898.011108,1897.952148,1897.619385,1896.276978,1894.574585,1893.823242,1893.038574,1892.859619,1892.092773,1890.214600,1890.304932,1888.969116,1888.351196,1888.799194,1887.448608</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-08-09 02:18:56</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>24</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>1914.870117,1914.197021,1914.607910,1914.531372,1914.298340,1914.454834,1914.432617,1914.204590,1914.484863,1914.573730,1914.494873,1914.635254,1914.704590,1914.474609,1914.624756,1914.401367,1914.772461,1914.788330,1914.190186,1914.145508,1913.631104,1913.178223,1913.596191,1913.218506</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>1914.380859,1913.928467,1914.653076,1914.486450,1914.212891,1913.936523,1914.355957,1914.033203,1913.500488,1914.006592,1913.274902,1912.527466,1913.246948,1913.974121,1913.228271,1912.843018,1912.684326,1912.294067,1911.680786,1912.712891,1911.681396,1910.772461,1910.957153,1911.453979</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>1911.014771,1909.307617,1908.177734,1907.118164,1905.454590,1904.002319,1903.043701,1901.393799,1900.795410,1899.861694,1898.728027,1897.778076,1897.411377,1896.289795,1894.488525,1893.462402,1892.843384,1893.021240,1889.391235,1888.594482,1888.021973,1887.173950,1886.725342,1885.584229</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>1913.016724,1911.608643,1910.960571,1910.715820,1909.224731,1908.511108,1907.762573,1907.460938,1906.951172,1906.245728,1905.235474,1905.056641,1904.828491,1903.439575,1902.949707,1902.355713,1902.731201,1902.485107,1901.049072,1900.702637,1900.118042,1899.053223,1899.292969,1898.520142</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1253,6 +1253,44 @@
       </c>
       <c r="F22" t="n">
         <v>1913.218505859375</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1914.369995117188</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.1514892578125</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.060149775683358</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.2534490237917821</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-08-10 02:24:15</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>24</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1913.435791015625</v>
       </c>
     </row>
   </sheetData>
@@ -1266,7 +1304,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2583,6 +2621,24 @@
           <t>1914.870117,1914.197021,1914.607910,1914.531372,1914.298340,1914.454834,1914.432617,1914.204590,1914.484863,1914.573730,1914.494873,1914.635254,1914.704590,1914.474609,1914.624756,1914.401367,1914.772461,1914.788330,1914.190186,1914.145508,1913.631104,1913.178223,1913.596191,1913.218506</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>1912.699951,1911.839966,1913.150024,1917.709961,1917.500000,1914.479980,1919.829956,1918.719971,1917.930054,1916.270020,1921.989990,1923.489990,1924.640015,1922.719971,1921.670044,1920.099976,1920.579956,1919.780029,1923.219971,1918.280029,1909.089966,1911.069946,1923.920044,1914.369995</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2.170166,2.357055,1.457886,3.178589,3.201660,0.025146,5.397339,4.515381,3.445191,1.696290,7.495117,8.854736,9.935425,8.245362,7.045288,5.698609,5.807495,4.991699,9.029785,4.134521,4.541138,2.108277,10.323853,1.151489</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>0.113461,0.123287,0.076203,0.165749,0.166971,0.001313,0.281136,0.235333,0.179631,0.088520,0.389967,0.460347,0.516222,0.428838,0.366623,0.296787,0.302382,0.260014,0.469514,0.215533,0.237869,0.110319,0.536605,0.060150</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>0.2534490237917821</v>
+      </c>
       <c r="K22" t="inlineStr">
         <is>
           <t>1914.380859,1913.928467,1914.653076,1914.486450,1914.212891,1913.936523,1914.355957,1914.033203,1913.500488,1914.006592,1913.274902,1912.527466,1913.246948,1913.974121,1913.228271,1912.843018,1912.684326,1912.294067,1911.680786,1912.712891,1911.681396,1910.772461,1910.957153,1911.453979</t>
@@ -2596,6 +2652,49 @@
       <c r="M22" t="inlineStr">
         <is>
           <t>1913.016724,1911.608643,1910.960571,1910.715820,1909.224731,1908.511108,1907.762573,1907.460938,1906.951172,1906.245728,1905.235474,1905.056641,1904.828491,1903.439575,1902.949707,1902.355713,1902.731201,1902.485107,1901.049072,1900.702637,1900.118042,1899.053223,1899.292969,1898.520142</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-08-10 02:24:15</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>24</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>1914.755615,1913.764160,1914.073486,1914.339355,1914.324707,1914.181641,1914.710815,1914.389648,1914.152832,1914.376343,1914.751709,1914.570679,1914.818359,1914.493530,1914.678955,1914.000610,1914.113159,1914.328613,1913.344482,1913.984863,1913.257080,1913.563721,1913.562256,1913.435791</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>1913.701172,1913.018066,1912.925293,1914.302490,1914.540771,1913.663086,1913.499268,1912.478271,1913.065308,1913.766357,1913.886719,1911.767456,1912.867676,1913.778320,1912.698975,1913.122314,1913.757690,1911.917969,1911.053711,1911.885986,1911.754883,1911.895752,1911.075928,1911.715332</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>1906.824951,1904.391846,1903.278076,1902.223267,1900.850586,1899.201172,1899.383545,1898.168213,1897.177734,1896.885010,1896.619873,1895.899902,1895.685547,1894.911377,1894.105957,1892.645996,1892.013062,1891.648438,1888.437988,1888.340942,1887.590454,1886.802979,1886.090820,1885.467285</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>1909.906494,1907.959717,1907.201172,1907.326660,1906.004150,1905.117920,1905.283447,1904.945557,1903.977417,1903.816895,1903.430054,1903.472656,1903.243408,1902.463745,1902.532959,1901.418945,1901.480225,1900.778931,1899.388672,1899.683350,1898.597778,1897.832764,1897.845093,1896.895508</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1291,6 +1291,44 @@
       </c>
       <c r="F23" t="n">
         <v>1913.435791015625</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1876.349975585938</v>
+      </c>
+      <c r="H23" t="n">
+        <v>37.0858154296875</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.976487111265398</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.285204463642467</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-08-11 02:14:51</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>24</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1877.606689453125</v>
       </c>
     </row>
   </sheetData>
@@ -1304,7 +1342,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2682,6 +2720,24 @@
           <t>1914.755615,1913.764160,1914.073486,1914.339355,1914.324707,1914.181641,1914.710815,1914.389648,1914.152832,1914.376343,1914.751709,1914.570679,1914.818359,1914.493530,1914.678955,1914.000610,1914.113159,1914.328613,1913.344482,1913.984863,1913.257080,1913.563721,1913.562256,1913.435791</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>1915.839966,1914.119995,1921.630005,1926.489990,1923.979980,1925.199951,1914.900024,1915.989990,1918.500000,1904.640015,1895.699951,1891.619995,1875.020020,1870.339966,1871.869995,1870.709961,1876.640015,1877.810059,1872.780029,1872.780029,1873.510010,1873.510010,1876.150024,1876.349976</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>1.084351,0.355835,7.556519,12.150635,9.655273,11.018310,0.189209,1.600342,4.347168,9.736328,19.051758,22.950684,39.798339,44.153564,42.808960,43.290649,37.473144,36.518554,40.564453,41.204834,39.747070,40.053711,37.412232,37.085815</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>0.056599,0.018590,0.393235,0.630714,0.501839,0.572320,0.009881,0.083526,0.226592,0.511190,1.004999,1.213282,2.122555,2.360724,2.286962,2.314129,1.996821,1.944742,2.166002,2.200196,2.121530,2.137897,1.994096,1.976487</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>1.285204463642467</v>
+      </c>
       <c r="K23" t="inlineStr">
         <is>
           <t>1913.701172,1913.018066,1912.925293,1914.302490,1914.540771,1913.663086,1913.499268,1912.478271,1913.065308,1913.766357,1913.886719,1911.767456,1912.867676,1913.778320,1912.698975,1913.122314,1913.757690,1911.917969,1911.053711,1911.885986,1911.754883,1911.895752,1911.075928,1911.715332</t>
@@ -2695,6 +2751,49 @@
       <c r="M23" t="inlineStr">
         <is>
           <t>1909.906494,1907.959717,1907.201172,1907.326660,1906.004150,1905.117920,1905.283447,1904.945557,1903.977417,1903.816895,1903.430054,1903.472656,1903.243408,1902.463745,1902.532959,1901.418945,1901.480225,1900.778931,1899.388672,1899.683350,1898.597778,1897.832764,1897.845093,1896.895508</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-08-11 02:14:51</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>24</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>1876.018677,1875.610352,1875.720215,1875.252930,1875.548096,1875.389648,1875.573975,1874.943237,1874.713135,1874.881470,1875.186523,1875.400757,1875.548340,1875.492188,1875.721680,1875.434814,1875.672485,1875.913818,1875.627930,1876.638794,1876.956055,1877.171387,1877.141846,1877.606689</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>1876.511963,1876.886963,1874.949951,1876.563232,1876.759033,1877.301392,1876.718018,1875.073975,1877.205566,1876.779785,1876.636719,1876.797974,1877.571533,1877.860840,1877.469238,1875.980469,1878.447021,1877.302734,1878.477539,1878.386230,1878.775635,1877.152344,1878.830566,1878.899170</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>1869.747314,1867.557617,1865.689819,1863.642090,1862.056763,1860.473267,1860.125000,1857.810059,1856.401367,1855.435181,1855.467651,1855.136963,1854.606445,1852.961670,1852.652832,1851.082153,1850.438965,1849.374023,1846.297485,1846.427979,1846.309326,1845.830322,1844.878662,1844.351074</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>1872.577393,1870.707153,1869.028564,1868.018799,1867.072021,1866.233887,1865.678833,1864.019287,1863.629761,1862.985840,1862.722046,1863.614990,1862.547852,1861.858521,1862.045044,1860.944336,1860.179932,1859.342285,1858.446533,1859.273926,1858.871094,1858.326538,1857.909912,1858.006592</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1329,6 +1329,44 @@
       </c>
       <c r="F24" t="n">
         <v>1877.606689453125</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1883.9599609375</v>
+      </c>
+      <c r="H24" t="n">
+        <v>6.353271484375</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.3372296447963508</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.3609097877037751</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-08-12 02:32:36</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>24</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1886.7060546875</v>
       </c>
     </row>
   </sheetData>
@@ -1342,7 +1380,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2781,6 +2819,24 @@
           <t>1876.018677,1875.610352,1875.720215,1875.252930,1875.548096,1875.389648,1875.573975,1874.943237,1874.713135,1874.881470,1875.186523,1875.400757,1875.548340,1875.492188,1875.721680,1875.434814,1875.672485,1875.913818,1875.627930,1876.638794,1876.956055,1877.171387,1877.141846,1877.606689</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>1879.079956,1874.430054,1872.140015,1872.500000,1876.010010,1877.579956,1883.790039,1884.609985,1891.420044,1886.319946,1888.310059,1871.859985,1861.199951,1863.189941,1862.739990,1864.390015,1879.689941,1880.479980,1883.000000,1880.630005,1877.290039,1880.760010,1882.920044,1883.959961</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>3.061279,1.180298,3.580200,2.752930,0.461914,2.190308,8.216064,9.666748,16.706909,11.438476,13.123536,3.540772,14.348389,12.302247,12.981690,11.044799,4.017456,4.566162,7.372070,3.991211,0.333984,3.588623,5.778198,6.353272</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>0.162914,0.062968,0.191236,0.147019,0.024622,0.116656,0.436145,0.512931,0.883300,0.606391,0.694988,0.189158,0.770921,0.660279,0.696914,0.592408,0.213730,0.242819,0.391507,0.212227,0.017791,0.190807,0.306874,0.337230</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>0.3609097877037751</v>
+      </c>
       <c r="K24" t="inlineStr">
         <is>
           <t>1876.511963,1876.886963,1874.949951,1876.563232,1876.759033,1877.301392,1876.718018,1875.073975,1877.205566,1876.779785,1876.636719,1876.797974,1877.571533,1877.860840,1877.469238,1875.980469,1878.447021,1877.302734,1878.477539,1878.386230,1878.775635,1877.152344,1878.830566,1878.899170</t>
@@ -2794,6 +2850,49 @@
       <c r="M24" t="inlineStr">
         <is>
           <t>1872.577393,1870.707153,1869.028564,1868.018799,1867.072021,1866.233887,1865.678833,1864.019287,1863.629761,1862.985840,1862.722046,1863.614990,1862.547852,1861.858521,1862.045044,1860.944336,1860.179932,1859.342285,1858.446533,1859.273926,1858.871094,1858.326538,1857.909912,1858.006592</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-08-12 02:32:36</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>24</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>1883.233398,1883.585205,1884.108154,1884.036621,1884.809814,1884.965210,1885.240479,1884.955078,1884.689087,1884.381348,1884.534424,1884.765137,1884.550903,1884.411865,1884.786865,1884.132568,1884.666504,1884.907471,1885.309937,1885.898438,1885.972656,1885.908691,1886.114014,1886.706055</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>1883.351685,1883.679932,1884.125000,1884.357178,1885.164795,1884.666016,1884.962158,1884.924438,1884.395264,1884.940063,1884.635742,1884.550171,1885.099854,1885.084473,1885.636719,1885.085938,1885.432129,1885.524536,1886.301270,1885.920898,1886.443726,1886.317139,1886.877441,1886.660156</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>1875.791260,1874.292969,1872.833984,1871.236328,1870.224609,1868.905151,1867.780029,1866.426880,1865.123657,1863.668701,1863.046509,1862.454102,1861.255737,1859.810059,1859.606689,1858.219727,1858.413086,1858.028198,1856.165894,1856.204102,1855.865234,1855.396729,1854.701660,1854.676025</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>1879.066162,1877.786255,1876.801758,1876.109985,1875.633789,1874.725098,1874.125488,1873.148682,1872.358643,1871.524780,1871.111694,1870.969482,1869.678223,1869.028931,1869.054443,1868.128418,1867.806396,1867.673340,1867.335205,1867.883911,1867.469971,1866.355347,1866.634033,1867.061035</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1367,6 +1367,44 @@
       </c>
       <c r="F25" t="n">
         <v>1886.7060546875</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1872.449951171875</v>
+      </c>
+      <c r="H25" t="n">
+        <v>14.256103515625</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.7613609916090308</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.4284802293635827</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-08-13 02:34:04</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>24</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1878.454467773438</v>
       </c>
     </row>
   </sheetData>
@@ -1380,7 +1418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2880,6 +2918,24 @@
           <t>1883.233398,1883.585205,1884.108154,1884.036621,1884.809814,1884.965210,1885.240479,1884.955078,1884.689087,1884.381348,1884.534424,1884.765137,1884.550903,1884.411865,1884.786865,1884.132568,1884.666504,1884.907471,1885.309937,1885.898438,1885.972656,1885.908691,1886.114014,1886.706055</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>1884.959961,1887.800049,1890.199951,1885.900024,1890.010010,1889.119995,1904.150024,1907.500000,1913.910034,1909.829956,1899.540039,1884.969971,1890.699951,1888.810059,1886.020020,1883.449951,1877.170044,1884.599976,1885.579956,1885.579956,1878.260010,1878.260010,1876.140015,1872.449951</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>1.726563,4.214844,6.091797,1.863403,5.200196,4.154785,18.909545,22.544922,29.220947,25.448608,15.005615,0.204834,6.149048,4.398194,1.233155,0.682617,7.496460,0.307495,0.270019,0.318482,7.712646,7.648681,9.973999,14.256104</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>0.091597,0.223267,0.322283,0.098807,0.275141,0.219932,0.993070,1.181909,1.526767,1.332506,0.789960,0.010867,0.325226,0.232855,0.065384,0.036243,0.399349,0.016316,0.014320,0.016890,0.410627,0.407222,0.531623,0.761361</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>0.4284802293635827</v>
+      </c>
       <c r="K25" t="inlineStr">
         <is>
           <t>1883.351685,1883.679932,1884.125000,1884.357178,1885.164795,1884.666016,1884.962158,1884.924438,1884.395264,1884.940063,1884.635742,1884.550171,1885.099854,1885.084473,1885.636719,1885.085938,1885.432129,1885.524536,1886.301270,1885.920898,1886.443726,1886.317139,1886.877441,1886.660156</t>
@@ -2893,6 +2949,49 @@
       <c r="M25" t="inlineStr">
         <is>
           <t>1879.066162,1877.786255,1876.801758,1876.109985,1875.633789,1874.725098,1874.125488,1873.148682,1872.358643,1871.524780,1871.111694,1870.969482,1869.678223,1869.028931,1869.054443,1868.128418,1867.806396,1867.673340,1867.335205,1867.883911,1867.469971,1866.355347,1866.634033,1867.061035</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-08-13 02:34:04</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>24</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>1873.206543,1873.479492,1873.654541,1873.913818,1874.173828,1874.441162,1874.886719,1875.860840,1876.365601,1876.614258,1876.737549,1877.117188,1876.958862,1877.109985,1876.771606,1876.471680,1876.594727,1876.407471,1876.670898,1877.149170,1877.529297,1878.015747,1878.034180,1878.454468</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>1873.271851,1873.694702,1874.271118,1874.635254,1874.994873,1875.116211,1875.752197,1876.951904,1877.227783,1877.750122,1877.140259,1879.077637,1878.545288,1878.001343,1877.897949,1877.631592,1877.300781,1876.505615,1876.949219,1877.850098,1877.941650,1878.083008,1878.207031,1878.498779</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>1862.564697,1860.638184,1858.843750,1857.184204,1855.982910,1854.800293,1853.885620,1853.492798,1852.729492,1851.262573,1850.261719,1850.264893,1849.598877,1848.763184,1847.899414,1847.189453,1847.055908,1846.454224,1845.344238,1845.081787,1845.218018,1845.613770,1845.522095,1845.317139</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>1867.009521,1865.514404,1864.188232,1863.590576,1862.697266,1861.917969,1861.406250,1861.754272,1861.369629,1860.830811,1859.756592,1859.830811,1859.016602,1859.050781,1858.139404,1857.863281,1857.326782,1856.904785,1856.783203,1857.310547,1857.234619,1857.186768,1857.318970,1857.858887</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1405,6 +1405,44 @@
       </c>
       <c r="F26" t="n">
         <v>1878.454467773438</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1886.219970703125</v>
+      </c>
+      <c r="H26" t="n">
+        <v>7.765502929687045</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.4116965704054286</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.5490299438358522</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-08-14 02:32:51</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>24</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1886.567749023438</v>
       </c>
     </row>
   </sheetData>
@@ -1418,7 +1456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2979,6 +3017,24 @@
           <t>1873.206543,1873.479492,1873.654541,1873.913818,1874.173828,1874.441162,1874.886719,1875.860840,1876.365601,1876.614258,1876.737549,1877.117188,1876.958862,1877.109985,1876.771606,1876.471680,1876.594727,1876.407471,1876.670898,1877.149170,1877.529297,1878.015747,1878.034180,1878.454468</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>1885.569946,1890.329956,1893.910034,1896.819946,1893.869995,1888.290039,1887.770020,1881.069946,1878.349976,1887.040039,1888.390015,1891.209961,1878.390015,1872.660034,1874.930054,1883.569946,1885.310059,1884.420044,1886.979980,1887.729980,1884.609985,1887.660034,1887.810059,1886.219971</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>12.363403,16.850464,20.255493,22.906128,19.696167,13.848877,12.883301,5.209106,1.984375,10.425781,11.652466,14.092773,1.431153,4.449951,1.841552,7.098266,8.715332,8.012573,10.309082,10.580810,7.080688,9.644287,9.775879,7.765503</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>0.655685,0.891403,1.069507,1.207607,1.039996,0.733408,0.682461,0.276923,0.105645,0.552494,0.617058,0.745172,0.076190,0.237627,0.098220,0.376852,0.462276,0.425201,0.546327,0.560504,0.375711,0.510912,0.517842,0.411697</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>0.5490299438358522</v>
+      </c>
       <c r="K26" t="inlineStr">
         <is>
           <t>1873.271851,1873.694702,1874.271118,1874.635254,1874.994873,1875.116211,1875.752197,1876.951904,1877.227783,1877.750122,1877.140259,1879.077637,1878.545288,1878.001343,1877.897949,1877.631592,1877.300781,1876.505615,1876.949219,1877.850098,1877.941650,1878.083008,1878.207031,1878.498779</t>
@@ -2992,6 +3048,49 @@
       <c r="M26" t="inlineStr">
         <is>
           <t>1867.009521,1865.514404,1864.188232,1863.590576,1862.697266,1861.917969,1861.406250,1861.754272,1861.369629,1860.830811,1859.756592,1859.830811,1859.016602,1859.050781,1858.139404,1857.863281,1857.326782,1856.904785,1856.783203,1857.310547,1857.234619,1857.186768,1857.318970,1857.858887</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-08-14 02:32:51</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>24</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>1885.466797,1886.197266,1886.884521,1887.276855,1887.006348,1886.989258,1886.916504,1886.887695,1887.080566,1887.207642,1886.805786,1886.053467,1885.355469,1884.832031,1884.578857,1884.791260,1885.569092,1885.690918,1886.048950,1885.864380,1885.601562,1885.582031,1885.950928,1886.567749</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>1885.189331,1885.679443,1886.805420,1887.051147,1887.017700,1886.477539,1886.661377,1886.916992,1886.515259,1886.483887,1886.541504,1885.914795,1885.320435,1883.891602,1883.217529,1884.244385,1883.866577,1884.894531,1885.172607,1885.041016,1884.631348,1884.413208,1884.902222,1885.359619</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>1877.215820,1875.879395,1874.446777,1873.589600,1871.633789,1870.632568,1869.215942,1868.109619,1867.291260,1866.327637,1864.854126,1863.711426,1862.833496,1861.478394,1860.488281,1860.363403,1860.719482,1860.772827,1859.850586,1859.590454,1859.014648,1858.875488,1858.465088,1858.685303</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>1880.817871,1879.872803,1879.208984,1879.062012,1877.510010,1876.912109,1875.868408,1875.352173,1875.060547,1874.439941,1873.053833,1872.210205,1871.239502,1870.386230,1869.434326,1869.794434,1870.265747,1869.810547,1870.206055,1870.253540,1869.501465,1868.906494,1869.310303,1869.585327</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1443,6 +1443,44 @@
       </c>
       <c r="F27" t="n">
         <v>1886.567749023438</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1882.219970703125</v>
+      </c>
+      <c r="H27" t="n">
+        <v>4.347778320312955</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.2309920406746504</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.5071027526158883</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-08-15 01:42:50</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>24</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1885.323364257812</v>
       </c>
     </row>
   </sheetData>
@@ -1456,7 +1494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3078,6 +3116,24 @@
           <t>1885.466797,1886.197266,1886.884521,1887.276855,1887.006348,1886.989258,1886.916504,1886.887695,1887.080566,1887.207642,1886.805786,1886.053467,1885.355469,1884.832031,1884.578857,1884.791260,1885.569092,1885.690918,1886.048950,1885.864380,1885.601562,1885.582031,1885.950928,1886.567749</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1881.260010,1882.979980,1882.089966,1870.939941,1871.180054,1876.410034,1871.060059,1873.939941,1876.410034,1871.229980,1867.319946,1864.930054,1879.239990,1883.369995,1876.630005,1873.630005,1879.040039,1878.560059,1876.560059,1876.560059,1880.689941,1880.689941,1882.219971,1882.219971</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>4.206787,3.217286,4.794555,16.336914,15.826294,10.579224,15.856445,12.947754,10.670532,15.977662,19.485840,21.123413,6.115479,1.462036,7.948852,11.161255,6.529053,7.130859,9.488891,9.304321,4.911621,4.892090,3.730957,4.347778</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>0.223615,0.170861,0.254746,0.873193,0.845792,0.563801,0.847458,0.690937,0.568667,0.853859,1.043519,1.132665,0.325423,0.077629,0.423571,0.595702,0.347467,0.379592,0.505653,0.495818,0.261161,0.260122,0.198221,0.230992</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>0.5071027526158883</v>
+      </c>
       <c r="K27" t="inlineStr">
         <is>
           <t>1885.189331,1885.679443,1886.805420,1887.051147,1887.017700,1886.477539,1886.661377,1886.916992,1886.515259,1886.483887,1886.541504,1885.914795,1885.320435,1883.891602,1883.217529,1884.244385,1883.866577,1884.894531,1885.172607,1885.041016,1884.631348,1884.413208,1884.902222,1885.359619</t>
@@ -3091,6 +3147,49 @@
       <c r="M27" t="inlineStr">
         <is>
           <t>1880.817871,1879.872803,1879.208984,1879.062012,1877.510010,1876.912109,1875.868408,1875.352173,1875.060547,1874.439941,1873.053833,1872.210205,1871.239502,1870.386230,1869.434326,1869.794434,1870.265747,1869.810547,1870.206055,1870.253540,1869.501465,1868.906494,1869.310303,1869.585327</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-08-15 01:42:50</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>24</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>1881.711182,1882.471191,1882.881836,1883.102051,1882.948242,1882.694824,1882.374023,1882.213867,1882.784180,1883.166016,1883.255371,1883.330811,1883.066650,1882.793701,1882.848511,1882.672119,1882.587158,1883.342163,1883.444214,1883.718262,1884.135254,1884.361084,1884.729980,1885.323364</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>1881.360107,1882.543945,1883.298828,1882.800903,1883.594727,1882.953125,1882.946777,1882.791992,1883.331543,1882.809326,1883.788818,1883.497314,1883.853760,1883.015381,1883.479248,1883.192627,1883.099365,1884.521606,1885.159790,1883.888672,1884.954956,1884.726318,1885.641113,1886.394531</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>1873.622803,1872.369141,1870.992432,1870.347168,1868.685791,1867.173828,1865.846924,1864.396973,1864.287598,1863.728027,1863.312988,1863.472900,1862.595703,1861.788818,1861.365234,1860.872559,1860.063965,1860.528809,1859.185059,1859.368652,1859.580322,1859.665405,1859.146484,1858.912842</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>1877.001953,1876.174805,1875.309326,1875.235840,1873.900513,1873.010498,1871.930176,1870.658691,1871.081787,1870.667725,1870.263428,1870.407104,1869.687988,1869.261353,1869.024292,1868.696167,1867.967285,1868.134521,1868.174194,1868.902710,1868.747559,1868.492676,1868.652344,1868.862793</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1481,6 +1481,44 @@
       </c>
       <c r="F28" t="n">
         <v>1885.323364257812</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1877.900024414062</v>
+      </c>
+      <c r="H28" t="n">
+        <v>7.423339843749545</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.3953000557665873</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.1381349502523493</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-08-16 01:49:52</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>24</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1881.41552734375</v>
       </c>
     </row>
   </sheetData>
@@ -1494,7 +1532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3177,6 +3215,24 @@
           <t>1881.711182,1882.471191,1882.881836,1883.102051,1882.948242,1882.694824,1882.374023,1882.213867,1882.784180,1883.166016,1883.255371,1883.330811,1883.066650,1882.793701,1882.848511,1882.672119,1882.587158,1883.342163,1883.444214,1883.718262,1884.135254,1884.361084,1884.729980,1885.323364</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>1883.119995,1880.890015,1882.579956,1878.959961,1880.359985,1878.560059,1875.099976,1878.410034,1879.160034,1877.290039,1881.560059,1881.500000,1881.479980,1882.890015,1883.089966,1882.400024,1880.869995,1882.359985,1881.329956,1883.130005,1882.579956,1880.979980,1880.650024,1877.900024</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>1.408813,1.581176,0.301880,4.142090,2.588257,4.134765,7.274047,3.803833,3.624146,5.875977,1.695312,1.830811,1.586670,0.096314,0.241455,0.272095,1.717163,0.982178,2.114258,0.588257,1.555298,3.381104,4.079956,7.423340</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>0.074813,0.084065,0.016035,0.220446,0.137647,0.220103,0.387929,0.202503,0.192860,0.313003,0.090101,0.097306,0.084331,0.005115,0.012822,0.014455,0.091296,0.052178,0.112381,0.031238,0.082615,0.179752,0.216944,0.395300</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>0.1381349502523493</v>
+      </c>
       <c r="K28" t="inlineStr">
         <is>
           <t>1881.360107,1882.543945,1883.298828,1882.800903,1883.594727,1882.953125,1882.946777,1882.791992,1883.331543,1882.809326,1883.788818,1883.497314,1883.853760,1883.015381,1883.479248,1883.192627,1883.099365,1884.521606,1885.159790,1883.888672,1884.954956,1884.726318,1885.641113,1886.394531</t>
@@ -3190,6 +3246,49 @@
       <c r="M28" t="inlineStr">
         <is>
           <t>1877.001953,1876.174805,1875.309326,1875.235840,1873.900513,1873.010498,1871.930176,1870.658691,1871.081787,1870.667725,1870.263428,1870.407104,1869.687988,1869.261353,1869.024292,1868.696167,1867.967285,1868.134521,1868.174194,1868.902710,1868.747559,1868.492676,1868.652344,1868.862793</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-08-16 01:49:52</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>24</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>1878.302002,1878.517822,1878.643555,1878.758911,1878.377930,1878.031982,1878.149902,1878.228516,1878.201660,1878.553467,1878.691895,1878.968750,1879.078857,1879.568848,1879.733887,1880.025269,1880.032227,1880.263428,1880.332153,1880.612549,1880.653198,1881.157837,1881.128662,1881.415527</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>1878.102539,1878.445435,1878.723877,1878.445557,1879.436890,1879.137817,1878.663818,1878.906494,1879.306885,1879.411987,1879.431641,1880.089111,1881.057129,1880.636963,1881.355469,1881.897461,1881.339844,1882.016846,1882.288330,1881.750244,1882.771118,1882.898682,1883.015259,1883.648438</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>1873.435791,1872.683105,1871.565674,1871.344849,1869.877441,1868.944336,1868.602051,1868.124512,1867.138672,1866.765869,1866.185913,1866.347412,1865.474976,1865.905029,1865.336182,1865.169556,1864.696045,1864.263184,1863.138672,1863.514648,1863.172363,1863.181519,1862.748047,1862.265503</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>1875.684326,1875.134033,1874.551514,1874.292236,1873.219971,1872.621826,1872.275635,1872.087036,1871.817627,1871.364258,1870.900269,1871.159424,1870.816895,1871.056641,1871.268799,1871.211060,1870.767944,1870.459839,1870.282471,1870.647705,1870.233887,1870.046021,1869.958008,1870.069092</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1519,6 +1519,44 @@
       </c>
       <c r="F29" t="n">
         <v>1881.41552734375</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1890.550048828125</v>
+      </c>
+      <c r="H29" t="n">
+        <v>9.134521484375</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.483167398294328</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.1572583709191611</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-08-17 01:47:23</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>24</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1888.040771484375</v>
       </c>
     </row>
   </sheetData>
@@ -1532,7 +1570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3276,6 +3314,24 @@
           <t>1878.302002,1878.517822,1878.643555,1878.758911,1878.377930,1878.031982,1878.149902,1878.228516,1878.201660,1878.553467,1878.691895,1878.968750,1879.078857,1879.568848,1879.733887,1880.025269,1880.032227,1880.263428,1880.332153,1880.612549,1880.653198,1881.157837,1881.128662,1881.415527</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>1881.790039,1881.010010,1879.949951,1878.119995,1878.660034,1879.300049,1878.829956,1878.140015,1878.760010,1878.910034,1877.750000,1879.910034,1881.380005,1882.010010,1887.589966,1883.119995,1883.689941,1884.150024,1880.099976,1873.719971,1870.959961,1876.770020,1876.770020,1890.550049</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>3.488037,2.492188,1.306396,0.638916,0.282104,1.268067,0.680054,0.088501,0.558350,0.356567,0.941895,0.941284,2.301148,2.441162,7.856079,3.094726,3.657714,3.886596,0.232177,6.892578,9.693237,4.387817,4.358642,9.134522</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>0.185357,0.132492,0.069491,0.034019,0.015016,0.067475,0.036196,0.004712,0.029719,0.018977,0.050161,0.050071,0.122312,0.129710,0.416196,0.164340,0.194178,0.206279,0.012349,0.367855,0.518089,0.233796,0.232242,0.483167</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>0.1572583709191611</v>
+      </c>
       <c r="K29" t="inlineStr">
         <is>
           <t>1878.102539,1878.445435,1878.723877,1878.445557,1879.436890,1879.137817,1878.663818,1878.906494,1879.306885,1879.411987,1879.431641,1880.089111,1881.057129,1880.636963,1881.355469,1881.897461,1881.339844,1882.016846,1882.288330,1881.750244,1882.771118,1882.898682,1883.015259,1883.648438</t>
@@ -3289,6 +3345,49 @@
       <c r="M29" t="inlineStr">
         <is>
           <t>1875.684326,1875.134033,1874.551514,1874.292236,1873.219971,1872.621826,1872.275635,1872.087036,1871.817627,1871.364258,1870.900269,1871.159424,1870.816895,1871.056641,1871.268799,1871.211060,1870.767944,1870.459839,1870.282471,1870.647705,1870.233887,1870.046021,1869.958008,1870.069092</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-08-17 01:47:23</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>24</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>1889.373047,1889.209595,1888.701416,1888.106201,1887.642700,1887.713867,1887.821045,1887.695801,1887.694092,1887.684937,1887.816284,1887.870117,1887.856201,1888.385132,1888.428711,1888.453369,1888.356079,1888.466919,1888.540771,1888.492920,1888.329102,1888.187012,1888.231201,1888.040771</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>1889.602051,1888.651489,1888.843384,1887.906006,1888.433838,1888.133545,1888.171875,1888.484863,1888.569580,1888.508057,1888.560547,1888.736328,1889.426392,1888.960938,1889.130615,1889.525635,1889.259033,1889.559326,1889.764282,1889.472168,1889.393066,1889.254639,1889.463379,1889.707520</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>1880.323730,1878.290527,1875.713867,1874.024658,1872.683350,1871.736206,1870.825439,1869.910889,1869.316650,1869.022461,1868.640625,1868.704590,1868.495972,1868.321289,1867.855591,1867.502197,1867.357178,1867.189697,1866.319580,1865.940674,1865.424805,1865.117432,1864.994873,1864.871094</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>1883.974365,1882.567627,1880.486206,1879.238037,1877.935303,1877.476440,1876.813843,1875.990479,1875.887207,1875.588135,1875.213623,1875.584595,1875.033447,1875.298340,1875.171021,1874.986084,1874.693848,1874.734619,1874.616699,1874.571411,1874.038574,1873.415283,1873.566528,1873.448486</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1557,6 +1557,44 @@
       </c>
       <c r="F30" t="n">
         <v>1888.040771484375</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1903.510009765625</v>
+      </c>
+      <c r="H30" t="n">
+        <v>15.46923828125</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.8126691323863695</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.7851237473589779</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-08-18 01:42:43</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>24</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1905.07421875</v>
       </c>
     </row>
   </sheetData>
@@ -1570,7 +1608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M30"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3375,6 +3413,24 @@
           <t>1889.373047,1889.209595,1888.701416,1888.106201,1887.642700,1887.713867,1887.821045,1887.695801,1887.694092,1887.684937,1887.816284,1887.870117,1887.856201,1888.385132,1888.428711,1888.453369,1888.356079,1888.466919,1888.540771,1888.492920,1888.329102,1888.187012,1888.231201,1888.040771</t>
         </is>
       </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>1900.400024,1899.060059,1901.780029,1897.790039,1905.140015,1899.140015,1892.369995,1891.969971,1905.040039,1902.709961,1896.939941,1902.869995,1907.699951,1911.459961,1905.359985,1907.180054,1908.410034,1905.630005,1904.880005,1905.250000,1905.250000,1908.079956,1908.079956,1903.510010</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>11.026977,9.850464,13.078613,9.683838,17.497315,11.426148,4.548950,4.274170,17.345947,15.025024,9.123657,14.999878,19.843750,23.074829,16.931274,18.726685,20.053955,17.163086,16.339234,16.757080,16.920898,19.892944,19.848755,15.469239</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>0.580245,0.518702,0.687704,0.510269,0.918427,0.601649,0.240384,0.225911,0.910529,0.789664,0.480967,0.788277,1.040192,1.207183,0.888613,0.981904,1.050820,0.900652,0.857757,0.879521,0.888120,1.042563,1.040248,0.812669</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>0.7851237473589779</v>
+      </c>
       <c r="K30" t="inlineStr">
         <is>
           <t>1889.602051,1888.651489,1888.843384,1887.906006,1888.433838,1888.133545,1888.171875,1888.484863,1888.569580,1888.508057,1888.560547,1888.736328,1889.426392,1888.960938,1889.130615,1889.525635,1889.259033,1889.559326,1889.764282,1889.472168,1889.393066,1889.254639,1889.463379,1889.707520</t>
@@ -3388,6 +3444,49 @@
       <c r="M30" t="inlineStr">
         <is>
           <t>1883.974365,1882.567627,1880.486206,1879.238037,1877.935303,1877.476440,1876.813843,1875.990479,1875.887207,1875.588135,1875.213623,1875.584595,1875.033447,1875.298340,1875.171021,1874.986084,1874.693848,1874.734619,1874.616699,1874.571411,1874.038574,1873.415283,1873.566528,1873.448486</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-08-18 01:42:43</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>24</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>1904.189941,1904.570312,1904.421387,1904.527588,1904.467285,1904.972168,1905.369385,1905.784424,1905.678955,1905.682129,1905.808838,1905.629761,1905.687256,1905.653320,1905.780029,1905.532593,1905.444824,1905.594482,1905.763184,1905.564453,1905.234497,1905.076904,1905.173096,1905.074219</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>1903.462036,1903.637939,1904.197754,1904.145508,1904.152832,1903.455566,1904.584229,1905.007324,1903.820801,1904.345337,1903.814575,1903.954590,1903.629639,1904.136719,1904.075684,1904.640625,1904.035278,1903.379639,1904.002930,1904.390991,1903.764526,1903.943359,1903.342285,1903.417725</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>1896.912354,1895.736572,1893.789551,1892.823486,1891.408447,1890.765747,1889.834961,1889.571289,1888.542480,1887.768799,1886.519165,1886.095093,1885.761353,1884.801636,1883.941406,1883.107422,1882.618896,1882.552490,1881.100220,1880.337402,1879.392334,1878.878418,1878.628662,1878.205322</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>1900.064575,1899.166748,1897.862305,1897.400635,1896.474854,1896.123047,1895.782715,1895.527344,1895.348999,1894.904175,1894.358154,1893.787720,1893.366577,1893.089966,1892.432129,1892.032471,1891.557617,1891.509033,1891.084473,1891.048828,1890.156494,1889.131592,1889.315552,1889.131348</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1595,6 +1595,44 @@
       </c>
       <c r="F31" t="n">
         <v>1905.07421875</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1911.800048828125</v>
+      </c>
+      <c r="H31" t="n">
+        <v>6.725830078125</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.3518061463722489</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.4294899673851628</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-08-19 01:44:27</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>24</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1911.6376953125</v>
       </c>
     </row>
   </sheetData>
@@ -1608,7 +1646,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3474,6 +3512,24 @@
           <t>1904.189941,1904.570312,1904.421387,1904.527588,1904.467285,1904.972168,1905.369385,1905.784424,1905.678955,1905.682129,1905.808838,1905.629761,1905.687256,1905.653320,1905.780029,1905.532593,1905.444824,1905.594482,1905.763184,1905.564453,1905.234497,1905.076904,1905.173096,1905.074219</t>
         </is>
       </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>1891.390015,1892.890015,1894.770020,1893.900024,1901.329956,1896.939941,1898.380005,1894.800049,1896.089966,1901.209961,1897.650024,1896.000000,1909.750000,1916.469971,1917.380005,1910.229980,1915.310059,1912.199951,1911.520020,1910.969971,1912.239990,1915.989990,1912.209961,1911.800049</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>12.799926,11.680297,9.651367,10.627564,3.137329,8.032227,6.989380,10.984375,9.588989,4.472168,8.158814,9.629761,4.062744,10.816651,11.599976,4.697387,9.865235,6.605469,5.756836,5.405518,7.005493,10.913086,7.036865,6.725830</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>0.676747,0.617062,0.509369,0.561147,0.165007,0.423431,0.368176,0.579712,0.505724,0.235227,0.429943,0.507899,0.212737,0.564405,0.604991,0.245907,0.515072,0.345438,0.301165,0.282868,0.366350,0.569580,0.367996,0.351806</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>0.4294899673851628</v>
+      </c>
       <c r="K31" t="inlineStr">
         <is>
           <t>1903.462036,1903.637939,1904.197754,1904.145508,1904.152832,1903.455566,1904.584229,1905.007324,1903.820801,1904.345337,1903.814575,1903.954590,1903.629639,1904.136719,1904.075684,1904.640625,1904.035278,1903.379639,1904.002930,1904.390991,1903.764526,1903.943359,1903.342285,1903.417725</t>
@@ -3487,6 +3543,49 @@
       <c r="M31" t="inlineStr">
         <is>
           <t>1900.064575,1899.166748,1897.862305,1897.400635,1896.474854,1896.123047,1895.782715,1895.527344,1895.348999,1894.904175,1894.358154,1893.787720,1893.366577,1893.089966,1892.432129,1892.032471,1891.557617,1891.509033,1891.084473,1891.048828,1890.156494,1889.131592,1889.315552,1889.131348</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-08-19 01:44:27</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>24</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>1912.358154,1912.550293,1912.422241,1912.754150,1912.737915,1912.798340,1913.133057,1913.318848,1913.565918,1913.362305,1913.838379,1913.351807,1913.364136,1913.335938,1913.161865,1913.136841,1913.048096,1912.619507,1912.628662,1912.262207,1912.069824,1911.982666,1912.232910,1911.637695</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>1911.916992,1911.809204,1912.473633,1912.311035,1912.213989,1911.688965,1912.210449,1912.689453,1911.892090,1912.068604,1912.182617,1911.711304,1911.286865,1912.131104,1911.269165,1911.674927,1911.282959,1909.992920,1910.913086,1910.575073,1910.186035,1910.072388,1909.927734,1909.667725</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>1905.036133,1903.748535,1902.252686,1901.666138,1900.653564,1899.914795,1899.425049,1898.883301,1898.624756,1897.551758,1897.055176,1895.833496,1895.636475,1894.439941,1893.652588,1892.871826,1892.165894,1891.524292,1890.253174,1889.270264,1888.650391,1888.068359,1887.768799,1886.385986</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>1907.927856,1906.971802,1905.959106,1905.857178,1905.425049,1904.760742,1904.741211,1904.462891,1904.335205,1903.788818,1903.790894,1902.859863,1902.199097,1901.781006,1901.108643,1900.902100,1900.260742,1899.934692,1899.360107,1899.160400,1898.415039,1897.853271,1898.048096,1897.050415</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1633,6 +1633,44 @@
       </c>
       <c r="F32" t="n">
         <v>1911.6376953125</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2263.969970703125</v>
+      </c>
+      <c r="H32" t="n">
+        <v>352.332275390625</v>
+      </c>
+      <c r="I32" t="n">
+        <v>15.56258607446107</v>
+      </c>
+      <c r="J32" t="n">
+        <v>5.913499375325404</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-08-20 01:43:27</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>24</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1978.92578125</v>
       </c>
     </row>
   </sheetData>
@@ -1646,7 +1684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:M33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3573,6 +3611,24 @@
           <t>1912.358154,1912.550293,1912.422241,1912.754150,1912.737915,1912.798340,1913.133057,1913.318848,1913.565918,1913.362305,1913.838379,1913.351807,1913.364136,1913.335938,1913.161865,1913.136841,1913.048096,1912.619507,1912.628662,1912.262207,1912.069824,1911.982666,1912.232910,1911.637695</t>
         </is>
       </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>1906.280029,1910.410034,1909.109985,1908.699951,1916.089966,1914.459961,1920.099976,1917.630005,1918.510010,1921.550049,1935.699951,1931.310059,1968.599976,2085.350098,2088.770020,2090.620117,2091.620117,2101.929932,2218.300049,2285.479980,2262.139893,2261.139893,2261.139893,2263.969971</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>6.078125,2.140259,3.312256,4.054199,3.352051,1.661621,6.966919,4.311157,4.944092,8.187744,21.861572,17.958252,55.235840,172.014160,175.608155,177.483276,178.572021,189.310425,305.671387,373.217773,350.070069,349.157227,348.906983,352.332276</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>0.318847,0.112031,0.173497,0.212406,0.174942,0.086793,0.362841,0.224817,0.257705,0.426101,1.129388,0.929848,2.805844,8.248695,8.407252,8.489504,8.537498,9.006505,13.779533,16.329952,15.475173,15.441646,15.430579,15.562586</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>5.913499375325404</v>
+      </c>
       <c r="K32" t="inlineStr">
         <is>
           <t>1911.916992,1911.809204,1912.473633,1912.311035,1912.213989,1911.688965,1912.210449,1912.689453,1911.892090,1912.068604,1912.182617,1911.711304,1911.286865,1912.131104,1911.269165,1911.674927,1911.282959,1909.992920,1910.913086,1910.575073,1910.186035,1910.072388,1909.927734,1909.667725</t>
@@ -3586,6 +3642,49 @@
       <c r="M32" t="inlineStr">
         <is>
           <t>1907.927856,1906.971802,1905.959106,1905.857178,1905.425049,1904.760742,1904.741211,1904.462891,1904.335205,1903.788818,1903.790894,1902.859863,1902.199097,1901.781006,1901.108643,1900.902100,1900.260742,1899.934692,1899.360107,1899.160400,1898.415039,1897.853271,1898.048096,1897.050415</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-08-20 01:43:27</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>24</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2257.928711,2246.980713,2233.536377,2220.592773,2205.530762,2187.585449,2171.360107,2159.818848,2143.962891,2126.084961,2113.247314,2099.003662,2082.281250,2068.703857,2053.434814,2039.959351,2029.402954,2018.052612,2009.855713,1998.406738,1992.993164,1988.735962,1984.886841,1978.925781</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>2249.975586,2229.524902,2222.199951,2204.074219,2183.247070,2165.104736,2146.629395,2137.459717,2120.935059,2104.521240,2093.724365,2083.213623,2067.801514,2058.485107,2047.534424,2045.132446,2033.114014,2027.498291,2018.958496,2010.443970,2004.996338,2007.781494,1998.460205,1993.951904</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>2202.881592,2168.003174,2134.285156,2099.522705,2070.079590,2034.265137,2005.129150,1985.050415,1966.639648,1945.901367,1927.612061,1910.468262,1900.482178,1884.871948,1873.283569,1867.582031,1863.416260,1856.068604,1853.197266,1841.313965,1847.802612,1850.036011,1849.308105,1850.461670</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>2225.143799,2200.015625,2172.169189,2148.775879,2120.403809,2091.573486,2067.415283,2047.852783,2028.633545,2006.754639,1988.216309,1974.094727,1956.058838,1943.351807,1928.963501,1921.004150,1914.232422,1903.975342,1901.181274,1890.111816,1889.905762,1886.549561,1887.710815,1883.592285</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:J34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1671,6 +1671,44 @@
       </c>
       <c r="F33" t="n">
         <v>1978.92578125</v>
+      </c>
+      <c r="G33" t="n">
+        <v>2374.52001953125</v>
+      </c>
+      <c r="H33" t="n">
+        <v>395.59423828125</v>
+      </c>
+      <c r="I33" t="n">
+        <v>16.65996643647349</v>
+      </c>
+      <c r="J33" t="n">
+        <v>8.50809663014771</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-08-21 01:48:49</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>24</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2131.485107421875</v>
       </c>
     </row>
   </sheetData>
@@ -1684,7 +1722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:M34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3672,6 +3710,24 @@
           <t>2257.928711,2246.980713,2233.536377,2220.592773,2205.530762,2187.585449,2171.360107,2159.818848,2143.962891,2126.084961,2113.247314,2099.003662,2082.281250,2068.703857,2053.434814,2039.959351,2029.402954,2018.052612,2009.855713,1998.406738,1992.993164,1988.735962,1984.886841,1978.925781</t>
         </is>
       </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2250.649902,2249.419922,2248.550049,2246.750000,2261.100098,2249.959961,2280.000000,2276.949951,2285.139893,2294.830078,2288.600098,2274.500000,2279.899902,2325.939941,2343.199951,2343.500000,2315.850098,2323.469971,2317.909912,2318.510010,2313.669922,2326.600098,2340.229980,2374.520020</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>7.278809,2.439209,15.013672,26.157227,55.569336,62.374512,108.639893,117.131103,141.177002,168.745117,175.352784,175.496338,197.618652,257.236084,289.765137,303.540649,286.447144,305.417359,308.054199,320.103272,320.676758,337.864136,355.343139,395.594239</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>0.323409,0.108437,0.667705,1.164225,2.457624,2.772250,4.764908,5.144211,6.178046,7.353273,7.662011,7.715821,8.667865,11.059447,12.366215,12.952449,12.368985,13.144881,13.290171,13.806422,13.860091,14.521797,15.184112,16.659966</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>8.50809663014771</v>
+      </c>
       <c r="K33" t="inlineStr">
         <is>
           <t>2249.975586,2229.524902,2222.199951,2204.074219,2183.247070,2165.104736,2146.629395,2137.459717,2120.935059,2104.521240,2093.724365,2083.213623,2067.801514,2058.485107,2047.534424,2045.132446,2033.114014,2027.498291,2018.958496,2010.443970,2004.996338,2007.781494,1998.460205,1993.951904</t>
@@ -3685,6 +3741,49 @@
       <c r="M33" t="inlineStr">
         <is>
           <t>2225.143799,2200.015625,2172.169189,2148.775879,2120.403809,2091.573486,2067.415283,2047.852783,2028.633545,2006.754639,1988.216309,1974.094727,1956.058838,1943.351807,1928.963501,1921.004150,1914.232422,1903.975342,1901.181274,1890.111816,1889.905762,1886.549561,1887.710815,1883.592285</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-08-21 01:48:49</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>24</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2377.747803,2377.819092,2376.050781,2370.484863,2362.872559,2351.067383,2335.187012,2321.573486,2306.091064,2291.481201,2278.540039,2265.517578,2247.872314,2230.406494,2217.168945,2197.651367,2187.725586,2171.989990,2161.759766,2149.579102,2144.356201,2136.374268,2132.304199,2131.485107</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>2364.516113,2359.850586,2359.882812,2346.217773,2329.764648,2315.607910,2288.679932,2288.106445,2272.507568,2260.980225,2245.271484,2236.455811,2213.685059,2210.721924,2194.796631,2187.493652,2175.735596,2157.147461,2155.995361,2142.826660,2132.578125,2139.902832,2121.715820,2120.658691</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>2331.528809,2309.502686,2286.368896,2257.953369,2228.274414,2196.835938,2161.521973,2137.100342,2115.215088,2094.688721,2069.271729,2049.596680,2036.851318,2012.270508,1995.671143,1982.087769,1968.854492,1953.846558,1942.723755,1922.051270,1926.603760,1919.606445,1916.677490,1923.472900</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>2350.390869,2338.939209,2321.650879,2304.346191,2280.066895,2256.300781,2232.677490,2207.327637,2186.596924,2166.397217,2144.562988,2129.010254,2108.320557,2088.802490,2071.651367,2058.415283,2045.049561,2028.530762,2019.998413,2006.780518,2003.717285,1991.847290,1990.464844,1989.200439</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:J35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1709,6 +1709,44 @@
       </c>
       <c r="F34" t="n">
         <v>2131.485107421875</v>
+      </c>
+      <c r="G34" t="n">
+        <v>2516.090087890625</v>
+      </c>
+      <c r="H34" t="n">
+        <v>384.60498046875</v>
+      </c>
+      <c r="I34" t="n">
+        <v>15.28581914931294</v>
+      </c>
+      <c r="J34" t="n">
+        <v>6.849165719241002</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-08-22 01:41:49</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>24</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2419.12353515625</v>
       </c>
     </row>
   </sheetData>
@@ -1722,7 +1760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M34"/>
+  <dimension ref="A1:M35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3771,6 +3809,24 @@
           <t>2377.747803,2377.819092,2376.050781,2370.484863,2362.872559,2351.067383,2335.187012,2321.573486,2306.091064,2291.481201,2278.540039,2265.517578,2247.872314,2230.406494,2217.168945,2197.651367,2187.725586,2171.989990,2161.759766,2149.579102,2144.356201,2136.374268,2132.304199,2131.485107</t>
         </is>
       </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2344.520020,2340.030029,2353.280029,2367.600098,2371.280029,2369.979980,2443.090088,2403.600098,2395.020020,2369.850098,2387.560059,2388.129883,2392.969971,2392.889893,2406.020020,2423.120117,2419.899902,2413.209961,2440.510010,2489.540039,2489.540039,2521.810059,2521.810059,2516.090088</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>33.227783,37.789063,22.770752,2.884765,8.407470,18.912597,107.903076,82.026612,88.928956,78.368897,109.020020,122.612305,145.097657,162.483399,188.851075,225.468750,232.174316,241.219971,278.750244,339.960937,345.183838,385.435791,389.505860,384.604981</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1.417253,1.614896,0.967618,0.121843,0.354554,0.798007,4.416664,3.412656,3.713078,3.306914,4.566169,5.134239,6.063497,6.790258,7.849107,9.304894,9.594377,9.995814,11.421803,13.655572,13.865366,15.284093,15.445488,15.285819</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>6.849165719241002</v>
+      </c>
       <c r="K34" t="inlineStr">
         <is>
           <t>2364.516113,2359.850586,2359.882812,2346.217773,2329.764648,2315.607910,2288.679932,2288.106445,2272.507568,2260.980225,2245.271484,2236.455811,2213.685059,2210.721924,2194.796631,2187.493652,2175.735596,2157.147461,2155.995361,2142.826660,2132.578125,2139.902832,2121.715820,2120.658691</t>
@@ -3784,6 +3840,49 @@
       <c r="M34" t="inlineStr">
         <is>
           <t>2350.390869,2338.939209,2321.650879,2304.346191,2280.066895,2256.300781,2232.677490,2207.327637,2186.596924,2166.397217,2144.562988,2129.010254,2108.320557,2088.802490,2071.651367,2058.415283,2045.049561,2028.530762,2019.998413,2006.780518,2003.717285,1991.847290,1990.464844,1989.200439</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-08-22 01:41:49</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>24</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2525.089844,2524.488037,2517.490479,2521.157227,2515.725098,2510.076660,2499.402344,2496.185547,2490.338623,2482.510254,2474.841553,2474.006836,2468.818848,2456.452148,2452.519531,2442.540039,2440.365234,2436.811035,2431.406250,2426.065430,2420.685059,2421.835205,2419.094238,2419.123535</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>2525.875000,2507.349609,2508.169434,2506.725586,2490.949219,2481.455811,2455.595215,2467.695312,2449.065918,2444.475342,2431.098633,2424.675293,2407.253418,2417.697266,2400.720703,2397.797852,2403.396484,2377.395020,2383.788086,2381.222656,2380.030273,2384.657227,2355.802734,2360.538574</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>2485.176270,2463.785645,2433.885254,2418.850342,2390.331787,2371.029297,2340.403809,2321.642578,2313.005615,2296.739746,2277.508301,2262.364990,2262.811523,2236.322998,2220.643555,2212.737793,2199.279785,2189.265869,2169.578125,2150.240967,2145.711914,2139.826904,2133.320801,2137.666992</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>2499.387695,2488.520020,2463.462646,2459.692383,2438.470703,2422.651855,2406.317871,2390.622559,2380.185059,2368.489746,2354.320312,2346.357910,2335.343262,2318.146729,2305.384766,2299.432129,2290.073242,2282.429932,2271.292480,2259.808105,2250.469971,2244.286621,2244.769775,2243.584961</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J35"/>
+  <dimension ref="A1:J36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1747,6 +1747,44 @@
       </c>
       <c r="F35" t="n">
         <v>2419.12353515625</v>
+      </c>
+      <c r="G35" t="n">
+        <v>2427.9599609375</v>
+      </c>
+      <c r="H35" t="n">
+        <v>8.83642578125</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.3639444605107088</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.461552015161733</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-08-23 01:51:43</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>24</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2414.269287109375</v>
       </c>
     </row>
   </sheetData>
@@ -1760,7 +1798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M35"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3870,6 +3908,24 @@
           <t>2525.089844,2524.488037,2517.490479,2521.157227,2515.725098,2510.076660,2499.402344,2496.185547,2490.338623,2482.510254,2474.841553,2474.006836,2468.818848,2456.452148,2452.519531,2442.540039,2440.365234,2436.811035,2431.406250,2426.065430,2420.685059,2421.835205,2419.094238,2419.123535</t>
         </is>
       </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2515.469971,2514.659912,2514.810059,2440.239990,2437.560059,2432.760010,2425.510010,2421.689941,2412.850098,2424.020020,2428.399902,2429.979980,2413.629883,2410.469971,2422.370117,2426.100098,2427.600098,2439.000000,2431.800049,2406.969971,2414.219971,2430.820068,2430.820068,2427.959961</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>9.619873,9.828125,2.680420,80.917237,78.165039,77.316650,73.892334,74.495606,77.488525,58.490234,46.441651,44.026856,55.188965,45.982177,30.149414,16.439941,12.765136,2.188965,0.393799,19.095459,6.465088,8.984863,11.725830,8.836426</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>0.382428,0.390833,0.106585,3.315954,3.206692,3.178145,3.046466,3.076183,3.211494,2.412944,1.912438,1.811820,2.286555,1.907602,1.244625,0.677628,0.525834,0.089748,0.016194,0.793340,0.267792,0.369623,0.482382,0.363944</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>1.461552015161733</v>
+      </c>
       <c r="K35" t="inlineStr">
         <is>
           <t>2525.875000,2507.349609,2508.169434,2506.725586,2490.949219,2481.455811,2455.595215,2467.695312,2449.065918,2444.475342,2431.098633,2424.675293,2407.253418,2417.697266,2400.720703,2397.797852,2403.396484,2377.395020,2383.788086,2381.222656,2380.030273,2384.657227,2355.802734,2360.538574</t>
@@ -3883,6 +3939,49 @@
       <c r="M35" t="inlineStr">
         <is>
           <t>2499.387695,2488.520020,2463.462646,2459.692383,2438.470703,2422.651855,2406.317871,2390.622559,2380.185059,2368.489746,2354.320312,2346.357910,2335.343262,2318.146729,2305.384766,2299.432129,2290.073242,2282.429932,2271.292480,2259.808105,2250.469971,2244.286621,2244.769775,2243.584961</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-08-23 01:51:43</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>24</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2430.460449,2429.766113,2431.435059,2434.244141,2429.852539,2428.641602,2425.494141,2422.877930,2426.271973,2424.229492,2423.851074,2421.449707,2419.595459,2414.125732,2416.040283,2412.865723,2414.110352,2414.743652,2415.161865,2411.844238,2410.395508,2413.696777,2411.208008,2414.269287</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>2427.176270,2417.240234,2427.688477,2431.461426,2415.308105,2419.489258,2403.850586,2408.368652,2404.570312,2404.652588,2394.607666,2392.116699,2376.671143,2387.580811,2382.661133,2380.459229,2376.367676,2364.184814,2363.670410,2368.228027,2366.570068,2362.482422,2345.346191,2348.572510</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>2410.093750,2400.595947,2386.770020,2381.766113,2361.635254,2354.301758,2341.445312,2325.303711,2325.102051,2316.046631,2303.877441,2287.862305,2288.248535,2268.532471,2258.152100,2249.437012,2241.707275,2232.008789,2215.288086,2195.816406,2188.282959,2179.504883,2173.697266,2175.778809</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>2418.350586,2410.883789,2403.079590,2403.394043,2391.045410,2385.940430,2380.513672,2368.872559,2370.239014,2365.023438,2360.857422,2351.633301,2344.168945,2333.565918,2328.113525,2322.335693,2319.568848,2312.328369,2304.016357,2295.770996,2287.568359,2278.006836,2280.149658,2280.601074</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J36"/>
+  <dimension ref="A1:J37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1785,6 +1785,44 @@
       </c>
       <c r="F36" t="n">
         <v>2414.269287109375</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2437.9599609375</v>
+      </c>
+      <c r="H36" t="n">
+        <v>23.690673828125</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.9717417105986811</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.274270331448567</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-08-24 01:49:22</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>24</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2426.85888671875</v>
       </c>
     </row>
   </sheetData>
@@ -1798,7 +1836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3969,6 +4007,24 @@
           <t>2430.460449,2429.766113,2431.435059,2434.244141,2429.852539,2428.641602,2425.494141,2422.877930,2426.271973,2424.229492,2423.851074,2421.449707,2419.595459,2414.125732,2416.040283,2412.865723,2414.110352,2414.743652,2415.161865,2411.844238,2410.395508,2413.696777,2411.208008,2414.269287</t>
         </is>
       </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2416.520020,2413.739990,2379.989990,2373.169922,2389.510010,2388.419922,2412.389893,2411.179932,2414.750000,2433.360107,2426.719971,2459.280029,2438.500000,2438.389893,2450.540039,2440.260010,2448.239990,2444.459961,2450.100098,2469.870117,2455.000000,2463.540039,2465.429932,2437.959961</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>13.940429,16.026123,51.445069,61.074219,40.342529,40.221680,13.104248,11.697998,11.521973,9.130615,2.868897,37.830322,18.904541,24.264161,34.499756,27.394287,34.129638,29.716309,34.938233,58.025879,44.604492,49.843262,54.221924,23.690674</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>0.576880,0.663954,2.161567,2.573529,1.688318,1.684029,0.543206,0.485157,0.477150,0.375227,0.118221,1.538268,0.775253,0.995089,1.407843,1.122597,1.394048,1.215659,1.425992,2.349349,1.816884,2.023237,2.199289,0.971742</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>1.274270331448567</v>
+      </c>
       <c r="K36" t="inlineStr">
         <is>
           <t>2427.176270,2417.240234,2427.688477,2431.461426,2415.308105,2419.489258,2403.850586,2408.368652,2404.570312,2404.652588,2394.607666,2392.116699,2376.671143,2387.580811,2382.661133,2380.459229,2376.367676,2364.184814,2363.670410,2368.228027,2366.570068,2362.482422,2345.346191,2348.572510</t>
@@ -3982,6 +4038,49 @@
       <c r="M36" t="inlineStr">
         <is>
           <t>2418.350586,2410.883789,2403.079590,2403.394043,2391.045410,2385.940430,2380.513672,2368.872559,2370.239014,2365.023438,2360.857422,2351.633301,2344.168945,2333.565918,2328.113525,2322.335693,2319.568848,2312.328369,2304.016357,2295.770996,2287.568359,2278.006836,2280.149658,2280.601074</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-08-24 01:49:22</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>24</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2438.166260,2436.384766,2434.769043,2437.383301,2434.792969,2437.062988,2436.983887,2434.497559,2436.501953,2436.179199,2435.659180,2434.647705,2433.108398,2431.355713,2431.998535,2432.551025,2431.811035,2431.050781,2432.701904,2431.435547,2431.447998,2430.008789,2428.052246,2426.858887</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>2433.082031,2427.311035,2433.352051,2437.103027,2430.940430,2432.395996,2417.369629,2426.260742,2424.295898,2421.075439,2416.909668,2412.778809,2408.188965,2412.604980,2409.317383,2412.907715,2400.457031,2400.048828,2401.979492,2404.177734,2403.738281,2396.855469,2392.303223,2390.636719</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>2407.416504,2398.957520,2386.325195,2387.984863,2374.306396,2371.317871,2368.868164,2357.632324,2353.566650,2347.816895,2340.610352,2328.768311,2326.249268,2312.862549,2301.256592,2299.174316,2292.047852,2285.982422,2277.290039,2262.161377,2258.006592,2244.985352,2242.612793,2238.516602</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>2419.923096,2413.029297,2406.045410,2407.562744,2400.555664,2399.546875,2399.312012,2391.339355,2391.059326,2387.143066,2383.056396,2378.414551,2371.188477,2362.992188,2356.965332,2356.672119,2354.459717,2349.164307,2345.016846,2342.253662,2337.783691,2326.738770,2328.544434,2327.265869</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:J38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1823,6 +1823,44 @@
       </c>
       <c r="F37" t="n">
         <v>2426.85888671875</v>
+      </c>
+      <c r="G37" t="n">
+        <v>2495.469970703125</v>
+      </c>
+      <c r="H37" t="n">
+        <v>68.611083984375</v>
+      </c>
+      <c r="I37" t="n">
+        <v>2.749425350329625</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.633662893677655</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-08-25 01:43:44</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>24</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2492.23095703125</v>
       </c>
     </row>
   </sheetData>
@@ -1836,7 +1874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4068,6 +4106,24 @@
           <t>2438.166260,2436.384766,2434.769043,2437.383301,2434.792969,2437.062988,2436.983887,2434.497559,2436.501953,2436.179199,2435.659180,2434.647705,2433.108398,2431.355713,2431.998535,2432.551025,2431.811035,2431.050781,2432.701904,2431.435547,2431.447998,2430.008789,2428.052246,2426.858887</t>
         </is>
       </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2443.790039,2430.290039,2438.300049,2449.290039,2456.409912,2454.229980,2454.379883,2462.729980,2464.590088,2494.129883,2512.290039,2493.050049,2515.500000,2487.209961,2476.899902,2468.649902,2473.919922,2469.820068,2474.469971,2482.479980,2482.479980,2493.719971,2493.719971,2495.469971</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>5.623779,6.094727,3.531006,11.906738,21.616943,17.166992,17.395996,28.232421,28.088135,57.950684,76.630859,58.402344,82.391602,55.854248,44.901367,36.098877,42.108887,38.769287,41.768067,51.044433,51.031982,63.711182,65.667725,68.611084</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>0.230125,0.250782,0.144814,0.486130,0.880022,0.699486,0.708774,1.146387,1.139668,2.323483,3.050239,2.342606,3.275357,2.245659,1.812805,1.462292,1.702112,1.569721,1.687960,2.056187,2.055686,2.554865,2.633324,2.749425</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>1.633662893677655</v>
+      </c>
       <c r="K37" t="inlineStr">
         <is>
           <t>2433.082031,2427.311035,2433.352051,2437.103027,2430.940430,2432.395996,2417.369629,2426.260742,2424.295898,2421.075439,2416.909668,2412.778809,2408.188965,2412.604980,2409.317383,2412.907715,2400.457031,2400.048828,2401.979492,2404.177734,2403.738281,2396.855469,2392.303223,2390.636719</t>
@@ -4081,6 +4137,49 @@
       <c r="M37" t="inlineStr">
         <is>
           <t>2419.923096,2413.029297,2406.045410,2407.562744,2400.555664,2399.546875,2399.312012,2391.339355,2391.059326,2387.143066,2383.056396,2378.414551,2371.188477,2362.992188,2356.965332,2356.672119,2354.459717,2349.164307,2345.016846,2342.253662,2337.783691,2326.738770,2328.544434,2327.265869</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-08-25 01:43:44</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>24</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2498.067139,2497.684082,2497.015137,2498.215332,2495.656738,2497.707520,2499.636963,2495.103516,2495.110107,2495.727539,2495.598877,2495.706055,2493.485840,2492.159424,2493.798828,2493.949951,2492.339600,2491.254150,2492.311035,2494.450684,2491.275391,2491.069824,2491.113281,2492.230957</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>2496.395020,2495.640625,2494.763184,2496.612793,2494.782227,2494.569336,2489.884033,2490.918945,2494.168945,2489.020996,2487.291992,2482.661621,2483.340332,2482.926270,2482.486816,2484.751465,2474.915527,2471.805664,2475.930664,2480.683838,2479.364990,2470.536865,2472.593750,2477.772949</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>2467.885254,2466.174072,2460.484619,2463.709473,2454.708984,2454.329102,2455.257080,2444.495361,2439.460449,2435.416016,2432.735107,2425.730469,2425.352295,2414.259277,2408.305420,2406.193604,2401.399414,2396.817871,2389.685303,2385.493652,2379.818359,2372.814941,2371.787842,2372.011475</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>2482.208252,2478.471436,2476.667725,2478.608643,2473.532227,2475.010742,2476.002686,2468.168457,2467.199707,2464.728760,2463.898926,2461.085449,2457.239746,2449.722168,2449.278809,2447.433594,2447.493652,2441.840332,2440.574219,2443.204590,2436.406250,2430.743164,2433.809082,2435.290039</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1861,6 +1861,44 @@
       </c>
       <c r="F38" t="n">
         <v>2492.23095703125</v>
+      </c>
+      <c r="G38" t="n">
+        <v>2455.77001953125</v>
+      </c>
+      <c r="H38" t="n">
+        <v>36.4609375</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.484704887266258</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.9666676627669962</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-08-26 01:49:10</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>24</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2448.604736328125</v>
       </c>
     </row>
   </sheetData>
@@ -1874,7 +1912,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M38"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4167,6 +4205,24 @@
           <t>2498.067139,2497.684082,2497.015137,2498.215332,2495.656738,2497.707520,2499.636963,2495.103516,2495.110107,2495.727539,2495.598877,2495.706055,2493.485840,2492.159424,2493.798828,2493.949951,2492.339600,2491.254150,2492.311035,2494.450684,2491.275391,2491.069824,2491.113281,2492.230957</t>
         </is>
       </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2507.159912,2498.790039,2494.169922,2507.899902,2500.270020,2478.120117,2484.110107,2474.030029,2481.469971,2477.520020,2473.129883,2460.739990,2476.969971,2483.350098,2471.080078,2471.250000,2467.510010,2463.669922,2435.860107,2441.520020,2451.250000,2446.580078,2446.580078,2455.770020</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>9.092773,1.105957,2.845215,9.684570,4.613282,19.587403,15.526856,21.073487,13.640136,18.207519,22.468994,34.966065,16.515869,8.809326,22.718750,22.699951,24.829590,27.584228,56.450928,52.930664,40.025391,44.489746,44.533203,36.460937</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>0.362672,0.044260,0.114075,0.386163,0.184511,0.790414,0.625047,0.851788,0.549680,0.734909,0.908525,1.420957,0.666777,0.354736,0.919385,0.918561,1.006261,1.119640,2.317495,2.167939,1.632856,1.818446,1.820223,1.484705</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>0.9666676627669962</v>
+      </c>
       <c r="K38" t="inlineStr">
         <is>
           <t>2496.395020,2495.640625,2494.763184,2496.612793,2494.782227,2494.569336,2489.884033,2490.918945,2494.168945,2489.020996,2487.291992,2482.661621,2483.340332,2482.926270,2482.486816,2484.751465,2474.915527,2471.805664,2475.930664,2480.683838,2479.364990,2470.536865,2472.593750,2477.772949</t>
@@ -4180,6 +4236,49 @@
       <c r="M38" t="inlineStr">
         <is>
           <t>2482.208252,2478.471436,2476.667725,2478.608643,2473.532227,2475.010742,2476.002686,2468.168457,2467.199707,2464.728760,2463.898926,2461.085449,2457.239746,2449.722168,2449.278809,2447.433594,2447.493652,2441.840332,2440.574219,2443.204590,2436.406250,2430.743164,2433.809082,2435.290039</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-08-26 01:49:10</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>24</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2457.562012,2454.398926,2453.783691,2454.490479,2452.339355,2451.969727,2453.228027,2450.341553,2451.582031,2452.066162,2450.867676,2451.718750,2452.503174,2450.055420,2451.889893,2450.914062,2452.162109,2449.896729,2449.731934,2451.590088,2451.350098,2447.907715,2448.459473,2448.604736</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>2453.829590,2456.340576,2452.854980,2454.605713,2454.254883,2450.087646,2451.170410,2445.555420,2448.892578,2447.742432,2447.532959,2443.599609,2443.659180,2445.267090,2442.083496,2440.262207,2439.917480,2436.362305,2437.817627,2437.675293,2438.308105,2431.085449,2433.315430,2437.077637</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>2433.542969,2431.251709,2426.603516,2429.870605,2421.490723,2419.047852,2421.336426,2414.795166,2410.319092,2406.565918,2402.412598,2399.760010,2401.291748,2392.320068,2387.899414,2384.705566,2382.896973,2378.166016,2371.891357,2368.449951,2365.841064,2358.267090,2357.737061,2356.547607</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2446.273438,2440.615967,2440.229980,2439.745605,2436.727539,2435.593994,2435.076660,2429.037598,2431.237305,2428.515625,2426.626221,2425.168945,2425.275391,2419.190918,2419.311279,2416.531738,2419.126953,2413.985840,2411.395752,2414.416016,2411.377686,2403.752686,2406.191895,2407.103760</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1899,6 +1899,44 @@
       </c>
       <c r="F39" t="n">
         <v>2448.604736328125</v>
+      </c>
+      <c r="G39" t="n">
+        <v>2497.780029296875</v>
+      </c>
+      <c r="H39" t="n">
+        <v>49.17529296875</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.968759954518207</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.7109629128489695</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-08-27 08:54:15</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>24</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2508.95751953125</v>
       </c>
     </row>
   </sheetData>
@@ -1912,7 +1950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M39"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4266,6 +4304,24 @@
           <t>2457.562012,2454.398926,2453.783691,2454.490479,2452.339355,2451.969727,2453.228027,2450.341553,2451.582031,2452.066162,2450.867676,2451.718750,2452.503174,2450.055420,2451.889893,2450.914062,2452.162109,2449.896729,2449.731934,2451.590088,2451.350098,2447.907715,2448.459473,2448.604736</t>
         </is>
       </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2465.280029,2465.290039,2456.580078,2464.560059,2459.830078,2461.330078,2456.030029,2447.610107,2468.550049,2462.310059,2454.510010,2457.179932,2439.290039,2450.090088,2444.820068,2460.899902,2473.080078,2469.790039,2472.100098,2497.000000,2493.899902,2507.239990,2492.000000,2497.780029</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>7.718017,10.891113,2.796387,10.069580,7.490723,9.360351,2.802002,2.731446,16.968018,10.243897,3.642334,5.461182,13.213135,0.034668,7.069825,9.985840,20.917969,19.893310,22.368164,45.409912,42.549804,59.332275,43.540527,49.175293</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>0.313069,0.441778,0.113833,0.408575,0.304522,0.380296,0.114087,0.111596,0.687368,0.416028,0.148394,0.222254,0.541680,0.001415,0.289176,0.405780,0.845827,0.805466,0.904824,1.818579,1.706155,2.366438,1.747212,1.968760</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>0.7109629128489695</v>
+      </c>
       <c r="K39" t="inlineStr">
         <is>
           <t>2453.829590,2456.340576,2452.854980,2454.605713,2454.254883,2450.087646,2451.170410,2445.555420,2448.892578,2447.742432,2447.532959,2443.599609,2443.659180,2445.267090,2442.083496,2440.262207,2439.917480,2436.362305,2437.817627,2437.675293,2438.308105,2431.085449,2433.315430,2437.077637</t>
@@ -4279,6 +4335,49 @@
       <c r="M39" t="inlineStr">
         <is>
           <t>2446.273438,2440.615967,2440.229980,2439.745605,2436.727539,2435.593994,2435.076660,2429.037598,2431.237305,2428.515625,2426.626221,2425.168945,2425.275391,2419.190918,2419.311279,2416.531738,2419.126953,2413.985840,2411.395752,2414.416016,2411.377686,2403.752686,2406.191895,2407.103760</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-08-27 08:54:15</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>24</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2530.616211,2526.033203,2526.030029,2523.627441,2522.376709,2522.511719,2523.961670,2518.489258,2518.911133,2517.597656,2518.210449,2516.028809,2517.742676,2514.397461,2517.531250,2516.134033,2516.390625,2513.364258,2511.741211,2511.298096,2510.636719,2508.101562,2508.860840,2508.957520</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>2527.009766,2529.677734,2524.148682,2520.871338,2523.164062,2517.486328,2519.026611,2513.061279,2518.643555,2513.957031,2516.876953,2503.975098,2509.480957,2510.920898,2510.243408,2511.573730,2508.113525,2503.524414,2506.584473,2504.048096,2499.487061,2499.109863,2500.604004,2498.987793</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>2496.645752,2491.736816,2489.982422,2493.146240,2487.369141,2486.344727,2489.121094,2482.052246,2476.288574,2471.308594,2469.419922,2467.902344,2470.198975,2459.481934,2457.865234,2455.115723,2452.508789,2449.476562,2441.394043,2436.392090,2435.905029,2427.643066,2428.874512,2427.890869</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>2511.345703,2504.270020,2506.103027,2503.029053,2502.226074,2500.511719,2500.988281,2493.171387,2495.190430,2491.136719,2490.699219,2487.630371,2491.372559,2481.572266,2483.349609,2481.852539,2483.583740,2479.266846,2474.540527,2474.424805,2471.742188,2465.989258,2467.395996,2469.452148</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1937,6 +1937,44 @@
       </c>
       <c r="F40" t="n">
         <v>2508.95751953125</v>
+      </c>
+      <c r="G40" t="n">
+        <v>2488.659912109375</v>
+      </c>
+      <c r="H40" t="n">
+        <v>20.297607421875</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.8156039048610244</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.493315837911688</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-08-28 11:07:11</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>24</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2502.406982421875</v>
       </c>
     </row>
   </sheetData>
@@ -1950,7 +1988,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M40"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4365,6 +4403,24 @@
           <t>2530.616211,2526.033203,2526.030029,2523.627441,2522.376709,2522.511719,2523.961670,2518.489258,2518.911133,2517.597656,2518.210449,2516.028809,2517.742676,2514.397461,2517.531250,2516.134033,2516.390625,2513.364258,2511.741211,2511.298096,2510.636719,2508.101562,2508.860840,2508.957520</t>
         </is>
       </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2534.699951,2503.500000,2501.580078,2495.360107,2497.500000,2517.649902,2522.020020,2522.399902,2518.479980,2507.260010,2499.159912,2508.729980,2504.510010,2515.610107,2511.729980,2516.149902,2512.879883,2492.479980,2490.750000,2486.850098,2494.010010,2503.610107,2496.600098,2488.659912</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>4.083740,22.533203,24.449951,28.267334,24.876709,4.861817,1.941650,3.910644,0.431153,10.337646,19.050537,7.298829,13.232666,1.212646,5.801270,0.015869,3.510742,20.884278,20.991211,24.447998,16.626709,4.491455,12.260742,20.297608</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>0.161113,0.900068,0.977380,1.132796,0.996064,0.193109,0.076988,0.155037,0.017120,0.412309,0.762278,0.290937,0.528353,0.048205,0.230967,0.000631,0.139710,0.837891,0.842767,0.983091,0.666666,0.179399,0.491098,0.815604</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>0.493315837911688</v>
+      </c>
       <c r="K40" t="inlineStr">
         <is>
           <t>2527.009766,2529.677734,2524.148682,2520.871338,2523.164062,2517.486328,2519.026611,2513.061279,2518.643555,2513.957031,2516.876953,2503.975098,2509.480957,2510.920898,2510.243408,2511.573730,2508.113525,2503.524414,2506.584473,2504.048096,2499.487061,2499.109863,2500.604004,2498.987793</t>
@@ -4378,6 +4434,49 @@
       <c r="M40" t="inlineStr">
         <is>
           <t>2511.345703,2504.270020,2506.103027,2503.029053,2502.226074,2500.511719,2500.988281,2493.171387,2495.190430,2491.136719,2490.699219,2487.630371,2491.372559,2481.572266,2483.349609,2481.852539,2483.583740,2479.266846,2474.540527,2474.424805,2471.742188,2465.989258,2467.395996,2469.452148</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-08-28 11:07:11</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>24</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2508.728516,2505.984375,2504.456543,2505.202393,2503.842773,2505.640137,2505.588867,2502.791016,2504.307129,2505.007080,2503.337402,2503.008789,2503.607910,2501.836914,2503.507568,2502.804688,2504.341309,2501.586426,2500.812012,2502.682617,2501.368164,2499.620117,2499.434814,2502.406982</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>2506.850586,2509.818848,2503.773438,2504.195068,2504.840332,2499.554443,2499.204834,2498.207520,2503.314697,2500.130859,2504.065430,2493.035400,2494.496826,2496.678223,2494.765625,2493.408936,2493.207031,2493.450195,2493.978516,2492.015137,2489.992432,2487.555176,2489.849609,2491.238281</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>2493.715820,2492.159668,2489.033691,2493.906738,2486.678955,2487.220215,2488.091309,2482.696533,2478.407715,2475.780518,2470.673828,2472.379639,2472.941406,2465.900391,2462.983887,2459.387207,2458.668945,2454.584473,2449.668701,2449.121094,2446.877441,2441.090576,2440.674072,2443.814941</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2502.270996,2497.006348,2497.824219,2497.536133,2495.661621,2496.366699,2494.881836,2490.277344,2492.388672,2490.067871,2487.348145,2487.187988,2489.413086,2482.665039,2483.999512,2481.482910,2485.350098,2479.432129,2477.459961,2478.817383,2476.777100,2471.777344,2472.886230,2478.583008</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J41"/>
+  <dimension ref="A1:J42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1975,6 +1975,44 @@
       </c>
       <c r="F41" t="n">
         <v>2502.406982421875</v>
+      </c>
+      <c r="G41" t="n">
+        <v>2435.510009765625</v>
+      </c>
+      <c r="H41" t="n">
+        <v>66.89697265625</v>
+      </c>
+      <c r="I41" t="n">
+        <v>2.746733636405283</v>
+      </c>
+      <c r="J41" t="n">
+        <v>2.346408799803377</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-08-29 06:51:46</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>24</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2440.154541015625</v>
       </c>
     </row>
   </sheetData>
@@ -1988,7 +2026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M41"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4464,6 +4502,24 @@
           <t>2508.728516,2505.984375,2504.456543,2505.202393,2503.842773,2505.640137,2505.588867,2502.791016,2504.307129,2505.007080,2503.337402,2503.008789,2503.607910,2501.836914,2503.507568,2502.804688,2504.341309,2501.586426,2500.812012,2502.682617,2501.368164,2499.620117,2499.434814,2502.406982</t>
         </is>
       </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2499.010010,2510.320068,2513.199951,2472.100098,2442.239990,2443.810059,2428.100098,2435.679932,2427.709961,2424.929932,2442.250000,2442.790039,2442.500000,2443.620117,2438.780029,2435.110107,2440.590088,2439.030029,2435.510010,2435.510010,2435.510010,2435.510010,2435.510010,2435.510010</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>9.718506,4.335693,8.743408,33.102295,61.602783,61.830078,77.488769,67.111084,76.597168,80.077148,61.087402,60.218750,61.107910,58.216797,64.727539,67.694581,63.751221,62.556397,65.302002,67.172607,65.858154,64.110107,63.924804,66.896972</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>0.388894,0.172715,0.347899,1.339035,2.522389,2.530069,3.191333,2.755333,3.155120,3.302246,2.501276,2.465163,2.501859,2.382400,2.654095,2.779939,2.612123,2.564806,2.681245,2.758051,2.704081,2.632307,2.624699,2.746734</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>2.346408799803377</v>
+      </c>
       <c r="K41" t="inlineStr">
         <is>
           <t>2506.850586,2509.818848,2503.773438,2504.195068,2504.840332,2499.554443,2499.204834,2498.207520,2503.314697,2500.130859,2504.065430,2493.035400,2494.496826,2496.678223,2494.765625,2493.408936,2493.207031,2493.450195,2493.978516,2492.015137,2489.992432,2487.555176,2489.849609,2491.238281</t>
@@ -4477,6 +4533,49 @@
       <c r="M41" t="inlineStr">
         <is>
           <t>2502.270996,2497.006348,2497.824219,2497.536133,2495.661621,2496.366699,2494.881836,2490.277344,2492.388672,2490.067871,2487.348145,2487.187988,2489.413086,2482.665039,2483.999512,2481.482910,2485.350098,2479.432129,2477.459961,2478.817383,2476.777100,2471.777344,2472.886230,2478.583008</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-08-29 06:51:46</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>24</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2439.812500,2437.097900,2437.010254,2437.812256,2439.206787,2440.126221,2440.407227,2437.970215,2440.854492,2440.963379,2439.309326,2438.701660,2440.593262,2438.205811,2439.805420,2439.754395,2439.728516,2440.014648,2440.086182,2440.586914,2441.781738,2438.725342,2437.823242,2440.154541</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>2440.627930,2443.702148,2437.762939,2438.532471,2440.236572,2435.741699,2436.783447,2437.391602,2440.255859,2435.450684,2438.163818,2432.526855,2430.370850,2438.395264,2433.080566,2427.524658,2431.155273,2433.325195,2434.619141,2430.585693,2432.645752,2427.597168,2427.403076,2428.411621</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>2429.125977,2425.511719,2420.925781,2425.740723,2419.798340,2417.196289,2419.874512,2414.143799,2408.996826,2405.423584,2400.822510,2402.223145,2400.796875,2392.358887,2390.888428,2386.972656,2386.311035,2384.553711,2381.782715,2380.206543,2379.168457,2371.360352,2370.458008,2371.291992</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>2436.588623,2430.490234,2429.808350,2428.723145,2427.516602,2428.809082,2426.878174,2420.948242,2424.437744,2422.039795,2419.840820,2418.486084,2419.825195,2413.145264,2415.301270,2411.760010,2412.974854,2411.875732,2410.676514,2412.002197,2412.109375,2404.857910,2405.393555,2410.969238</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J42"/>
+  <dimension ref="A1:J43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2013,6 +2013,44 @@
       </c>
       <c r="F42" t="n">
         <v>2440.154541015625</v>
+      </c>
+      <c r="G42" t="n">
+        <v>2458.239990234375</v>
+      </c>
+      <c r="H42" t="n">
+        <v>18.08544921875</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.7357072251121294</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.4497978569085002</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-08-30 05:05:29</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>24</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2463.1474609375</v>
       </c>
     </row>
   </sheetData>
@@ -2026,7 +2064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M42"/>
+  <dimension ref="A1:M43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4563,6 +4601,24 @@
           <t>2439.812500,2437.097900,2437.010254,2437.812256,2439.206787,2440.126221,2440.407227,2437.970215,2440.854492,2440.963379,2439.309326,2438.701660,2440.593262,2438.205811,2439.805420,2439.754395,2439.728516,2440.014648,2440.086182,2440.586914,2441.781738,2438.725342,2437.823242,2440.154541</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2436.320068,2434.379883,2435.320068,2434.889893,2435.870117,2434.770020,2435.760010,2448.659912,2444.790039,2450.840088,2450.649902,2452.459961,2453.399902,2452.770020,2451.459961,2452.340088,2457.469971,2459.050049,2456.760010,2455.070068,2457.350098,2456.159912,2458.239990,2458.239990</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>3.492432,2.718017,1.690186,2.922363,3.336670,5.356201,4.647217,10.689697,3.935547,9.876709,11.340576,13.758301,12.806640,14.564209,11.654541,12.585693,17.741455,19.035401,16.673828,14.483154,15.568360,17.434570,20.416748,18.085449</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>0.143349,0.111651,0.069403,0.120020,0.136981,0.219988,0.190791,0.436553,0.160977,0.402993,0.462758,0.561000,0.521996,0.593786,0.475412,0.513212,0.721940,0.774096,0.678692,0.589928,0.633543,0.709830,0.830543,0.735707</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>0.4497978569085002</v>
+      </c>
       <c r="K42" t="inlineStr">
         <is>
           <t>2440.627930,2443.702148,2437.762939,2438.532471,2440.236572,2435.741699,2436.783447,2437.391602,2440.255859,2435.450684,2438.163818,2432.526855,2430.370850,2438.395264,2433.080566,2427.524658,2431.155273,2433.325195,2434.619141,2430.585693,2432.645752,2427.597168,2427.403076,2428.411621</t>
@@ -4576,6 +4632,49 @@
       <c r="M42" t="inlineStr">
         <is>
           <t>2436.588623,2430.490234,2429.808350,2428.723145,2427.516602,2428.809082,2426.878174,2420.948242,2424.437744,2422.039795,2419.840820,2418.486084,2419.825195,2413.145264,2415.301270,2411.760010,2412.974854,2411.875732,2410.676514,2412.002197,2412.109375,2404.857910,2405.393555,2410.969238</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-08-30 05:05:29</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>24</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2461.908691,2460.880371,2460.171875,2461.449707,2461.551758,2463.351562,2462.511719,2460.503418,2464.169434,2462.984863,2462.418945,2462.742432,2464.437988,2460.527100,2463.194580,2463.355469,2464.224121,2462.525879,2464.377930,2462.495605,2463.992188,2461.872559,2461.871582,2463.147461</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>2458.998047,2460.024658,2461.307617,2462.438232,2466.737305,2455.394043,2459.194824,2464.929199,2462.858887,2458.598633,2457.480713,2455.007812,2455.270264,2459.470947,2459.280762,2454.821777,2457.534180,2455.055420,2457.839844,2456.198242,2456.182617,2452.300781,2452.904297,2450.220215</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>2451.819580,2450.244629,2446.350098,2453.749023,2447.301758,2446.311279,2444.607178,2440.489746,2436.247559,2431.570801,2426.463867,2429.031738,2425.940430,2420.863281,2419.249512,2416.446045,2414.924316,2410.014648,2407.790527,2402.008789,2402.730469,2396.503418,2397.088135,2393.603760</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2459.367676,2456.396973,2455.694336,2455.728027,2453.987549,2454.270996,2451.811523,2448.212891,2451.601318,2447.547119,2445.520020,2444.625488,2447.759766,2440.326416,2442.061523,2440.965332,2442.893066,2438.971191,2438.744385,2437.919922,2439.206787,2432.973145,2432.746338,2438.364746</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J43"/>
+  <dimension ref="A1:J44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2051,6 +2051,44 @@
       </c>
       <c r="F43" t="n">
         <v>2463.1474609375</v>
+      </c>
+      <c r="G43" t="n">
+        <v>2421.77001953125</v>
+      </c>
+      <c r="H43" t="n">
+        <v>41.37744140625</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1.70856196387545</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.086446129010805</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-08-31 05:13:02</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>24</v>
+      </c>
+      <c r="F44" t="n">
+        <v>2438.376953125</v>
       </c>
     </row>
   </sheetData>
@@ -2064,7 +2102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M43"/>
+  <dimension ref="A1:M44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4662,6 +4700,24 @@
           <t>2461.908691,2460.880371,2460.171875,2461.449707,2461.551758,2463.351562,2462.511719,2460.503418,2464.169434,2462.984863,2462.418945,2462.742432,2464.437988,2460.527100,2463.194580,2463.355469,2464.224121,2462.525879,2464.377930,2462.495605,2463.992188,2461.872559,2461.871582,2463.147461</t>
         </is>
       </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2461.189941,2455.229980,2456.959961,2453.229980,2459.300049,2460.010010,2469.000000,2475.419922,2477.030029,2481.020020,2529.100098,2505.489990,2510.649902,2503.590088,2490.610107,2481.709961,2470.679932,2417.810059,2428.360107,2412.560059,2407.449951,2420.810059,2417.159912,2421.770020</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>0.718750,5.650391,3.211914,8.219727,2.251709,3.341552,6.488281,14.916504,12.860595,18.035157,66.681153,42.747558,46.211914,43.062988,27.415527,18.354492,6.455811,44.715820,36.017823,49.935546,56.542237,41.062500,44.711670,41.377441</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>0.029203,0.230137,0.130727,0.335057,0.091559,0.135835,0.262790,0.602585,0.519194,0.726925,2.636556,1.706156,1.840636,1.720049,1.100755,0.739591,0.261297,1.849435,1.483216,2.069816,2.348636,1.696230,1.849761,1.708562</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>1.086446129010805</v>
+      </c>
       <c r="K43" t="inlineStr">
         <is>
           <t>2458.998047,2460.024658,2461.307617,2462.438232,2466.737305,2455.394043,2459.194824,2464.929199,2462.858887,2458.598633,2457.480713,2455.007812,2455.270264,2459.470947,2459.280762,2454.821777,2457.534180,2455.055420,2457.839844,2456.198242,2456.182617,2452.300781,2452.904297,2450.220215</t>
@@ -4675,6 +4731,49 @@
       <c r="M43" t="inlineStr">
         <is>
           <t>2459.367676,2456.396973,2455.694336,2455.728027,2453.987549,2454.270996,2451.811523,2448.212891,2451.601318,2447.547119,2445.520020,2444.625488,2447.759766,2440.326416,2442.061523,2440.965332,2442.893066,2438.971191,2438.744385,2437.919922,2439.206787,2432.973145,2432.746338,2438.364746</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-08-31 05:13:02</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>24</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2425.755859,2426.742188,2425.864014,2429.300293,2429.406494,2432.858154,2433.516602,2432.164795,2433.886963,2436.418701,2435.467285,2436.634033,2437.569824,2435.438965,2437.250000,2437.750488,2437.303467,2436.603271,2438.467773,2437.946533,2439.135010,2436.867432,2436.996582,2438.376953</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>2426.730957,2431.011719,2429.221924,2435.419189,2436.428223,2428.387695,2434.684082,2436.547607,2435.272949,2434.648926,2432.932617,2435.231201,2429.590088,2436.934814,2430.015869,2430.024902,2430.814941,2428.500244,2432.548340,2426.999512,2432.303223,2422.644531,2429.244141,2427.191162</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>2411.562500,2410.529541,2404.750244,2412.119629,2404.503906,2405.891602,2405.153809,2400.953369,2394.696533,2393.559082,2389.409668,2390.360107,2387.733887,2382.705811,2378.518555,2375.662598,2372.783203,2368.486816,2365.031494,2360.239258,2359.201416,2352.917480,2352.351318,2349.743652</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2420.650879,2417.179199,2415.145264,2417.384277,2415.186035,2416.576660,2415.302246,2411.933838,2413.980957,2412.784180,2411.343750,2410.978516,2411.753418,2405.615723,2406.895264,2405.005859,2404.679443,2402.104004,2402.298340,2403.267578,2402.614746,2396.213867,2396.339844,2400.709473</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J44"/>
+  <dimension ref="A1:J45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2089,6 +2089,44 @@
       </c>
       <c r="F44" t="n">
         <v>2438.376953125</v>
+      </c>
+      <c r="G44" t="n">
+        <v>2471.489990234375</v>
+      </c>
+      <c r="H44" t="n">
+        <v>33.113037109375</v>
+      </c>
+      <c r="I44" t="n">
+        <v>1.339800575370117</v>
+      </c>
+      <c r="J44" t="n">
+        <v>1.13085937390927</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-09-01 04:48:49</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>24</v>
+      </c>
+      <c r="F45" t="n">
+        <v>2470.173095703125</v>
       </c>
     </row>
   </sheetData>
@@ -2102,7 +2140,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M44"/>
+  <dimension ref="A1:M45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4761,6 +4799,24 @@
           <t>2425.755859,2426.742188,2425.864014,2429.300293,2429.406494,2432.858154,2433.516602,2432.164795,2433.886963,2436.418701,2435.467285,2436.634033,2437.569824,2435.438965,2437.250000,2437.750488,2437.303467,2436.603271,2438.467773,2437.946533,2439.135010,2436.867432,2436.996582,2438.376953</t>
         </is>
       </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2438.340088,2440.459961,2446.110107,2446.139893,2454.679932,2445.750000,2450.820068,2439.370117,2466.290039,2467.219971,2468.870117,2475.040039,2477.370117,2481.600098,2472.479980,2478.090088,2468.919922,2467.290039,2471.219971,2462.290039,2464.330078,2471.610107,2471.489990,2471.489990</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>12.584229,13.717773,20.246093,16.839600,25.273438,12.891846,17.303466,7.205322,32.403076,30.801270,33.402832,38.406006,39.800293,46.161133,35.229980,40.339600,31.616455,30.686768,32.752198,24.343506,25.195068,34.742675,34.493408,33.113037</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>0.516098,0.562098,0.827685,0.688415,1.029602,0.527112,0.706028,0.295376,1.313839,1.248420,1.352960,1.551733,1.606554,1.860136,1.424884,1.627850,1.280578,1.243744,1.325345,0.988653,1.022390,1.405670,1.395652,1.339801</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>1.13085937390927</v>
+      </c>
       <c r="K44" t="inlineStr">
         <is>
           <t>2426.730957,2431.011719,2429.221924,2435.419189,2436.428223,2428.387695,2434.684082,2436.547607,2435.272949,2434.648926,2432.932617,2435.231201,2429.590088,2436.934814,2430.015869,2430.024902,2430.814941,2428.500244,2432.548340,2426.999512,2432.303223,2422.644531,2429.244141,2427.191162</t>
@@ -4774,6 +4830,49 @@
       <c r="M44" t="inlineStr">
         <is>
           <t>2420.650879,2417.179199,2415.145264,2417.384277,2415.186035,2416.576660,2415.302246,2411.933838,2413.980957,2412.784180,2411.343750,2410.978516,2411.753418,2405.615723,2406.895264,2405.005859,2404.679443,2402.104004,2402.298340,2403.267578,2402.614746,2396.213867,2396.339844,2400.709473</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-09-01 04:48:49</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>24</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2473.996826,2473.575684,2473.470703,2474.022461,2475.907715,2477.111328,2475.675293,2472.803223,2474.557373,2476.478516,2474.035156,2473.895996,2475.008545,2473.580078,2475.029053,2474.294922,2474.488770,2474.588623,2473.442139,2474.089355,2473.959961,2470.748535,2469.587402,2470.173096</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>2474.398193,2478.762207,2476.305908,2474.471924,2482.331055,2471.946533,2475.811523,2475.128906,2470.906250,2472.400879,2469.072266,2470.265381,2470.937988,2473.160156,2469.376709,2463.739014,2471.933838,2469.417725,2468.565674,2464.661621,2466.197754,2452.640869,2460.098389,2461.050781</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>2460.711182,2459.626221,2457.201904,2460.994629,2457.565186,2458.195312,2455.492676,2448.885498,2444.808350,2443.951660,2440.867676,2440.491699,2440.069824,2433.468262,2430.534424,2426.660400,2425.842041,2424.253174,2418.486328,2414.729004,2415.897217,2408.294922,2407.994629,2405.076416</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2467.887695,2464.761230,2464.895996,2464.135986,2465.887939,2464.865479,2461.986328,2457.122803,2458.756104,2457.930176,2457.166016,2456.310059,2457.596680,2451.645508,2454.520508,2452.063965,2453.230469,2452.257568,2449.761963,2450.712158,2450.404297,2443.895020,2444.299805,2446.932129</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J45"/>
+  <dimension ref="A1:J46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2127,6 +2127,44 @@
       </c>
       <c r="F45" t="n">
         <v>2470.173095703125</v>
+      </c>
+      <c r="G45" t="n">
+        <v>2407.31005859375</v>
+      </c>
+      <c r="H45" t="n">
+        <v>62.863037109375</v>
+      </c>
+      <c r="I45" t="n">
+        <v>2.61133944441278</v>
+      </c>
+      <c r="J45" t="n">
+        <v>1.710648293359181</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-09-02 04:10:00</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>24</v>
+      </c>
+      <c r="F46" t="n">
+        <v>2422.39599609375</v>
       </c>
     </row>
   </sheetData>
@@ -2140,7 +2178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M45"/>
+  <dimension ref="A1:M46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4860,6 +4898,24 @@
           <t>2473.996826,2473.575684,2473.470703,2474.022461,2475.907715,2477.111328,2475.675293,2472.803223,2474.557373,2476.478516,2474.035156,2473.895996,2475.008545,2473.580078,2475.029053,2474.294922,2474.488770,2474.588623,2473.442139,2474.089355,2473.959961,2470.748535,2469.587402,2470.173096</t>
         </is>
       </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2484.070068,2471.139893,2472.020020,2447.500000,2451.610107,2456.239990,2458.320068,2445.850098,2443.750000,2448.360107,2448.020020,2431.919922,2417.709961,2412.520020,2417.800049,2419.939941,2414.360107,2411.739990,2412.949951,2408.000000,2398.179932,2408.320068,2413.189941,2407.310059</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>10.073242,2.435791,1.450683,26.522461,24.297608,20.871338,17.355225,26.953125,30.807373,28.118409,26.015136,41.976074,57.298584,61.060058,57.229004,54.354981,60.128663,62.848633,60.492188,66.089355,75.780029,62.428467,56.397461,62.863037</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>0.405514,0.098570,0.058684,1.083655,0.991088,0.849727,0.705979,1.101994,1.260660,1.148459,1.062701,1.726047,2.369953,2.530966,2.366987,2.246129,2.490460,2.605946,2.506981,2.744575,3.159898,2.592200,2.337050,2.611339</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>1.710648293359181</v>
+      </c>
       <c r="K45" t="inlineStr">
         <is>
           <t>2474.398193,2478.762207,2476.305908,2474.471924,2482.331055,2471.946533,2475.811523,2475.128906,2470.906250,2472.400879,2469.072266,2470.265381,2470.937988,2473.160156,2469.376709,2463.739014,2471.933838,2469.417725,2468.565674,2464.661621,2466.197754,2452.640869,2460.098389,2461.050781</t>
@@ -4873,6 +4929,49 @@
       <c r="M45" t="inlineStr">
         <is>
           <t>2467.887695,2464.761230,2464.895996,2464.135986,2465.887939,2464.865479,2461.986328,2457.122803,2458.756104,2457.930176,2457.166016,2456.310059,2457.596680,2451.645508,2454.520508,2452.063965,2453.230469,2452.257568,2449.761963,2450.712158,2450.404297,2443.895020,2444.299805,2446.932129</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-09-02 04:10:00</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>24</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2406.767334,2407.293945,2406.877441,2408.336182,2407.639160,2411.612793,2410.832031,2409.273438,2411.447266,2414.721191,2415.687500,2417.261475,2417.506348,2417.885254,2418.440918,2419.526367,2419.640137,2421.734619,2422.794189,2421.676514,2423.505127,2422.080322,2421.453613,2422.395996</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>2402.361572,2410.842773,2408.058350,2411.992676,2409.577393,2404.526367,2413.096680,2408.494873,2404.936523,2406.088623,2406.734131,2409.270264,2405.681152,2411.117676,2407.719727,2407.074219,2410.817383,2406.794434,2408.289062,2407.645264,2409.244385,2399.488770,2406.670166,2404.224121</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>2388.440918,2387.638428,2383.505371,2388.928223,2382.901123,2386.541992,2386.678711,2382.596680,2378.879883,2377.829346,2377.778320,2378.308105,2374.157471,2367.838379,2364.159668,2361.436035,2358.863281,2357.748047,2349.922607,2345.431396,2341.925537,2336.782471,2334.768799,2328.084473</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2398.295166,2395.700684,2393.846924,2394.527832,2392.907471,2397.209229,2396.222656,2392.209961,2395.705078,2396.345215,2397.902100,2396.587646,2394.675293,2391.929199,2393.593018,2392.219238,2392.025635,2392.077148,2390.053223,2391.325684,2388.624512,2383.856934,2382.219727,2386.190918</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J46"/>
+  <dimension ref="A1:J47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2165,6 +2165,44 @@
       </c>
       <c r="F46" t="n">
         <v>2422.39599609375</v>
+      </c>
+      <c r="G46" t="n">
+        <v>2404.510009765625</v>
+      </c>
+      <c r="H46" t="n">
+        <v>17.885986328125</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.7438516061685434</v>
+      </c>
+      <c r="J46" t="n">
+        <v>1.07969439075947</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-09-03 04:06:58</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>24</v>
+      </c>
+      <c r="F47" t="n">
+        <v>2398.61962890625</v>
       </c>
     </row>
   </sheetData>
@@ -2178,7 +2216,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M46"/>
+  <dimension ref="A1:M47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4959,6 +4997,24 @@
           <t>2406.767334,2407.293945,2406.877441,2408.336182,2407.639160,2411.612793,2410.832031,2409.273438,2411.447266,2414.721191,2415.687500,2417.261475,2417.506348,2417.885254,2418.440918,2419.526367,2419.640137,2421.734619,2422.794189,2421.676514,2423.505127,2422.080322,2421.453613,2422.395996</t>
         </is>
       </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2421.409912,2419.500000,2416.530029,2391.840088,2375.540039,2371.250000,2380.500000,2376.570068,2401.719971,2393.500000,2390.159912,2384.790039,2392.540039,2394.050049,2391.909912,2392.870117,2389.649902,2378.729980,2390.830078,2379.100098,2385.709961,2404.949951,2402.300049,2404.510010</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>14.642578,12.206055,9.652588,16.496094,32.099121,40.362793,30.332031,32.703370,9.727295,21.221191,25.527588,32.471436,24.966309,23.835205,26.531006,26.656250,29.990235,43.004639,31.964111,42.576416,37.795166,17.130371,19.153564,17.885986</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>0.604713,0.504487,0.399440,0.689682,1.351235,1.702174,1.274187,1.376074,0.405014,0.886618,1.068028,1.361606,1.043506,0.995602,1.109198,1.113986,1.255005,1.807882,1.336946,1.789602,1.584231,0.712296,0.797301,0.743852</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>1.07969439075947</v>
+      </c>
       <c r="K46" t="inlineStr">
         <is>
           <t>2402.361572,2410.842773,2408.058350,2411.992676,2409.577393,2404.526367,2413.096680,2408.494873,2404.936523,2406.088623,2406.734131,2409.270264,2405.681152,2411.117676,2407.719727,2407.074219,2410.817383,2406.794434,2408.289062,2407.645264,2409.244385,2399.488770,2406.670166,2404.224121</t>
@@ -4972,6 +5028,49 @@
       <c r="M46" t="inlineStr">
         <is>
           <t>2398.295166,2395.700684,2393.846924,2394.527832,2392.907471,2397.209229,2396.222656,2392.209961,2395.705078,2396.345215,2397.902100,2396.587646,2394.675293,2391.929199,2393.593018,2392.219238,2392.025635,2392.077148,2390.053223,2391.325684,2388.624512,2383.856934,2382.219727,2386.190918</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-09-03 04:06:58</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>24</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2403.990723,2405.592285,2404.636230,2406.045166,2404.804199,2406.197266,2404.897949,2403.768311,2403.349609,2403.725098,2402.011230,2403.072754,2402.715820,2401.281738,2402.152344,2400.967285,2400.703613,2400.104980,2401.208008,2398.665527,2399.399170,2399.944336,2396.833984,2398.619629</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>2402.632080,2407.800537,2405.116211,2409.494141,2406.512207,2405.435547,2402.555176,2404.417725,2401.089844,2405.082031,2396.544189,2398.921387,2399.193115,2399.065918,2395.903564,2393.127930,2390.580566,2395.864258,2392.760742,2386.311035,2391.713867,2387.281738,2387.124756,2387.603760</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>2386.659424,2386.941895,2381.769775,2386.368896,2379.763184,2379.983154,2378.407471,2376.030273,2367.201660,2362.434570,2357.737793,2359.041992,2352.815430,2350.058594,2347.644531,2341.792725,2341.110107,2336.936035,2332.729004,2325.239746,2323.062500,2320.001221,2314.984131,2312.406982</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>2396.738770,2393.634277,2393.335449,2391.837158,2390.500977,2389.201172,2386.410400,2383.901855,2385.549561,2381.421143,2378.010254,2375.589355,2375.650879,2372.987061,2373.916504,2370.797852,2370.974609,2366.553711,2366.941162,2365.296875,2363.608643,2359.677734,2357.566895,2361.445557</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J47"/>
+  <dimension ref="A1:J48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2203,6 +2203,44 @@
       </c>
       <c r="F47" t="n">
         <v>2398.61962890625</v>
+      </c>
+      <c r="G47" t="n">
+        <v>2503.68994140625</v>
+      </c>
+      <c r="H47" t="n">
+        <v>105.0703125</v>
+      </c>
+      <c r="I47" t="n">
+        <v>4.196618389615171</v>
+      </c>
+      <c r="J47" t="n">
+        <v>2.746508349451428</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-09-04 04:12:37</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>24</v>
+      </c>
+      <c r="F48" t="n">
+        <v>2490.22119140625</v>
       </c>
     </row>
   </sheetData>
@@ -2216,7 +2254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M47"/>
+  <dimension ref="A1:M48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5058,6 +5096,24 @@
           <t>2403.990723,2405.592285,2404.636230,2406.045166,2404.804199,2406.197266,2404.897949,2403.768311,2403.349609,2403.725098,2402.011230,2403.072754,2402.715820,2401.281738,2402.152344,2400.967285,2400.703613,2400.104980,2401.208008,2398.665527,2399.399170,2399.944336,2396.833984,2398.619629</t>
         </is>
       </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2403.530029,2407.429932,2397.340088,2402.320068,2392.479980,2395.639893,2405.770020,2422.409912,2429.389893,2489.500000,2516.979980,2494.129883,2500.459961,2513.219971,2518.260010,2505.300049,2511.560059,2496.939941,2507.739990,2501.310059,2506.639893,2507.649902,2504.840088,2503.689941</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.460694,1.837647,7.296142,3.725098,12.324219,10.557373,0.872071,18.641601,26.040284,85.774902,114.968750,91.057129,97.744141,111.938233,116.107666,104.332764,110.856446,96.834961,106.531982,102.644532,107.240723,107.705566,108.006104,105.070312</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.019167,0.076332,0.304343,0.155063,0.515123,0.440691,0.036249,0.769548,1.071886,3.445467,4.567726,3.650858,3.909046,4.453977,4.610631,4.164482,4.413848,3.878145,4.248127,4.103631,4.278266,4.295080,4.311896,4.196618</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>2.746508349451428</v>
+      </c>
       <c r="K47" t="inlineStr">
         <is>
           <t>2402.632080,2407.800537,2405.116211,2409.494141,2406.512207,2405.435547,2402.555176,2404.417725,2401.089844,2405.082031,2396.544189,2398.921387,2399.193115,2399.065918,2395.903564,2393.127930,2390.580566,2395.864258,2392.760742,2386.311035,2391.713867,2387.281738,2387.124756,2387.603760</t>
@@ -5071,6 +5127,49 @@
       <c r="M47" t="inlineStr">
         <is>
           <t>2396.738770,2393.634277,2393.335449,2391.837158,2390.500977,2389.201172,2386.410400,2383.901855,2385.549561,2381.421143,2378.010254,2375.589355,2375.650879,2372.987061,2373.916504,2370.797852,2370.974609,2366.553711,2366.941162,2365.296875,2363.608643,2359.677734,2357.566895,2361.445557</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-09-04 04:12:37</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>24</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2507.278320,2506.214355,2504.864746,2505.703369,2503.429932,2503.071289,2502.163574,2501.053223,2501.212891,2499.541260,2501.000488,2500.817627,2501.155029,2498.274902,2499.911377,2497.044678,2496.723633,2494.480957,2493.294922,2492.848877,2492.311035,2492.649658,2490.699707,2490.221191</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>2503.085938,2504.232666,2504.133545,2505.341064,2501.356445,2495.369141,2494.616943,2499.250000,2490.505615,2492.293945,2490.761963,2489.403809,2487.666016,2490.833740,2485.416992,2485.071777,2482.479492,2474.859375,2472.409668,2474.734375,2476.442139,2473.725830,2472.070557,2467.932373</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>2487.290771,2485.025879,2478.916260,2480.865723,2472.323975,2469.752441,2463.398926,2460.890625,2455.730469,2450.630371,2446.655762,2443.955566,2439.949219,2435.578613,2430.508545,2422.377197,2419.160645,2413.182861,2402.045898,2396.591797,2393.744629,2392.932129,2385.877197,2381.048340</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>2499.707031,2493.979492,2491.822021,2492.384766,2487.110352,2483.149414,2480.230469,2478.997070,2480.457520,2476.612793,2475.712891,2472.036377,2472.417969,2466.933594,2466.005859,2460.356934,2460.734619,2454.777100,2450.696289,2450.158447,2448.055664,2441.787842,2441.215576,2442.415283</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J48"/>
+  <dimension ref="A1:J49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2241,6 +2241,44 @@
       </c>
       <c r="F48" t="n">
         <v>2490.22119140625</v>
+      </c>
+      <c r="G48" t="n">
+        <v>2452.2900390625</v>
+      </c>
+      <c r="H48" t="n">
+        <v>37.93115234375</v>
+      </c>
+      <c r="I48" t="n">
+        <v>1.546764523753109</v>
+      </c>
+      <c r="J48" t="n">
+        <v>1.434353009733466</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-09-05 04:08:34</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>24</v>
+      </c>
+      <c r="F49" t="n">
+        <v>2452.212890625</v>
       </c>
     </row>
   </sheetData>
@@ -2254,7 +2292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M48"/>
+  <dimension ref="A1:M49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5157,6 +5195,24 @@
           <t>2507.278320,2506.214355,2504.864746,2505.703369,2503.429932,2503.071289,2502.163574,2501.053223,2501.212891,2499.541260,2501.000488,2500.817627,2501.155029,2498.274902,2499.911377,2497.044678,2496.723633,2494.480957,2493.294922,2492.848877,2492.311035,2492.649658,2490.699707,2490.221191</t>
         </is>
       </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2508.949951,2507.719971,2504.179932,2526.879883,2520.689941,2526.139893,2522.979980,2451.419922,2451.860107,2440.169922,2452.080078,2460.469971,2445.469971,2450.679932,2456.479980,2451.489990,2452.429932,2451.500000,2456.070068,2452.340088,2452.159912,2453.300049,2452.840088,2452.290039</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>1.671631,1.505616,0.684814,21.176514,17.260009,23.068604,20.816406,49.633301,49.352784,59.371338,48.920410,40.347656,55.685058,47.594970,43.431397,45.554688,44.293701,42.980957,37.224854,40.508789,40.151123,39.349609,37.859619,37.931152</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.066627,0.060039,0.027347,0.838050,0.684734,0.913196,0.825072,2.024676,2.012871,2.433082,1.995058,1.639835,2.277070,1.942113,1.768034,1.858245,1.806115,1.753251,1.515627,1.651842,1.637378,1.603946,1.543501,1.546765</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>1.434353009733466</v>
+      </c>
       <c r="K48" t="inlineStr">
         <is>
           <t>2503.085938,2504.232666,2504.133545,2505.341064,2501.356445,2495.369141,2494.616943,2499.250000,2490.505615,2492.293945,2490.761963,2489.403809,2487.666016,2490.833740,2485.416992,2485.071777,2482.479492,2474.859375,2472.409668,2474.734375,2476.442139,2473.725830,2472.070557,2467.932373</t>
@@ -5170,6 +5226,49 @@
       <c r="M48" t="inlineStr">
         <is>
           <t>2499.707031,2493.979492,2491.822021,2492.384766,2487.110352,2483.149414,2480.230469,2478.997070,2480.457520,2476.612793,2475.712891,2472.036377,2472.417969,2466.933594,2466.005859,2460.356934,2460.734619,2454.777100,2450.696289,2450.158447,2448.055664,2441.787842,2441.215576,2442.415283</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-09-05 04:08:34</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>24</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2452.895020,2453.353516,2453.846680,2455.717285,2454.727539,2455.044434,2454.656982,2453.685059,2454.144043,2453.647217,2453.994629,2454.065918,2453.604248,2452.054932,2455.724854,2456.090820,2454.344238,2454.681641,2456.034424,2455.221924,2455.957275,2454.458252,2451.933838,2452.212891</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>2448.858887,2458.211182,2451.535645,2456.198975,2456.087402,2450.362793,2452.315918,2448.941406,2448.971680,2451.489014,2447.640137,2447.088867,2443.946045,2450.312744,2444.246582,2445.255859,2446.221191,2445.619873,2449.695801,2443.621338,2442.968506,2442.250977,2438.057617,2437.615234</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>2437.776123,2438.449219,2435.649414,2440.949707,2434.017334,2431.944824,2428.430664,2425.058838,2416.791016,2411.915283,2407.338867,2408.824463,2402.417969,2398.309814,2397.376709,2393.397949,2390.083984,2388.418457,2383.332520,2379.102295,2378.173340,2375.763672,2371.557617,2366.639404</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>2446.358887,2442.907715,2444.829834,2445.146484,2443.569824,2440.919678,2437.406738,2434.195312,2435.306152,2431.536133,2428.896240,2426.403564,2425.627441,2421.925781,2425.277344,2424.098633,2421.695312,2419.564453,2419.810059,2419.951416,2419.174561,2412.121094,2411.859375,2412.384277</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:J50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2279,6 +2279,44 @@
       </c>
       <c r="F49" t="n">
         <v>2452.212890625</v>
+      </c>
+      <c r="G49" t="n">
+        <v>2507.0400390625</v>
+      </c>
+      <c r="H49" t="n">
+        <v>54.8271484375</v>
+      </c>
+      <c r="I49" t="n">
+        <v>2.186927515445762</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0.8029582959768516</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-09-06 04:16:25</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>24</v>
+      </c>
+      <c r="F50" t="n">
+        <v>2491.14111328125</v>
       </c>
     </row>
   </sheetData>
@@ -2292,7 +2330,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M49"/>
+  <dimension ref="A1:M50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5256,6 +5294,24 @@
           <t>2452.895020,2453.353516,2453.846680,2455.717285,2454.727539,2455.044434,2454.656982,2453.685059,2454.144043,2453.647217,2453.994629,2454.065918,2453.604248,2452.054932,2455.724854,2456.090820,2454.344238,2454.681641,2456.034424,2455.221924,2455.957275,2454.458252,2451.933838,2452.212891</t>
         </is>
       </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2451.120117,2453.739990,2457.820068,2456.919922,2458.439941,2454.219971,2453.699951,2458.820068,2454.520020,2457.399902,2460.409912,2471.229980,2481.310059,2480.850098,2477.679932,2477.860107,2488.879883,2481.020020,2482.830078,2490.399902,2505.780029,2503.479980,2509.659912,2507.040039</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>1.774903,0.386474,3.973388,1.202637,3.712402,0.824463,0.957031,5.135009,0.375977,3.752685,6.415283,17.164062,27.705811,28.795166,21.955078,21.769287,34.535645,26.338379,26.795654,35.177978,49.822754,49.021728,57.726074,54.827148</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.072412,0.015750,0.161663,0.048949,0.151006,0.033594,0.039004,0.208840,0.015318,0.152710,0.260740,0.694555,1.116580,1.160698,0.886114,0.878552,1.387598,1.061595,1.079238,1.412543,1.988313,1.958143,2.300155,2.186928</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>0.8029582959768516</v>
+      </c>
       <c r="K49" t="inlineStr">
         <is>
           <t>2448.858887,2458.211182,2451.535645,2456.198975,2456.087402,2450.362793,2452.315918,2448.941406,2448.971680,2451.489014,2447.640137,2447.088867,2443.946045,2450.312744,2444.246582,2445.255859,2446.221191,2445.619873,2449.695801,2443.621338,2442.968506,2442.250977,2438.057617,2437.615234</t>
@@ -5269,6 +5325,49 @@
       <c r="M49" t="inlineStr">
         <is>
           <t>2446.358887,2442.907715,2444.829834,2445.146484,2443.569824,2440.919678,2437.406738,2434.195312,2435.306152,2431.536133,2428.896240,2426.403564,2425.627441,2421.925781,2425.277344,2424.098633,2421.695312,2419.564453,2419.810059,2419.951416,2419.174561,2412.121094,2411.859375,2412.384277</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-09-06 04:16:25</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>24</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2508.366699,2507.529541,2506.699219,2507.708984,2505.562256,2505.293457,2504.042969,2502.581787,2502.692383,2501.721191,2501.129883,2500.958984,2498.899658,2497.824707,2498.919434,2498.047363,2496.691895,2495.089355,2494.555664,2493.912598,2493.363037,2492.367920,2490.637695,2491.141113</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>2503.470215,2504.170898,2507.165039,2504.430664,2506.288330,2499.389160,2497.943848,2502.316162,2496.570068,2496.332275,2494.352051,2490.085938,2488.840576,2491.750977,2487.650879,2489.239014,2487.645996,2482.748047,2484.810059,2482.773193,2483.901855,2482.362305,2477.956543,2478.394287</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>2492.914551,2491.682617,2485.438965,2487.649658,2480.071777,2476.869141,2470.839600,2466.826416,2459.957764,2455.675781,2449.758545,2449.852051,2443.593994,2443.121582,2439.341797,2437.073975,2433.948975,2430.854004,2422.552979,2418.648438,2417.683105,2415.314941,2412.676270,2410.038086</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>2500.953369,2497.574707,2495.789795,2495.495605,2491.935059,2487.058838,2483.434082,2479.474121,2481.014404,2477.288818,2472.567383,2470.802002,2469.567383,2465.570312,2465.290039,2465.180664,2463.019043,2459.647461,2456.405273,2456.039551,2454.727051,2449.574219,2448.810547,2451.255615</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J50"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2317,6 +2317,44 @@
       </c>
       <c r="F50" t="n">
         <v>2491.14111328125</v>
+      </c>
+      <c r="G50" t="n">
+        <v>2497.4599609375</v>
+      </c>
+      <c r="H50" t="n">
+        <v>6.31884765625</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.2530109693481541</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0.3941787082188898</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-09-07 04:15:45</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>24</v>
+      </c>
+      <c r="F51" t="n">
+        <v>2488.23974609375</v>
       </c>
     </row>
   </sheetData>
@@ -2330,7 +2368,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M50"/>
+  <dimension ref="A1:M51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5355,6 +5393,24 @@
           <t>2508.366699,2507.529541,2506.699219,2507.708984,2505.562256,2505.293457,2504.042969,2502.581787,2502.692383,2501.721191,2501.129883,2500.958984,2498.899658,2497.824707,2498.919434,2498.047363,2496.691895,2495.089355,2494.555664,2493.912598,2493.363037,2492.367920,2490.637695,2491.141113</t>
         </is>
       </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2513.620117,2506.110107,2497.520020,2495.830078,2499.310059,2501.969971,2502.239990,2500.419922,2494.750000,2478.530029,2479.850098,2484.459961,2491.270020,2494.300049,2490.500000,2499.270020,2507.379883,2507.959961,2514.860107,2512.689941,2503.699951,2511.659912,2497.399902,2497.459961</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>5.253418,1.419434,9.179199,11.878906,6.252197,3.323486,1.802979,2.161865,7.942383,23.191162,21.279785,16.499023,7.629638,3.524658,8.419434,1.222657,10.687988,12.870606,20.304443,18.777343,10.336914,19.291992,6.762207,6.318848</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.208998,0.056639,0.367533,0.475950,0.250157,0.132835,0.072055,0.086460,0.318364,0.935682,0.858108,0.664089,0.306255,0.141309,0.338062,0.048921,0.426261,0.513190,0.807379,0.747300,0.412866,0.768097,0.270770,0.253011</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>0.3941787082188898</v>
+      </c>
       <c r="K50" t="inlineStr">
         <is>
           <t>2503.470215,2504.170898,2507.165039,2504.430664,2506.288330,2499.389160,2497.943848,2502.316162,2496.570068,2496.332275,2494.352051,2490.085938,2488.840576,2491.750977,2487.650879,2489.239014,2487.645996,2482.748047,2484.810059,2482.773193,2483.901855,2482.362305,2477.956543,2478.394287</t>
@@ -5368,6 +5424,49 @@
       <c r="M50" t="inlineStr">
         <is>
           <t>2500.953369,2497.574707,2495.789795,2495.495605,2491.935059,2487.058838,2483.434082,2479.474121,2481.014404,2477.288818,2472.567383,2470.802002,2469.567383,2465.570312,2465.290039,2465.180664,2463.019043,2459.647461,2456.405273,2456.039551,2454.727051,2449.574219,2448.810547,2451.255615</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-09-07 04:15:45</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>24</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2498.472412,2497.902832,2497.619629,2498.890381,2496.266113,2495.955811,2495.872314,2495.419434,2495.139160,2492.931152,2492.530518,2491.985107,2491.582031,2490.240234,2492.171631,2492.366211,2493.324219,2491.174072,2492.687988,2491.390137,2491.762939,2490.549561,2488.799316,2488.239746</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>2493.417480,2494.712158,2495.908691,2495.347656,2495.251465,2492.724609,2490.981201,2492.912109,2488.494141,2487.882568,2488.960938,2483.642334,2483.853271,2483.588867,2482.233154,2483.216797,2482.373047,2478.874756,2483.166260,2478.703857,2480.198730,2479.959961,2478.627441,2476.690918</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>2484.677246,2484.531982,2479.101074,2480.031982,2473.344727,2470.607910,2466.330078,2463.405762,2460.098145,2455.786133,2449.378662,2448.199951,2445.037109,2445.549805,2441.769287,2440.166016,2440.952637,2437.803711,2431.921143,2430.000244,2429.697998,2429.345703,2424.689209,2421.576172</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>2492.288574,2488.580566,2487.219238,2487.508545,2483.033691,2479.222168,2477.562988,2476.701660,2477.074707,2473.275391,2467.412109,2466.631104,2467.010742,2464.023926,2464.132568,2464.144287,2464.714844,2461.270996,2460.677490,2460.404053,2460.618164,2454.254883,2453.038574,2452.724609</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J51"/>
+  <dimension ref="A1:J52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2355,6 +2355,44 @@
       </c>
       <c r="F51" t="n">
         <v>2488.23974609375</v>
+      </c>
+      <c r="G51" t="n">
+        <v>2481.080078125</v>
+      </c>
+      <c r="H51" t="n">
+        <v>7.15966796875</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.2885706121247283</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0.2584981499627075</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-09-08 04:16:29</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>24</v>
+      </c>
+      <c r="F52" t="n">
+        <v>2477.419189453125</v>
       </c>
     </row>
   </sheetData>
@@ -2368,7 +2406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M51"/>
+  <dimension ref="A1:M52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5454,6 +5492,24 @@
           <t>2498.472412,2497.902832,2497.619629,2498.890381,2496.266113,2495.955811,2495.872314,2495.419434,2495.139160,2492.931152,2492.530518,2491.985107,2491.582031,2490.240234,2492.171631,2492.366211,2493.324219,2491.174072,2492.687988,2491.390137,2491.762939,2490.549561,2488.799316,2488.239746</t>
         </is>
       </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2504.540039,2498.000000,2489.169922,2491.199951,2484.209961,2488.750000,2488.989990,2505.179932,2498.610107,2489.820068,2470.030029,2482.600098,2494.979980,2491.199951,2495.820068,2494.159912,2490.459961,2482.310059,2489.570068,2495.370117,2503.689941,2484.060059,2485.320068,2481.080078</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>6.067627,0.097168,8.449707,7.690430,12.056152,7.205811,6.882324,9.760498,3.470947,3.111084,22.500489,9.385009,3.397949,0.959717,3.648437,1.793701,2.864258,8.864013,3.117920,3.979980,11.927002,6.489502,3.479248,7.159668</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.242265,0.003890,0.339459,0.308704,0.485311,0.289535,0.276511,0.389613,0.138915,0.124952,0.910940,0.378031,0.136191,0.038524,0.146182,0.071916,0.115009,0.357087,0.125239,0.159495,0.476377,0.261246,0.139992,0.288571</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>0.2584981499627075</v>
+      </c>
       <c r="K51" t="inlineStr">
         <is>
           <t>2493.417480,2494.712158,2495.908691,2495.347656,2495.251465,2492.724609,2490.981201,2492.912109,2488.494141,2487.882568,2488.960938,2483.642334,2483.853271,2483.588867,2482.233154,2483.216797,2482.373047,2478.874756,2483.166260,2478.703857,2480.198730,2479.959961,2478.627441,2476.690918</t>
@@ -5467,6 +5523,49 @@
       <c r="M51" t="inlineStr">
         <is>
           <t>2492.288574,2488.580566,2487.219238,2487.508545,2483.033691,2479.222168,2477.562988,2476.701660,2477.074707,2473.275391,2467.412109,2466.631104,2467.010742,2464.023926,2464.132568,2464.144287,2464.714844,2461.270996,2460.677490,2460.404053,2460.618164,2454.254883,2453.038574,2452.724609</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-09-08 04:16:29</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>24</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2481.562012,2480.019043,2479.484863,2480.229492,2478.785400,2479.529541,2480.090576,2480.082520,2480.500488,2480.509521,2479.626953,2480.489014,2480.944580,2479.226074,2480.080322,2480.203613,2480.713867,2478.843506,2479.585938,2479.254883,2479.980713,2478.584473,2476.783203,2477.419189</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>2478.066162,2478.067627,2477.705078,2480.049072,2479.973877,2480.073242,2476.101074,2477.551025,2477.675049,2476.041016,2476.266602,2472.732666,2474.216309,2477.384766,2473.621826,2469.849609,2472.793945,2470.337402,2472.785156,2468.377197,2469.715332,2468.403076,2468.453613,2467.896973</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>2468.033447,2467.771729,2462.981201,2463.281738,2457.397705,2456.184082,2456.124756,2452.325439,2449.128418,2446.402344,2440.932861,2440.832275,2436.896973,2436.348145,2434.118408,2431.718262,2431.252197,2428.208984,2422.222656,2421.270508,2422.248047,2421.698486,2418.853760,2417.008789</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>2475.395264,2471.795410,2469.179199,2468.895508,2465.389648,2464.136475,2464.959961,2464.035889,2464.910400,2462.074219,2456.057129,2457.409912,2457.536377,2454.198486,2454.871826,2453.816650,2453.154785,2449.902588,2449.643311,2450.043945,2451.049805,2445.423828,2444.097168,2445.098145</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J52"/>
+  <dimension ref="A1:J53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2393,6 +2393,44 @@
       </c>
       <c r="F52" t="n">
         <v>2477.419189453125</v>
+      </c>
+      <c r="G52" t="n">
+        <v>2497.449951171875</v>
+      </c>
+      <c r="H52" t="n">
+        <v>20.03076171875</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.8020485739604508</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0.390471147157734</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-09-09 04:23:07</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>24</v>
+      </c>
+      <c r="F53" t="n">
+        <v>2492.5029296875</v>
       </c>
     </row>
   </sheetData>
@@ -2406,7 +2444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M52"/>
+  <dimension ref="A1:M53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5553,6 +5591,24 @@
           <t>2481.562012,2480.019043,2479.484863,2480.229492,2478.785400,2479.529541,2480.090576,2480.082520,2480.500488,2480.509521,2479.626953,2480.489014,2480.944580,2479.226074,2480.080322,2480.203613,2480.713867,2478.843506,2479.585938,2479.254883,2479.980713,2478.584473,2476.783203,2477.419189</t>
         </is>
       </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2472.659912,2467.780029,2478.929932,2476.479980,2491.320068,2479.270020,2473.729980,2471.790039,2458.360107,2485.070068,2498.399902,2496.590088,2487.879883,2486.739990,2482.229980,2483.020020,2482.550049,2488.580078,2484.959961,2496.280029,2497.449951,2494.280029,2488.719971,2497.449951</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>8.902100,12.239014,0.554931,3.749512,12.534668,0.259521,6.360596,8.292481,22.140381,4.560547,18.772949,16.101074,6.935303,7.513916,2.149658,2.816407,1.836182,9.736572,5.374023,17.025146,17.469238,15.695556,11.936768,20.030762</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.360021,0.495952,0.022386,0.151405,0.503134,0.010468,0.257126,0.335485,0.900616,0.183518,0.751399,0.644923,0.278764,0.302159,0.086602,0.113427,0.073964,0.391250,0.216262,0.682021,0.699483,0.629262,0.479635,0.802049</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>0.390471147157734</v>
+      </c>
       <c r="K52" t="inlineStr">
         <is>
           <t>2478.066162,2478.067627,2477.705078,2480.049072,2479.973877,2480.073242,2476.101074,2477.551025,2477.675049,2476.041016,2476.266602,2472.732666,2474.216309,2477.384766,2473.621826,2469.849609,2472.793945,2470.337402,2472.785156,2468.377197,2469.715332,2468.403076,2468.453613,2467.896973</t>
@@ -5566,6 +5622,49 @@
       <c r="M52" t="inlineStr">
         <is>
           <t>2475.395264,2471.795410,2469.179199,2468.895508,2465.389648,2464.136475,2464.959961,2464.035889,2464.910400,2462.074219,2456.057129,2457.409912,2457.536377,2454.198486,2454.871826,2453.816650,2453.154785,2449.902588,2449.643311,2450.043945,2451.049805,2445.423828,2444.097168,2445.098145</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-09-09 04:23:07</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>24</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2497.199707,2495.951172,2494.578125,2494.526367,2492.582520,2493.605225,2494.610352,2492.437744,2493.880371,2494.244385,2493.570801,2494.124512,2493.886475,2493.314453,2493.985840,2494.202637,2493.595703,2493.362061,2493.242188,2492.764648,2494.500000,2492.813232,2491.713623,2492.502930</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>2494.379883,2494.279541,2494.756592,2494.481689,2495.579102,2491.296631,2491.072510,2492.009277,2490.179443,2490.820557,2490.458252,2488.123535,2490.496582,2493.412354,2489.248535,2486.542725,2488.993164,2487.903809,2488.537598,2484.938965,2486.294922,2483.617676,2485.767090,2485.367676</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>2483.573975,2482.350586,2476.347168,2476.799316,2472.124023,2473.011719,2472.313232,2467.111816,2465.743896,2464.634521,2460.609863,2459.520996,2456.633057,2457.783203,2455.865234,2453.964844,2452.201172,2451.753662,2445.319336,2443.412842,2445.753174,2445.015381,2442.663086,2440.657959</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>2490.679932,2487.433105,2483.566650,2483.589844,2480.014648,2478.939697,2480.060059,2477.619141,2479.276367,2477.738037,2472.464355,2474.467773,2474.721191,2471.571533,2471.942871,2472.049805,2470.305420,2468.984131,2468.225342,2467.303467,2469.332275,2465.716064,2464.264160,2465.665039</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J53"/>
+  <dimension ref="A1:J54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2431,6 +2431,44 @@
       </c>
       <c r="F53" t="n">
         <v>2492.5029296875</v>
+      </c>
+      <c r="G53" t="n">
+        <v>2476.679931640625</v>
+      </c>
+      <c r="H53" t="n">
+        <v>15.822998046875</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.6388794064477029</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0.6335056791666231</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-09-10 04:19:57</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>24</v>
+      </c>
+      <c r="F54" t="n">
+        <v>2472.75048828125</v>
       </c>
     </row>
   </sheetData>
@@ -2444,7 +2482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M53"/>
+  <dimension ref="A1:M54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5652,6 +5690,24 @@
           <t>2497.199707,2495.951172,2494.578125,2494.526367,2492.582520,2493.605225,2494.610352,2492.437744,2493.880371,2494.244385,2493.570801,2494.124512,2493.886475,2493.314453,2493.985840,2494.202637,2493.595703,2493.362061,2493.242188,2492.764648,2494.500000,2492.813232,2491.713623,2492.502930</t>
         </is>
       </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2496.260010,2500.879883,2510.209961,2519.709961,2490.020020,2487.139893,2500.149902,2511.100098,2502.060059,2498.780029,2489.850098,2495.479980,2493.250000,2481.040039,2465.000000,2471.120117,2461.199951,2449.500000,2467.719971,2464.040039,2462.919922,2474.169922,2474.500000,2476.679932</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>0.939697,4.928711,15.631836,25.183594,2.562500,6.465332,5.539550,18.662354,8.179688,4.535644,3.720703,1.355468,0.636475,12.274414,28.985840,23.082520,32.395752,43.862061,25.522217,28.724609,31.580078,18.643310,17.213623,15.822998</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>0.037644,0.197079,0.622730,0.999464,0.102911,0.259950,0.221569,0.743194,0.326918,0.181514,0.149435,0.054317,0.025528,0.494729,1.175896,0.934091,1.316258,1.790654,1.034243,1.165753,1.282221,0.753518,0.695640,0.638879</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>0.6335056791666231</v>
+      </c>
       <c r="K53" t="inlineStr">
         <is>
           <t>2494.379883,2494.279541,2494.756592,2494.481689,2495.579102,2491.296631,2491.072510,2492.009277,2490.179443,2490.820557,2490.458252,2488.123535,2490.496582,2493.412354,2489.248535,2486.542725,2488.993164,2487.903809,2488.537598,2484.938965,2486.294922,2483.617676,2485.767090,2485.367676</t>
@@ -5665,6 +5721,49 @@
       <c r="M53" t="inlineStr">
         <is>
           <t>2490.679932,2487.433105,2483.566650,2483.589844,2480.014648,2478.939697,2480.060059,2477.619141,2479.276367,2477.738037,2472.464355,2474.467773,2474.721191,2471.571533,2471.942871,2472.049805,2470.305420,2468.984131,2468.225342,2467.303467,2469.332275,2465.716064,2464.264160,2465.665039</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-09-10 04:19:57</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>24</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2474.758301,2473.916504,2473.909180,2474.222900,2472.773438,2471.825928,2472.929688,2471.627930,2471.762695,2471.485107,2471.504395,2472.755859,2472.661133,2472.234131,2472.903320,2472.802246,2472.854492,2471.608643,2472.568115,2472.487305,2473.136963,2473.281738,2471.385254,2472.750488</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>2472.226562,2472.267090,2472.068359,2472.097168,2474.054932,2472.138428,2469.298096,2469.284424,2467.591553,2471.231934,2470.364990,2466.999512,2467.599854,2471.321777,2468.395020,2466.850830,2467.796875,2466.227295,2468.337158,2465.420166,2467.788086,2466.257324,2465.259521,2465.528809</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>2462.386963,2460.896484,2456.087402,2456.031982,2451.001709,2448.758057,2449.414795,2445.032227,2442.562988,2440.729004,2436.723145,2437.000977,2435.618652,2437.676025,2436.316895,2434.143555,2434.244141,2432.150391,2428.005859,2427.874268,2429.193359,2430.556885,2427.407471,2426.668213</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>2469.083984,2465.083496,2462.938477,2462.192871,2458.242188,2455.723877,2456.441895,2455.100098,2456.096924,2453.079346,2448.401611,2450.507080,2451.409668,2450.394287,2451.352295,2450.417480,2450.113525,2447.484863,2448.332275,2448.720215,2450.257568,2445.962891,2444.699219,2446.358887</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J54"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2469,6 +2469,44 @@
       </c>
       <c r="F54" t="n">
         <v>2472.75048828125</v>
+      </c>
+      <c r="G54" t="n">
+        <v>2450.409912109375</v>
+      </c>
+      <c r="H54" t="n">
+        <v>22.340576171875</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.9117077131247672</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0.7561731040139835</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-09-11 04:19:43</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>24</v>
+      </c>
+      <c r="F55" t="n">
+        <v>2447.98193359375</v>
       </c>
     </row>
   </sheetData>
@@ -2482,7 +2520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M54"/>
+  <dimension ref="A1:M55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5751,6 +5789,24 @@
           <t>2474.758301,2473.916504,2473.909180,2474.222900,2472.773438,2471.825928,2472.929688,2471.627930,2471.762695,2471.485107,2471.504395,2472.755859,2472.661133,2472.234131,2472.903320,2472.802246,2472.854492,2471.608643,2472.568115,2472.487305,2473.136963,2473.281738,2471.385254,2472.750488</t>
         </is>
       </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2481.229980,2479.600098,2472.199951,2470.620117,2467.800049,2463.399902,2461.500000,2413.469971,2434.520020,2443.229980,2440.439941,2447.669922,2465.590088,2467.520020,2461.790039,2460.870117,2459.479980,2444.310059,2437.209961,2455.989990,2453.659912,2446.159912,2446.189941,2450.409912</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>6.471679,5.683594,1.709229,3.602783,4.973389,8.426026,11.429688,58.157959,37.242675,28.255127,31.064454,25.085937,7.071045,4.714111,11.113281,11.932129,13.374512,27.298584,35.358154,16.497315,19.477051,27.121826,25.195313,22.340576</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>0.260825,0.229214,0.069138,0.145825,0.201531,0.342049,0.464338,2.409724,1.529775,1.156466,1.272904,1.024891,0.286789,0.191047,0.451431,0.484874,0.543794,1.116822,1.450764,0.671718,0.793796,1.108751,1.029982,0.911708</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>0.7561731040139835</v>
+      </c>
       <c r="K54" t="inlineStr">
         <is>
           <t>2472.226562,2472.267090,2472.068359,2472.097168,2474.054932,2472.138428,2469.298096,2469.284424,2467.591553,2471.231934,2470.364990,2466.999512,2467.599854,2471.321777,2468.395020,2466.850830,2467.796875,2466.227295,2468.337158,2465.420166,2467.788086,2466.257324,2465.259521,2465.528809</t>
@@ -5764,6 +5820,49 @@
       <c r="M54" t="inlineStr">
         <is>
           <t>2469.083984,2465.083496,2462.938477,2462.192871,2458.242188,2455.723877,2456.441895,2455.100098,2456.096924,2453.079346,2448.401611,2450.507080,2451.409668,2450.394287,2451.352295,2450.417480,2450.113525,2447.484863,2448.332275,2448.720215,2450.257568,2445.962891,2444.699219,2446.358887</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-09-11 04:19:43</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>24</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2450.119141,2449.344482,2449.940918,2450.240967,2451.133545,2450.550781,2451.109863,2450.607910,2450.309082,2451.499023,2451.072510,2452.131104,2452.486328,2452.554199,2453.066650,2452.870117,2452.479004,2451.628174,2452.169434,2450.817871,2450.888672,2449.943848,2448.077881,2447.981934</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>2447.966309,2449.516602,2448.148926,2449.585938,2452.023926,2450.749023,2449.824707,2448.793457,2446.113770,2450.098633,2449.517578,2447.241943,2448.223389,2451.359863,2450.389160,2446.929688,2447.808105,2448.370361,2448.814209,2443.669678,2447.165283,2444.040039,2443.401367,2440.973633</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>2435.159424,2434.210938,2430.371338,2429.355957,2428.114502,2426.355469,2426.426270,2422.234863,2419.616699,2417.572754,2414.136963,2412.716797,2410.919434,2413.367432,2413.170898,2410.625000,2410.762939,2409.169922,2404.631592,2401.474121,2401.910889,2402.132324,2399.891846,2398.042969</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>2442.836182,2439.120605,2438.322754,2436.500732,2435.935791,2433.876709,2434.994385,2433.500488,2434.182373,2431.350586,2426.599609,2428.641113,2428.561279,2428.078857,2430.793945,2429.380127,2426.871826,2425.724854,2425.812012,2423.017822,2424.418457,2419.836914,2419.021484,2419.115234</t>
         </is>
       </c>
     </row>

--- a/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
+++ b/timesfm-2.5-200m-pytorch/ETH-USD_1h_30d_h24/log.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J55"/>
+  <dimension ref="A1:J56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2507,6 +2507,44 @@
       </c>
       <c r="F55" t="n">
         <v>2447.98193359375</v>
+      </c>
+      <c r="G55" t="n">
+        <v>2511.8798828125</v>
+      </c>
+      <c r="H55" t="n">
+        <v>63.89794921875</v>
+      </c>
+      <c r="I55" t="n">
+        <v>2.543829808740885</v>
+      </c>
+      <c r="J55" t="n">
+        <v>2.615334615279242</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-09-12 04:17:52</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>24</v>
+      </c>
+      <c r="F56" t="n">
+        <v>2490.846435546875</v>
       </c>
     </row>
   </sheetData>
@@ -2520,7 +2558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M55"/>
+  <dimension ref="A1:M56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5850,6 +5888,24 @@
           <t>2450.119141,2449.344482,2449.940918,2450.240967,2451.133545,2450.550781,2451.109863,2450.607910,2450.309082,2451.499023,2451.072510,2452.131104,2452.486328,2452.554199,2453.066650,2452.870117,2452.479004,2451.628174,2452.169434,2450.817871,2450.888672,2449.943848,2448.077881,2447.981934</t>
         </is>
       </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2467.469971,2466.159912,2466.040039,2475.709961,2468.310059,2461.010010,2457.610107,2510.169922,2626.739990,2607.100098,2558.800049,2577.439941,2566.139893,2536.000000,2539.010010,2530.060059,2516.330078,2511.459961,2516.100098,2511.060059,2513.340088,2514.389893,2512.899902,2511.879883</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>17.350830,16.815430,16.099121,25.468994,17.176514,10.459229,6.500244,59.562012,176.430908,155.601075,107.727539,125.308837,113.653565,83.445801,85.943360,77.189942,63.851074,59.831787,63.930664,60.242188,62.451416,64.446045,64.822021,63.897949</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>0.703183,0.681847,0.652833,1.028755,0.695882,0.424997,0.264495,2.372828,6.716725,5.968358,4.210080,4.861756,4.428970,3.290450,3.384916,3.050913,2.537468,2.382351,2.540863,2.399074,2.484798,2.563089,2.579570,2.543830</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>2.615334615279242</v>
+      </c>
       <c r="K55" t="inlineStr">
         <is>
           <t>2447.966309,2449.516602,2448.148926,2449.585938,2452.023926,2450.749023,2449.824707,2448.793457,2446.113770,2450.098633,2449.517578,2447.241943,2448.223389,2451.359863,2450.389160,2446.929688,2447.808105,2448.370361,2448.814209,2443.669678,2447.165283,2444.040039,2443.401367,2440.973633</t>
@@ -5863,6 +5919,49 @@
       <c r="M55" t="inlineStr">
         <is>
           <t>2442.836182,2439.120605,2438.322754,2436.500732,2435.935791,2433.876709,2434.994385,2433.500488,2434.182373,2431.350586,2426.599609,2428.641113,2428.561279,2428.078857,2430.793945,2429.380127,2426.871826,2425.724854,2425.812012,2423.017822,2424.418457,2419.836914,2419.021484,2419.115234</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-09-12 04:17:52</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>ETH-USD</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>24</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2511.205322,2509.528564,2508.287354,2507.708008,2507.758789,2506.948730,2505.855957,2503.460938,2502.809082,2501.979980,2500.980713,2500.898438,2498.820801,2497.524170,2496.728516,2494.369141,2494.117188,2492.467041,2491.899658,2491.181396,2491.604980,2490.705078,2490.104736,2490.846436</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>2510.087158,2508.637939,2508.242676,2506.195312,2507.093262,2505.547119,2499.458252,2499.779053,2497.089355,2499.552979,2497.160156,2494.262695,2489.469727,2492.969238,2490.762207,2489.160156,2487.483887,2485.916992,2483.254639,2480.257812,2484.547363,2484.175781,2483.177979,2484.202637</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>2500.894531,2498.744385,2494.496094,2491.131104,2488.140137,2483.693848,2478.571289,2471.283203,2468.360107,2465.282715,2462.612549,2457.872803,2453.231934,2453.195312,2449.825439,2445.859619,2443.995117,2442.179688,2436.541260,2432.562744,2434.873047,2433.981201,2431.358643,2428.644043</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>2506.665283,2502.338867,2500.887451,2498.666016,2496.673096,2492.830078,2489.661865,2486.291504,2484.500488,2481.604004,2478.656006,2477.873535,2476.345947,2472.798340,2473.396484,2469.073975,2466.346680,2464.590332,2462.234619,2462.221191,2462.879883,2458.699219,2457.694824,2456.783691</t>
         </is>
       </c>
     </row>
